--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B02_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B02_Normal_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J835"/>
+  <dimension ref="A1:K835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -514,7 +519,10 @@
           <t>Ostium</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -551,6 +559,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>34.19156206107118</v>
       </c>
     </row>
@@ -589,6 +600,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>13.70480619480816</v>
       </c>
     </row>
@@ -627,6 +641,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>13.70480619480816</v>
       </c>
     </row>
@@ -665,6 +682,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>10.07391314257579</v>
       </c>
     </row>
@@ -703,6 +723,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>9.086312375561954</v>
       </c>
     </row>
@@ -741,6 +764,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>8.746824124790566</v>
       </c>
     </row>
@@ -779,6 +805,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>8.218179902291242</v>
       </c>
     </row>
@@ -817,6 +846,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>7.836770619901664</v>
       </c>
     </row>
@@ -855,6 +887,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>7.162722102583384</v>
       </c>
     </row>
@@ -893,6 +928,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>7.310981061882006</v>
       </c>
     </row>
@@ -931,6 +969,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>7.037492341720552</v>
       </c>
     </row>
@@ -969,6 +1010,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>7.037492341720552</v>
       </c>
     </row>
@@ -1007,6 +1051,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
         <v>7.35339106782276</v>
       </c>
     </row>
@@ -1045,6 +1092,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>7.583117327938817</v>
       </c>
     </row>
@@ -1083,6 +1133,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>7.242916983385382</v>
       </c>
     </row>
@@ -1121,6 +1174,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>7.242916983385382</v>
       </c>
     </row>
@@ -1159,6 +1215,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>7.029415156162294</v>
       </c>
     </row>
@@ -1197,6 +1256,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>6.865852157295507</v>
       </c>
     </row>
@@ -1235,6 +1297,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>11.25822716312403</v>
       </c>
     </row>
@@ -1273,6 +1338,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>11.25822716312403</v>
       </c>
     </row>
@@ -1311,6 +1379,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>11.31967180213814</v>
       </c>
     </row>
@@ -1349,6 +1420,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
         <v>11.31967180213814</v>
       </c>
     </row>
@@ -1387,6 +1461,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>9.340757367394243</v>
       </c>
     </row>
@@ -1425,6 +1502,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
         <v>7.37504271750718</v>
       </c>
     </row>
@@ -1463,6 +1543,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>7.00396769655076</v>
       </c>
     </row>
@@ -1501,6 +1584,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>6.246385418365628</v>
       </c>
     </row>
@@ -1539,6 +1625,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.961063861809979</v>
       </c>
     </row>
@@ -1577,6 +1666,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.810927717997912</v>
       </c>
     </row>
@@ -1615,6 +1707,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
         <v>4.604746195129942</v>
       </c>
     </row>
@@ -1653,6 +1748,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
         <v>4.604144266601407</v>
       </c>
     </row>
@@ -1691,6 +1789,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
         <v>4.604144266601407</v>
       </c>
     </row>
@@ -1729,6 +1830,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>4.520964526493206</v>
       </c>
     </row>
@@ -1767,6 +1871,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
         <v>4.52056512164341</v>
       </c>
     </row>
@@ -1805,6 +1912,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
         <v>4.525642865811913</v>
       </c>
     </row>
@@ -1843,6 +1953,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
         <v>4.604866533467261</v>
       </c>
     </row>
@@ -1881,6 +1994,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
         <v>4.652057169465017</v>
       </c>
     </row>
@@ -1919,6 +2035,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
         <v>4.652749876206823</v>
       </c>
     </row>
@@ -1957,6 +2076,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
         <v>4.696696339864014</v>
       </c>
     </row>
@@ -1995,6 +2117,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
         <v>4.748860831718122</v>
       </c>
     </row>
@@ -2033,6 +2158,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>4.811573344793401</v>
       </c>
     </row>
@@ -2071,6 +2199,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
         <v>4.816660468128911</v>
       </c>
     </row>
@@ -2109,6 +2240,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
         <v>4.814067453605086</v>
       </c>
     </row>
@@ -2147,6 +2281,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>4.719044901501696</v>
       </c>
     </row>
@@ -2185,6 +2322,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>4.719044901501696</v>
       </c>
     </row>
@@ -2223,6 +2363,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>4.690335297446286</v>
       </c>
     </row>
@@ -2261,6 +2404,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
         <v>4.828542917916744</v>
       </c>
     </row>
@@ -2299,6 +2445,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
         <v>4.96164872873551</v>
       </c>
     </row>
@@ -2337,6 +2486,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
         <v>5.039110666438193</v>
       </c>
     </row>
@@ -2375,6 +2527,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
         <v>5.074606316374426</v>
       </c>
     </row>
@@ -2413,6 +2568,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
         <v>5.065709663904308</v>
       </c>
     </row>
@@ -2451,6 +2609,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>5.065709663904308</v>
       </c>
     </row>
@@ -2489,6 +2650,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
         <v>5.054404024498178</v>
       </c>
     </row>
@@ -2527,6 +2691,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
         <v>5.039667093960332</v>
       </c>
     </row>
@@ -2565,6 +2732,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
         <v>5.039667093960332</v>
       </c>
     </row>
@@ -2603,6 +2773,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>4.903338995259718</v>
       </c>
     </row>
@@ -2641,6 +2814,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
         <v>4.894737213849557</v>
       </c>
     </row>
@@ -2679,6 +2855,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
         <v>4.894640885829854</v>
       </c>
     </row>
@@ -2717,6 +2896,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
         <v>5.227704118554311</v>
       </c>
     </row>
@@ -2755,6 +2937,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
         <v>5.471537998053314</v>
       </c>
     </row>
@@ -2793,6 +2978,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
         <v>5.507123672228847</v>
       </c>
     </row>
@@ -2831,6 +3019,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
         <v>5.518110861263691</v>
       </c>
     </row>
@@ -2869,6 +3060,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
         <v>5.518110861263691</v>
       </c>
     </row>
@@ -2907,6 +3101,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
         <v>5.49335846138426</v>
       </c>
     </row>
@@ -2945,6 +3142,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
         <v>5.44725507868274</v>
       </c>
     </row>
@@ -2983,6 +3183,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
         <v>5.337330240029654</v>
       </c>
     </row>
@@ -3021,6 +3224,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
         <v>5.272110875401731</v>
       </c>
     </row>
@@ -3059,6 +3265,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
         <v>5.271395152924137</v>
       </c>
     </row>
@@ -3097,6 +3306,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
         <v>5.243135627754994</v>
       </c>
     </row>
@@ -3135,6 +3347,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
         <v>5.219658813463474</v>
       </c>
     </row>
@@ -3173,6 +3388,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
         <v>5.219658813463474</v>
       </c>
     </row>
@@ -3211,6 +3429,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
         <v>5.17805189203108</v>
       </c>
     </row>
@@ -3249,6 +3470,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
         <v>5.110164223168892</v>
       </c>
     </row>
@@ -3287,6 +3511,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
         <v>5.108337636734058</v>
       </c>
     </row>
@@ -3325,6 +3552,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
         <v>4.984118224760408</v>
       </c>
     </row>
@@ -3363,6 +3593,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
         <v>4.982660549268322</v>
       </c>
     </row>
@@ -3401,6 +3634,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
         <v>4.919601068125682</v>
       </c>
     </row>
@@ -3439,6 +3675,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
         <v>4.888790180696684</v>
       </c>
     </row>
@@ -3477,6 +3716,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
         <v>4.889922425709138</v>
       </c>
     </row>
@@ -3515,6 +3757,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
         <v>5.068979998549168</v>
       </c>
     </row>
@@ -3553,6 +3798,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
         <v>5.2087856985976</v>
       </c>
     </row>
@@ -3591,6 +3839,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
         <v>5.2419450880851</v>
       </c>
     </row>
@@ -3629,6 +3880,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
         <v>5.399676500771488</v>
       </c>
     </row>
@@ -3667,6 +3921,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3705,6 +3962,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3743,6 +4003,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3781,6 +4044,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3819,6 +4085,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3857,6 +4126,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3895,6 +4167,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3933,6 +4208,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -3971,6 +4249,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -4009,6 +4290,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
         <v>5.447998957898347</v>
       </c>
     </row>
@@ -4047,6 +4331,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
         <v>5.441091362290202</v>
       </c>
     </row>
@@ -4085,6 +4372,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
         <v>5.350149106817893</v>
       </c>
     </row>
@@ -4123,6 +4413,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
         <v>5.350149106817893</v>
       </c>
     </row>
@@ -4161,6 +4454,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
         <v>5.321137760810805</v>
       </c>
     </row>
@@ -4199,6 +4495,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
         <v>5.293142593572973</v>
       </c>
     </row>
@@ -4237,6 +4536,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
         <v>5.29220258959118</v>
       </c>
     </row>
@@ -4275,6 +4577,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
         <v>5.182799095741214</v>
       </c>
     </row>
@@ -4313,6 +4618,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
         <v>5.184480786233429</v>
       </c>
     </row>
@@ -4351,6 +4659,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
         <v>5.261606117541525</v>
       </c>
     </row>
@@ -4389,6 +4700,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
         <v>5.281654855398788</v>
       </c>
     </row>
@@ -4427,6 +4741,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
         <v>5.274356776317311</v>
       </c>
     </row>
@@ -4465,6 +4782,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
         <v>5.273946144825915</v>
       </c>
     </row>
@@ -4503,6 +4823,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
         <v>5.255614022299906</v>
       </c>
     </row>
@@ -4541,6 +4864,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="n">
         <v>5.168052363573718</v>
       </c>
     </row>
@@ -4579,6 +4905,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
         <v>4.978265744667874</v>
       </c>
     </row>
@@ -4617,6 +4946,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
         <v>4.857686321864007</v>
       </c>
     </row>
@@ -4655,6 +4987,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
         <v>4.570408572191353</v>
       </c>
     </row>
@@ -4693,6 +5028,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="n">
         <v>4.47667289145723</v>
       </c>
     </row>
@@ -4731,6 +5069,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
         <v>4.475535920170302</v>
       </c>
     </row>
@@ -4769,6 +5110,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
         <v>4.481449958104311</v>
       </c>
     </row>
@@ -4807,6 +5151,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
         <v>4.48827868502149</v>
       </c>
     </row>
@@ -4845,6 +5192,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
         <v>4.48827868502149</v>
       </c>
     </row>
@@ -4883,6 +5233,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
         <v>4.448927252778354</v>
       </c>
     </row>
@@ -4921,6 +5274,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
         <v>4.390655537686455</v>
       </c>
     </row>
@@ -4959,6 +5315,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
         <v>4.388062611826737</v>
       </c>
     </row>
@@ -4997,6 +5356,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
         <v>4.159196111622991</v>
       </c>
     </row>
@@ -5035,6 +5397,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
         <v>4.025915884462803</v>
       </c>
     </row>
@@ -5073,6 +5438,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
         <v>3.955044089417568</v>
       </c>
     </row>
@@ -5111,6 +5479,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="n">
         <v>3.879389486560219</v>
       </c>
     </row>
@@ -5149,6 +5520,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="n">
         <v>3.720063683783769</v>
       </c>
     </row>
@@ -5187,6 +5561,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="n">
         <v>3.663142399112596</v>
       </c>
     </row>
@@ -5225,6 +5602,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="n">
         <v>3.616880369179896</v>
       </c>
     </row>
@@ -5263,6 +5643,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
         <v>3.483863781539523</v>
       </c>
     </row>
@@ -5301,6 +5684,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
         <v>3.272254965340389</v>
       </c>
     </row>
@@ -5339,6 +5725,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" t="n">
         <v>3.163508701007812</v>
       </c>
     </row>
@@ -5377,6 +5766,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>2</v>
+      </c>
+      <c r="K130" t="n">
         <v>2.897312546155748</v>
       </c>
     </row>
@@ -5415,6 +5807,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" t="n">
         <v>2.897312546155748</v>
       </c>
     </row>
@@ -5453,6 +5848,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>2</v>
+      </c>
+      <c r="K132" t="n">
         <v>2.86197877602613</v>
       </c>
     </row>
@@ -5491,6 +5889,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K133" t="n">
         <v>2.86197877602613</v>
       </c>
     </row>
@@ -5529,6 +5930,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
         <v>2.777572678505286</v>
       </c>
     </row>
@@ -5567,6 +5971,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
         <v>3.105921000356857</v>
       </c>
     </row>
@@ -5605,6 +6012,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>2</v>
+      </c>
+      <c r="K136" t="n">
         <v>3.105921000356857</v>
       </c>
     </row>
@@ -5643,6 +6053,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>2</v>
+      </c>
+      <c r="K137" t="n">
         <v>3.105921000356857</v>
       </c>
     </row>
@@ -5681,6 +6094,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>2</v>
+      </c>
+      <c r="K138" t="n">
         <v>3.208083762654137</v>
       </c>
     </row>
@@ -5719,6 +6135,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="n">
         <v>3.314667267949773</v>
       </c>
     </row>
@@ -5757,6 +6176,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="n">
         <v>3.40206481722016</v>
       </c>
     </row>
@@ -5795,6 +6217,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>2</v>
+      </c>
+      <c r="K141" t="n">
         <v>3.720614311620269</v>
       </c>
     </row>
@@ -5833,6 +6258,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" t="n">
         <v>3.863251215112728</v>
       </c>
     </row>
@@ -5871,6 +6299,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="n">
         <v>4.598825145385264</v>
       </c>
     </row>
@@ -5909,6 +6340,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" t="n">
         <v>4.965709738323598</v>
       </c>
     </row>
@@ -5947,6 +6381,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="n">
         <v>5.431995942669801</v>
       </c>
     </row>
@@ -5985,6 +6422,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="n">
         <v>5.438284597218944</v>
       </c>
     </row>
@@ -6023,6 +6463,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="n">
         <v>5.569106366252102</v>
       </c>
     </row>
@@ -6061,6 +6504,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="n">
         <v>5.693965434565409</v>
       </c>
     </row>
@@ -6099,6 +6545,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>2</v>
+      </c>
+      <c r="K149" t="n">
         <v>5.693965434565409</v>
       </c>
     </row>
@@ -6137,6 +6586,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>2</v>
+      </c>
+      <c r="K150" t="n">
         <v>5.957387896354917</v>
       </c>
     </row>
@@ -6175,6 +6627,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="n">
         <v>6.0632511406987</v>
       </c>
     </row>
@@ -6213,6 +6668,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" t="n">
         <v>6.278040427638199</v>
       </c>
     </row>
@@ -6251,6 +6709,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>2</v>
+      </c>
+      <c r="K153" t="n">
         <v>6.331158442464466</v>
       </c>
     </row>
@@ -6289,6 +6750,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" t="n">
         <v>6.33339832003768</v>
       </c>
     </row>
@@ -6327,6 +6791,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" t="n">
         <v>6.374496999724887</v>
       </c>
     </row>
@@ -6365,6 +6832,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="n">
         <v>6.511712565723965</v>
       </c>
     </row>
@@ -6403,6 +6873,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>2</v>
+      </c>
+      <c r="K157" t="n">
         <v>6.511712565723965</v>
       </c>
     </row>
@@ -6441,6 +6914,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>2</v>
+      </c>
+      <c r="K158" t="n">
         <v>6.511712565723965</v>
       </c>
     </row>
@@ -6479,6 +6955,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>2</v>
+      </c>
+      <c r="K159" t="n">
         <v>6.598321683178505</v>
       </c>
     </row>
@@ -6517,6 +6996,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" t="n">
         <v>6.599548682223191</v>
       </c>
     </row>
@@ -6555,6 +7037,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="n">
         <v>6.61136411332074</v>
       </c>
     </row>
@@ -6593,6 +7078,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" t="n">
         <v>6.588846186423175</v>
       </c>
     </row>
@@ -6631,6 +7119,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" t="n">
         <v>6.448243618522249</v>
       </c>
     </row>
@@ -6669,6 +7160,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>2</v>
+      </c>
+      <c r="K164" t="n">
         <v>6.448243618522249</v>
       </c>
     </row>
@@ -6707,6 +7201,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" t="n">
         <v>6.276555442004401</v>
       </c>
     </row>
@@ -6745,6 +7242,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" t="n">
         <v>6.187751350891288</v>
       </c>
     </row>
@@ -6783,6 +7283,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="n">
         <v>6.187751350891288</v>
       </c>
     </row>
@@ -6821,6 +7324,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>2</v>
+      </c>
+      <c r="K168" t="n">
         <v>6.187751350891288</v>
       </c>
     </row>
@@ -6859,6 +7365,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>2</v>
+      </c>
+      <c r="K169" t="n">
         <v>5.968090253986067</v>
       </c>
     </row>
@@ -6897,6 +7406,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>2</v>
+      </c>
+      <c r="K170" t="n">
         <v>5.968090253986067</v>
       </c>
     </row>
@@ -6935,6 +7447,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>2</v>
+      </c>
+      <c r="K171" t="n">
         <v>5.962401649014894</v>
       </c>
     </row>
@@ -6973,6 +7488,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" t="n">
         <v>5.625522615893285</v>
       </c>
     </row>
@@ -7011,6 +7529,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" t="n">
         <v>5.625522615893285</v>
       </c>
     </row>
@@ -7049,6 +7570,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" t="n">
         <v>5.625522615893285</v>
       </c>
     </row>
@@ -7087,6 +7611,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>2</v>
+      </c>
+      <c r="K175" t="n">
         <v>5.618642598431981</v>
       </c>
     </row>
@@ -7125,6 +7652,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" t="n">
         <v>5.48374073803944</v>
       </c>
     </row>
@@ -7163,6 +7693,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>2</v>
+      </c>
+      <c r="K177" t="n">
         <v>5.48374073803944</v>
       </c>
     </row>
@@ -7201,6 +7734,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>2</v>
+      </c>
+      <c r="K178" t="n">
         <v>5.261902283668141</v>
       </c>
     </row>
@@ -7239,6 +7775,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" t="n">
         <v>5.261902283668141</v>
       </c>
     </row>
@@ -7277,6 +7816,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" t="n">
         <v>5.256868421934375</v>
       </c>
     </row>
@@ -7315,6 +7857,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" t="n">
         <v>5.173479699263016</v>
       </c>
     </row>
@@ -7353,6 +7898,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>2</v>
+      </c>
+      <c r="K182" t="n">
         <v>5.16871136317628</v>
       </c>
     </row>
@@ -7391,6 +7939,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" t="n">
         <v>4.94467320691931</v>
       </c>
     </row>
@@ -7429,6 +7980,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" t="n">
         <v>4.942257118594265</v>
       </c>
     </row>
@@ -7467,6 +8021,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>2</v>
+      </c>
+      <c r="K185" t="n">
         <v>4.942257118594265</v>
       </c>
     </row>
@@ -7505,6 +8062,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" t="n">
         <v>4.898274204949511</v>
       </c>
     </row>
@@ -7543,6 +8103,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>2</v>
+      </c>
+      <c r="K187" t="n">
         <v>4.898274204949511</v>
       </c>
     </row>
@@ -7581,6 +8144,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="n">
         <v>4.826177102010751</v>
       </c>
     </row>
@@ -7619,6 +8185,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>2</v>
+      </c>
+      <c r="K189" t="n">
         <v>4.814986343211633</v>
       </c>
     </row>
@@ -7657,6 +8226,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>2</v>
+      </c>
+      <c r="K190" t="n">
         <v>4.797564938606851</v>
       </c>
     </row>
@@ -7695,6 +8267,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" t="n">
         <v>4.794697441321851</v>
       </c>
     </row>
@@ -7733,6 +8308,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
         <v>4.794697441321851</v>
       </c>
     </row>
@@ -7771,6 +8349,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>2</v>
+      </c>
+      <c r="K193" t="n">
         <v>4.737079268416625</v>
       </c>
     </row>
@@ -7809,6 +8390,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>2</v>
+      </c>
+      <c r="K194" t="n">
         <v>4.737079268416625</v>
       </c>
     </row>
@@ -7847,6 +8431,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>2</v>
+      </c>
+      <c r="K195" t="n">
         <v>4.724954951187553</v>
       </c>
     </row>
@@ -7885,6 +8472,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>2</v>
+      </c>
+      <c r="K196" t="n">
         <v>4.726859722683427</v>
       </c>
     </row>
@@ -7923,6 +8513,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>2</v>
+      </c>
+      <c r="K197" t="n">
         <v>4.729177276649879</v>
       </c>
     </row>
@@ -7961,6 +8554,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" t="n">
         <v>4.675958750136996</v>
       </c>
     </row>
@@ -7999,6 +8595,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>2</v>
+      </c>
+      <c r="K199" t="n">
         <v>4.624668674974948</v>
       </c>
     </row>
@@ -8037,6 +8636,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>2</v>
+      </c>
+      <c r="K200" t="n">
         <v>4.567298609375684</v>
       </c>
     </row>
@@ -8075,6 +8677,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" t="n">
         <v>4.515915213569598</v>
       </c>
     </row>
@@ -8113,6 +8718,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" t="n">
         <v>4.46402541828445</v>
       </c>
     </row>
@@ -8151,6 +8759,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>2</v>
+      </c>
+      <c r="K203" t="n">
         <v>4.46402541828445</v>
       </c>
     </row>
@@ -8189,6 +8800,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>2</v>
+      </c>
+      <c r="K204" t="n">
         <v>4.46402541828445</v>
       </c>
     </row>
@@ -8227,6 +8841,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" t="n">
         <v>4.303009345775528</v>
       </c>
     </row>
@@ -8265,6 +8882,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>2</v>
+      </c>
+      <c r="K206" t="n">
         <v>4.22495659035648</v>
       </c>
     </row>
@@ -8303,6 +8923,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>2</v>
+      </c>
+      <c r="K207" t="n">
         <v>4.016251878796528</v>
       </c>
     </row>
@@ -8341,6 +8964,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>2</v>
+      </c>
+      <c r="K208" t="n">
         <v>4.016251878796528</v>
       </c>
     </row>
@@ -8379,6 +9005,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>2</v>
+      </c>
+      <c r="K209" t="n">
         <v>3.958532894978139</v>
       </c>
     </row>
@@ -8417,6 +9046,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" t="n">
         <v>3.807466580617577</v>
       </c>
     </row>
@@ -8455,6 +9087,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>2</v>
+      </c>
+      <c r="K211" t="n">
         <v>3.650102275673494</v>
       </c>
     </row>
@@ -8493,6 +9128,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" t="n">
         <v>3.429924988763214</v>
       </c>
     </row>
@@ -8531,6 +9169,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>2</v>
+      </c>
+      <c r="K213" t="n">
         <v>3.330474963041382</v>
       </c>
     </row>
@@ -8569,6 +9210,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>2</v>
+      </c>
+      <c r="K214" t="n">
         <v>3.169558168301719</v>
       </c>
     </row>
@@ -8607,6 +9251,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>2</v>
+      </c>
+      <c r="K215" t="n">
         <v>2.985057474354541</v>
       </c>
     </row>
@@ -8645,6 +9292,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="n">
         <v>2.940968310050378</v>
       </c>
     </row>
@@ -8683,6 +9333,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>2</v>
+      </c>
+      <c r="K217" t="n">
         <v>2.940968310050378</v>
       </c>
     </row>
@@ -8721,6 +9374,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>2</v>
+      </c>
+      <c r="K218" t="n">
         <v>2.851443090899801</v>
       </c>
     </row>
@@ -8759,6 +9415,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>2</v>
+      </c>
+      <c r="K219" t="n">
         <v>2.845670807942637</v>
       </c>
     </row>
@@ -8797,6 +9456,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>2</v>
+      </c>
+      <c r="K220" t="n">
         <v>2.867113795850832</v>
       </c>
     </row>
@@ -8835,6 +9497,9 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>2</v>
+      </c>
+      <c r="K221" t="n">
         <v>2.938893995496655</v>
       </c>
     </row>
@@ -8873,6 +9538,9 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>2</v>
+      </c>
+      <c r="K222" t="n">
         <v>2.969078485441361</v>
       </c>
     </row>
@@ -8911,6 +9579,9 @@
         </is>
       </c>
       <c r="J223" t="n">
+        <v>2</v>
+      </c>
+      <c r="K223" t="n">
         <v>3.002244687587088</v>
       </c>
     </row>
@@ -8949,6 +9620,9 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>2</v>
+      </c>
+      <c r="K224" t="n">
         <v>3.062525075900084</v>
       </c>
     </row>
@@ -8987,6 +9661,9 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>2</v>
+      </c>
+      <c r="K225" t="n">
         <v>3.135601813749316</v>
       </c>
     </row>
@@ -9025,6 +9702,9 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>2</v>
+      </c>
+      <c r="K226" t="n">
         <v>3.177930662845831</v>
       </c>
     </row>
@@ -9063,6 +9743,9 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>2</v>
+      </c>
+      <c r="K227" t="n">
         <v>3.17889225180968</v>
       </c>
     </row>
@@ -9101,6 +9784,9 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>2</v>
+      </c>
+      <c r="K228" t="n">
         <v>3.151715080389572</v>
       </c>
     </row>
@@ -9139,6 +9825,9 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>2</v>
+      </c>
+      <c r="K229" t="n">
         <v>3.14031107926097</v>
       </c>
     </row>
@@ -9177,6 +9866,9 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>2</v>
+      </c>
+      <c r="K230" t="n">
         <v>3.14031107926097</v>
       </c>
     </row>
@@ -9215,6 +9907,9 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>2</v>
+      </c>
+      <c r="K231" t="n">
         <v>3.033140300212055</v>
       </c>
     </row>
@@ -9253,6 +9948,9 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>2</v>
+      </c>
+      <c r="K232" t="n">
         <v>2.968311100292726</v>
       </c>
     </row>
@@ -9291,6 +9989,9 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>2</v>
+      </c>
+      <c r="K233" t="n">
         <v>2.843726701817145</v>
       </c>
     </row>
@@ -9329,6 +10030,9 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K234" t="n">
         <v>2.791348310464368</v>
       </c>
     </row>
@@ -9367,6 +10071,9 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>2</v>
+      </c>
+      <c r="K235" t="n">
         <v>2.730300795632749</v>
       </c>
     </row>
@@ -9405,6 +10112,9 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>2</v>
+      </c>
+      <c r="K236" t="n">
         <v>2.61432654124052</v>
       </c>
     </row>
@@ -9443,6 +10153,9 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>2</v>
+      </c>
+      <c r="K237" t="n">
         <v>2.598344416882548</v>
       </c>
     </row>
@@ -9481,6 +10194,9 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>2</v>
+      </c>
+      <c r="K238" t="n">
         <v>2.595497597082085</v>
       </c>
     </row>
@@ -9519,6 +10235,9 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>2</v>
+      </c>
+      <c r="K239" t="n">
         <v>2.583829018613124</v>
       </c>
     </row>
@@ -9557,6 +10276,9 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>2</v>
+      </c>
+      <c r="K240" t="n">
         <v>2.59189536848193</v>
       </c>
     </row>
@@ -9595,6 +10317,9 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>2</v>
+      </c>
+      <c r="K241" t="n">
         <v>2.589407019765873</v>
       </c>
     </row>
@@ -9633,6 +10358,9 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>2</v>
+      </c>
+      <c r="K242" t="n">
         <v>2.589687907277124</v>
       </c>
     </row>
@@ -9671,6 +10399,9 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>2</v>
+      </c>
+      <c r="K243" t="n">
         <v>2.612943531877011</v>
       </c>
     </row>
@@ -9709,6 +10440,9 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>2</v>
+      </c>
+      <c r="K244" t="n">
         <v>2.652526773658721</v>
       </c>
     </row>
@@ -9747,6 +10481,9 @@
         </is>
       </c>
       <c r="J245" t="n">
+        <v>2</v>
+      </c>
+      <c r="K245" t="n">
         <v>2.653387069045559</v>
       </c>
     </row>
@@ -9785,6 +10522,9 @@
         </is>
       </c>
       <c r="J246" t="n">
+        <v>2</v>
+      </c>
+      <c r="K246" t="n">
         <v>2.603708822001785</v>
       </c>
     </row>
@@ -9823,6 +10563,9 @@
         </is>
       </c>
       <c r="J247" t="n">
+        <v>2</v>
+      </c>
+      <c r="K247" t="n">
         <v>2.58124486085573</v>
       </c>
     </row>
@@ -9861,6 +10604,9 @@
         </is>
       </c>
       <c r="J248" t="n">
+        <v>2</v>
+      </c>
+      <c r="K248" t="n">
         <v>2.58124486085573</v>
       </c>
     </row>
@@ -9899,6 +10645,9 @@
         </is>
       </c>
       <c r="J249" t="n">
+        <v>2</v>
+      </c>
+      <c r="K249" t="n">
         <v>2.394174116912976</v>
       </c>
     </row>
@@ -9937,6 +10686,9 @@
         </is>
       </c>
       <c r="J250" t="n">
+        <v>2</v>
+      </c>
+      <c r="K250" t="n">
         <v>2.323527404257891</v>
       </c>
     </row>
@@ -9975,6 +10727,9 @@
         </is>
       </c>
       <c r="J251" t="n">
+        <v>2</v>
+      </c>
+      <c r="K251" t="n">
         <v>2.323527404257891</v>
       </c>
     </row>
@@ -10013,6 +10768,9 @@
         </is>
       </c>
       <c r="J252" t="n">
+        <v>2</v>
+      </c>
+      <c r="K252" t="n">
         <v>2.323527404257891</v>
       </c>
     </row>
@@ -10051,6 +10809,9 @@
         </is>
       </c>
       <c r="J253" t="n">
+        <v>2</v>
+      </c>
+      <c r="K253" t="n">
         <v>2.178512263367727</v>
       </c>
     </row>
@@ -10089,6 +10850,9 @@
         </is>
       </c>
       <c r="J254" t="n">
+        <v>2</v>
+      </c>
+      <c r="K254" t="n">
         <v>2.107295626771773</v>
       </c>
     </row>
@@ -10127,6 +10891,9 @@
         </is>
       </c>
       <c r="J255" t="n">
+        <v>2</v>
+      </c>
+      <c r="K255" t="n">
         <v>1.987483692471464</v>
       </c>
     </row>
@@ -10165,6 +10932,9 @@
         </is>
       </c>
       <c r="J256" t="n">
+        <v>2</v>
+      </c>
+      <c r="K256" t="n">
         <v>1.932824086218656</v>
       </c>
     </row>
@@ -10203,6 +10973,9 @@
         </is>
       </c>
       <c r="J257" t="n">
+        <v>2</v>
+      </c>
+      <c r="K257" t="n">
         <v>1.923623634721696</v>
       </c>
     </row>
@@ -10241,6 +11014,9 @@
         </is>
       </c>
       <c r="J258" t="n">
+        <v>2</v>
+      </c>
+      <c r="K258" t="n">
         <v>1.957517531078011</v>
       </c>
     </row>
@@ -10279,6 +11055,9 @@
         </is>
       </c>
       <c r="J259" t="n">
+        <v>2</v>
+      </c>
+      <c r="K259" t="n">
         <v>1.95965017891482</v>
       </c>
     </row>
@@ -10317,6 +11096,9 @@
         </is>
       </c>
       <c r="J260" t="n">
+        <v>2</v>
+      </c>
+      <c r="K260" t="n">
         <v>1.983190562722504</v>
       </c>
     </row>
@@ -10355,6 +11137,9 @@
         </is>
       </c>
       <c r="J261" t="n">
+        <v>2</v>
+      </c>
+      <c r="K261" t="n">
         <v>1.985341968832413</v>
       </c>
     </row>
@@ -10393,6 +11178,9 @@
         </is>
       </c>
       <c r="J262" t="n">
+        <v>2</v>
+      </c>
+      <c r="K262" t="n">
         <v>2.076671745171828</v>
       </c>
     </row>
@@ -10431,6 +11219,9 @@
         </is>
       </c>
       <c r="J263" t="n">
+        <v>2</v>
+      </c>
+      <c r="K263" t="n">
         <v>2.076671745171828</v>
       </c>
     </row>
@@ -10469,6 +11260,9 @@
         </is>
       </c>
       <c r="J264" t="n">
+        <v>2</v>
+      </c>
+      <c r="K264" t="n">
         <v>2.076671745171828</v>
       </c>
     </row>
@@ -10507,6 +11301,9 @@
         </is>
       </c>
       <c r="J265" t="n">
+        <v>2</v>
+      </c>
+      <c r="K265" t="n">
         <v>2.076671745171828</v>
       </c>
     </row>
@@ -10545,6 +11342,9 @@
         </is>
       </c>
       <c r="J266" t="n">
+        <v>2</v>
+      </c>
+      <c r="K266" t="n">
         <v>2.103609451171724</v>
       </c>
     </row>
@@ -10583,6 +11383,9 @@
         </is>
       </c>
       <c r="J267" t="n">
+        <v>2</v>
+      </c>
+      <c r="K267" t="n">
         <v>2.207109187052492</v>
       </c>
     </row>
@@ -10621,6 +11424,9 @@
         </is>
       </c>
       <c r="J268" t="n">
+        <v>2</v>
+      </c>
+      <c r="K268" t="n">
         <v>2.365192607018854</v>
       </c>
     </row>
@@ -10659,6 +11465,9 @@
         </is>
       </c>
       <c r="J269" t="n">
+        <v>2</v>
+      </c>
+      <c r="K269" t="n">
         <v>2.435866690199535</v>
       </c>
     </row>
@@ -10697,6 +11506,9 @@
         </is>
       </c>
       <c r="J270" t="n">
+        <v>2</v>
+      </c>
+      <c r="K270" t="n">
         <v>2.425409032074808</v>
       </c>
     </row>
@@ -10735,6 +11547,9 @@
         </is>
       </c>
       <c r="J271" t="n">
+        <v>2</v>
+      </c>
+      <c r="K271" t="n">
         <v>2.396543736374894</v>
       </c>
     </row>
@@ -10773,6 +11588,9 @@
         </is>
       </c>
       <c r="J272" t="n">
+        <v>2</v>
+      </c>
+      <c r="K272" t="n">
         <v>2.350263467785271</v>
       </c>
     </row>
@@ -10811,6 +11629,9 @@
         </is>
       </c>
       <c r="J273" t="n">
+        <v>2</v>
+      </c>
+      <c r="K273" t="n">
         <v>2.129465962429183</v>
       </c>
     </row>
@@ -10849,6 +11670,9 @@
         </is>
       </c>
       <c r="J274" t="n">
+        <v>2</v>
+      </c>
+      <c r="K274" t="n">
         <v>2.129465962429183</v>
       </c>
     </row>
@@ -10887,6 +11711,9 @@
         </is>
       </c>
       <c r="J275" t="n">
+        <v>2</v>
+      </c>
+      <c r="K275" t="n">
         <v>2.004075915674061</v>
       </c>
     </row>
@@ -10925,6 +11752,9 @@
         </is>
       </c>
       <c r="J276" t="n">
+        <v>2</v>
+      </c>
+      <c r="K276" t="n">
         <v>1.625975143562268</v>
       </c>
     </row>
@@ -10963,6 +11793,9 @@
         </is>
       </c>
       <c r="J277" t="n">
+        <v>2</v>
+      </c>
+      <c r="K277" t="n">
         <v>1.570960415991205</v>
       </c>
     </row>
@@ -11001,6 +11834,9 @@
         </is>
       </c>
       <c r="J278" t="n">
+        <v>2</v>
+      </c>
+      <c r="K278" t="n">
         <v>1.524866571415489</v>
       </c>
     </row>
@@ -11039,6 +11875,9 @@
         </is>
       </c>
       <c r="J279" t="n">
+        <v>2</v>
+      </c>
+      <c r="K279" t="n">
         <v>1.488686264258009</v>
       </c>
     </row>
@@ -11077,6 +11916,9 @@
         </is>
       </c>
       <c r="J280" t="n">
+        <v>2</v>
+      </c>
+      <c r="K280" t="n">
         <v>1.497804894034293</v>
       </c>
     </row>
@@ -11115,6 +11957,9 @@
         </is>
       </c>
       <c r="J281" t="n">
+        <v>2</v>
+      </c>
+      <c r="K281" t="n">
         <v>1.579994554165848</v>
       </c>
     </row>
@@ -11153,6 +11998,9 @@
         </is>
       </c>
       <c r="J282" t="n">
+        <v>2</v>
+      </c>
+      <c r="K282" t="n">
         <v>1.590866122184887</v>
       </c>
     </row>
@@ -11191,6 +12039,9 @@
         </is>
       </c>
       <c r="J283" t="n">
+        <v>2</v>
+      </c>
+      <c r="K283" t="n">
         <v>1.58925863011308</v>
       </c>
     </row>
@@ -11229,6 +12080,9 @@
         </is>
       </c>
       <c r="J284" t="n">
+        <v>2</v>
+      </c>
+      <c r="K284" t="n">
         <v>1.529737080909861</v>
       </c>
     </row>
@@ -11267,6 +12121,9 @@
         </is>
       </c>
       <c r="J285" t="n">
+        <v>2</v>
+      </c>
+      <c r="K285" t="n">
         <v>1.577381506298685</v>
       </c>
     </row>
@@ -11305,6 +12162,9 @@
         </is>
       </c>
       <c r="J286" t="n">
+        <v>2</v>
+      </c>
+      <c r="K286" t="n">
         <v>1.583267166688227</v>
       </c>
     </row>
@@ -11343,6 +12203,9 @@
         </is>
       </c>
       <c r="J287" t="n">
+        <v>2</v>
+      </c>
+      <c r="K287" t="n">
         <v>1.583267166688227</v>
       </c>
     </row>
@@ -11381,6 +12244,9 @@
         </is>
       </c>
       <c r="J288" t="n">
+        <v>2</v>
+      </c>
+      <c r="K288" t="n">
         <v>1.851146747346766</v>
       </c>
     </row>
@@ -11419,6 +12285,9 @@
         </is>
       </c>
       <c r="J289" t="n">
+        <v>2</v>
+      </c>
+      <c r="K289" t="n">
         <v>1.851146747346766</v>
       </c>
     </row>
@@ -11457,6 +12326,9 @@
         </is>
       </c>
       <c r="J290" t="n">
+        <v>2</v>
+      </c>
+      <c r="K290" t="n">
         <v>2.041712023511712</v>
       </c>
     </row>
@@ -11495,6 +12367,9 @@
         </is>
       </c>
       <c r="J291" t="n">
+        <v>2</v>
+      </c>
+      <c r="K291" t="n">
         <v>2.07079530130531</v>
       </c>
     </row>
@@ -11533,6 +12408,9 @@
         </is>
       </c>
       <c r="J292" t="n">
+        <v>2</v>
+      </c>
+      <c r="K292" t="n">
         <v>2.083321248488577</v>
       </c>
     </row>
@@ -11571,6 +12449,9 @@
         </is>
       </c>
       <c r="J293" t="n">
+        <v>2</v>
+      </c>
+      <c r="K293" t="n">
         <v>2.055674428269336</v>
       </c>
     </row>
@@ -11609,6 +12490,9 @@
         </is>
       </c>
       <c r="J294" t="n">
+        <v>2</v>
+      </c>
+      <c r="K294" t="n">
         <v>2.055674428269336</v>
       </c>
     </row>
@@ -11647,6 +12531,9 @@
         </is>
       </c>
       <c r="J295" t="n">
+        <v>2</v>
+      </c>
+      <c r="K295" t="n">
         <v>2.055674428269336</v>
       </c>
     </row>
@@ -11685,6 +12572,9 @@
         </is>
       </c>
       <c r="J296" t="n">
+        <v>2</v>
+      </c>
+      <c r="K296" t="n">
         <v>2.047996450400295</v>
       </c>
     </row>
@@ -11723,6 +12613,9 @@
         </is>
       </c>
       <c r="J297" t="n">
+        <v>2</v>
+      </c>
+      <c r="K297" t="n">
         <v>2.116974228969603</v>
       </c>
     </row>
@@ -11761,6 +12654,9 @@
         </is>
       </c>
       <c r="J298" t="n">
+        <v>2</v>
+      </c>
+      <c r="K298" t="n">
         <v>2.147156255293087</v>
       </c>
     </row>
@@ -11799,6 +12695,9 @@
         </is>
       </c>
       <c r="J299" t="n">
+        <v>2</v>
+      </c>
+      <c r="K299" t="n">
         <v>2.323137655304029</v>
       </c>
     </row>
@@ -11837,6 +12736,9 @@
         </is>
       </c>
       <c r="J300" t="n">
+        <v>2</v>
+      </c>
+      <c r="K300" t="n">
         <v>2.329056026964639</v>
       </c>
     </row>
@@ -11875,6 +12777,9 @@
         </is>
       </c>
       <c r="J301" t="n">
+        <v>2</v>
+      </c>
+      <c r="K301" t="n">
         <v>2.685241237967792</v>
       </c>
     </row>
@@ -11913,6 +12818,9 @@
         </is>
       </c>
       <c r="J302" t="n">
+        <v>2</v>
+      </c>
+      <c r="K302" t="n">
         <v>2.695146953387487</v>
       </c>
     </row>
@@ -11951,6 +12859,9 @@
         </is>
       </c>
       <c r="J303" t="n">
+        <v>2</v>
+      </c>
+      <c r="K303" t="n">
         <v>3.011581810556982</v>
       </c>
     </row>
@@ -11989,6 +12900,9 @@
         </is>
       </c>
       <c r="J304" t="n">
+        <v>2</v>
+      </c>
+      <c r="K304" t="n">
         <v>3.011581810556982</v>
       </c>
     </row>
@@ -12027,6 +12941,9 @@
         </is>
       </c>
       <c r="J305" t="n">
+        <v>2</v>
+      </c>
+      <c r="K305" t="n">
         <v>2.994110865192332</v>
       </c>
     </row>
@@ -12065,6 +12982,9 @@
         </is>
       </c>
       <c r="J306" t="n">
+        <v>2</v>
+      </c>
+      <c r="K306" t="n">
         <v>2.87321663544604</v>
       </c>
     </row>
@@ -12103,6 +13023,9 @@
         </is>
       </c>
       <c r="J307" t="n">
+        <v>2</v>
+      </c>
+      <c r="K307" t="n">
         <v>2.827988175400171</v>
       </c>
     </row>
@@ -12141,6 +13064,9 @@
         </is>
       </c>
       <c r="J308" t="n">
+        <v>2</v>
+      </c>
+      <c r="K308" t="n">
         <v>2.825759508280099</v>
       </c>
     </row>
@@ -12179,6 +13105,9 @@
         </is>
       </c>
       <c r="J309" t="n">
+        <v>2</v>
+      </c>
+      <c r="K309" t="n">
         <v>2.79583204026963</v>
       </c>
     </row>
@@ -12217,6 +13146,9 @@
         </is>
       </c>
       <c r="J310" t="n">
+        <v>2</v>
+      </c>
+      <c r="K310" t="n">
         <v>2.802735030441299</v>
       </c>
     </row>
@@ -12255,6 +13187,9 @@
         </is>
       </c>
       <c r="J311" t="n">
+        <v>2</v>
+      </c>
+      <c r="K311" t="n">
         <v>3.107462356651375</v>
       </c>
     </row>
@@ -12293,6 +13228,9 @@
         </is>
       </c>
       <c r="J312" t="n">
+        <v>2</v>
+      </c>
+      <c r="K312" t="n">
         <v>3.107462356651375</v>
       </c>
     </row>
@@ -12331,6 +13269,9 @@
         </is>
       </c>
       <c r="J313" t="n">
+        <v>2</v>
+      </c>
+      <c r="K313" t="n">
         <v>3.118220316946035</v>
       </c>
     </row>
@@ -12369,6 +13310,9 @@
         </is>
       </c>
       <c r="J314" t="n">
+        <v>2</v>
+      </c>
+      <c r="K314" t="n">
         <v>3.334659903431462</v>
       </c>
     </row>
@@ -12407,6 +13351,9 @@
         </is>
       </c>
       <c r="J315" t="n">
+        <v>2</v>
+      </c>
+      <c r="K315" t="n">
         <v>3.551931890928346</v>
       </c>
     </row>
@@ -12445,6 +13392,9 @@
         </is>
       </c>
       <c r="J316" t="n">
+        <v>2</v>
+      </c>
+      <c r="K316" t="n">
         <v>3.561210762418601</v>
       </c>
     </row>
@@ -12483,6 +13433,9 @@
         </is>
       </c>
       <c r="J317" t="n">
+        <v>2</v>
+      </c>
+      <c r="K317" t="n">
         <v>3.561210762418601</v>
       </c>
     </row>
@@ -12521,6 +13474,9 @@
         </is>
       </c>
       <c r="J318" t="n">
+        <v>2</v>
+      </c>
+      <c r="K318" t="n">
         <v>3.443396611788092</v>
       </c>
     </row>
@@ -12559,6 +13515,9 @@
         </is>
       </c>
       <c r="J319" t="n">
+        <v>2</v>
+      </c>
+      <c r="K319" t="n">
         <v>3.443396611788092</v>
       </c>
     </row>
@@ -12597,6 +13556,9 @@
         </is>
       </c>
       <c r="J320" t="n">
+        <v>2</v>
+      </c>
+      <c r="K320" t="n">
         <v>3.443396611788092</v>
       </c>
     </row>
@@ -12635,6 +13597,9 @@
         </is>
       </c>
       <c r="J321" t="n">
+        <v>2</v>
+      </c>
+      <c r="K321" t="n">
         <v>3.274698364995402</v>
       </c>
     </row>
@@ -12673,6 +13638,9 @@
         </is>
       </c>
       <c r="J322" t="n">
+        <v>2</v>
+      </c>
+      <c r="K322" t="n">
         <v>3.264246930979694</v>
       </c>
     </row>
@@ -12711,6 +13679,9 @@
         </is>
       </c>
       <c r="J323" t="n">
+        <v>2</v>
+      </c>
+      <c r="K323" t="n">
         <v>2.835115915339944</v>
       </c>
     </row>
@@ -12749,6 +13720,9 @@
         </is>
       </c>
       <c r="J324" t="n">
+        <v>2</v>
+      </c>
+      <c r="K324" t="n">
         <v>2.682210342487319</v>
       </c>
     </row>
@@ -12787,6 +13761,9 @@
         </is>
       </c>
       <c r="J325" t="n">
+        <v>2</v>
+      </c>
+      <c r="K325" t="n">
         <v>2.510223013898961</v>
       </c>
     </row>
@@ -12825,6 +13802,9 @@
         </is>
       </c>
       <c r="J326" t="n">
+        <v>2</v>
+      </c>
+      <c r="K326" t="n">
         <v>2.510223013898961</v>
       </c>
     </row>
@@ -12863,6 +13843,9 @@
         </is>
       </c>
       <c r="J327" t="n">
+        <v>2</v>
+      </c>
+      <c r="K327" t="n">
         <v>2.179595404042975</v>
       </c>
     </row>
@@ -12901,6 +13884,9 @@
         </is>
       </c>
       <c r="J328" t="n">
+        <v>2</v>
+      </c>
+      <c r="K328" t="n">
         <v>2.179595404042975</v>
       </c>
     </row>
@@ -12939,6 +13925,9 @@
         </is>
       </c>
       <c r="J329" t="n">
+        <v>2</v>
+      </c>
+      <c r="K329" t="n">
         <v>2.02957950664275</v>
       </c>
     </row>
@@ -12977,6 +13966,9 @@
         </is>
       </c>
       <c r="J330" t="n">
+        <v>2</v>
+      </c>
+      <c r="K330" t="n">
         <v>1.806605692162661</v>
       </c>
     </row>
@@ -13015,6 +14007,9 @@
         </is>
       </c>
       <c r="J331" t="n">
+        <v>2</v>
+      </c>
+      <c r="K331" t="n">
         <v>1.710193047933979</v>
       </c>
     </row>
@@ -13053,6 +14048,9 @@
         </is>
       </c>
       <c r="J332" t="n">
+        <v>2</v>
+      </c>
+      <c r="K332" t="n">
         <v>1.647682429716306</v>
       </c>
     </row>
@@ -13091,6 +14089,9 @@
         </is>
       </c>
       <c r="J333" t="n">
+        <v>2</v>
+      </c>
+      <c r="K333" t="n">
         <v>1.583792832529507</v>
       </c>
     </row>
@@ -13129,6 +14130,9 @@
         </is>
       </c>
       <c r="J334" t="n">
+        <v>2</v>
+      </c>
+      <c r="K334" t="n">
         <v>1.578009875877034</v>
       </c>
     </row>
@@ -13167,6 +14171,9 @@
         </is>
       </c>
       <c r="J335" t="n">
+        <v>2</v>
+      </c>
+      <c r="K335" t="n">
         <v>1.537359691172308</v>
       </c>
     </row>
@@ -13205,6 +14212,9 @@
         </is>
       </c>
       <c r="J336" t="n">
+        <v>2</v>
+      </c>
+      <c r="K336" t="n">
         <v>1.67174808184305</v>
       </c>
     </row>
@@ -13243,6 +14253,9 @@
         </is>
       </c>
       <c r="J337" t="n">
+        <v>2</v>
+      </c>
+      <c r="K337" t="n">
         <v>1.67174808184305</v>
       </c>
     </row>
@@ -13281,6 +14294,9 @@
         </is>
       </c>
       <c r="J338" t="n">
+        <v>2</v>
+      </c>
+      <c r="K338" t="n">
         <v>1.67174808184305</v>
       </c>
     </row>
@@ -13319,6 +14335,9 @@
         </is>
       </c>
       <c r="J339" t="n">
+        <v>2</v>
+      </c>
+      <c r="K339" t="n">
         <v>1.839021882331904</v>
       </c>
     </row>
@@ -13357,6 +14376,9 @@
         </is>
       </c>
       <c r="J340" t="n">
+        <v>2</v>
+      </c>
+      <c r="K340" t="n">
         <v>1.839021882331904</v>
       </c>
     </row>
@@ -13395,6 +14417,9 @@
         </is>
       </c>
       <c r="J341" t="n">
+        <v>2</v>
+      </c>
+      <c r="K341" t="n">
         <v>1.970393288605207</v>
       </c>
     </row>
@@ -13433,6 +14458,9 @@
         </is>
       </c>
       <c r="J342" t="n">
+        <v>2</v>
+      </c>
+      <c r="K342" t="n">
         <v>1.970393288605207</v>
       </c>
     </row>
@@ -13471,6 +14499,9 @@
         </is>
       </c>
       <c r="J343" t="n">
+        <v>2</v>
+      </c>
+      <c r="K343" t="n">
         <v>2.051132064713035</v>
       </c>
     </row>
@@ -13509,6 +14540,9 @@
         </is>
       </c>
       <c r="J344" t="n">
+        <v>2</v>
+      </c>
+      <c r="K344" t="n">
         <v>2.082241251394405</v>
       </c>
     </row>
@@ -13547,6 +14581,9 @@
         </is>
       </c>
       <c r="J345" t="n">
+        <v>2</v>
+      </c>
+      <c r="K345" t="n">
         <v>2.069344040356683</v>
       </c>
     </row>
@@ -13585,6 +14622,9 @@
         </is>
       </c>
       <c r="J346" t="n">
+        <v>2</v>
+      </c>
+      <c r="K346" t="n">
         <v>2.069344040356683</v>
       </c>
     </row>
@@ -13623,6 +14663,9 @@
         </is>
       </c>
       <c r="J347" t="n">
+        <v>2</v>
+      </c>
+      <c r="K347" t="n">
         <v>1.88896439373089</v>
       </c>
     </row>
@@ -13661,6 +14704,9 @@
         </is>
       </c>
       <c r="J348" t="n">
+        <v>2</v>
+      </c>
+      <c r="K348" t="n">
         <v>1.737308038584745</v>
       </c>
     </row>
@@ -13699,6 +14745,9 @@
         </is>
       </c>
       <c r="J349" t="n">
+        <v>2</v>
+      </c>
+      <c r="K349" t="n">
         <v>1.55804413722387</v>
       </c>
     </row>
@@ -13737,6 +14786,9 @@
         </is>
       </c>
       <c r="J350" t="n">
+        <v>2</v>
+      </c>
+      <c r="K350" t="n">
         <v>1.546199783804783</v>
       </c>
     </row>
@@ -13775,6 +14827,9 @@
         </is>
       </c>
       <c r="J351" t="n">
+        <v>2</v>
+      </c>
+      <c r="K351" t="n">
         <v>1.114379929383587</v>
       </c>
     </row>
@@ -13813,6 +14868,9 @@
         </is>
       </c>
       <c r="J352" t="n">
+        <v>2</v>
+      </c>
+      <c r="K352" t="n">
         <v>1.114379929383587</v>
       </c>
     </row>
@@ -13851,6 +14909,9 @@
         </is>
       </c>
       <c r="J353" t="n">
+        <v>2</v>
+      </c>
+      <c r="K353" t="n">
         <v>0.8896705009585302</v>
       </c>
     </row>
@@ -13889,6 +14950,9 @@
         </is>
       </c>
       <c r="J354" t="n">
+        <v>2</v>
+      </c>
+      <c r="K354" t="n">
         <v>0.8896705009585302</v>
       </c>
     </row>
@@ -13927,6 +14991,9 @@
         </is>
       </c>
       <c r="J355" t="n">
+        <v>2</v>
+      </c>
+      <c r="K355" t="n">
         <v>0.8896705009585302</v>
       </c>
     </row>
@@ -13965,6 +15032,9 @@
         </is>
       </c>
       <c r="J356" t="n">
+        <v>2</v>
+      </c>
+      <c r="K356" t="n">
         <v>0.8829607995543933</v>
       </c>
     </row>
@@ -14003,6 +15073,9 @@
         </is>
       </c>
       <c r="J357" t="n">
+        <v>2</v>
+      </c>
+      <c r="K357" t="n">
         <v>0.8363701103621043</v>
       </c>
     </row>
@@ -14041,6 +15114,9 @@
         </is>
       </c>
       <c r="J358" t="n">
+        <v>2</v>
+      </c>
+      <c r="K358" t="n">
         <v>0.7542362999802886</v>
       </c>
     </row>
@@ -14079,6 +15155,9 @@
         </is>
       </c>
       <c r="J359" t="n">
+        <v>2</v>
+      </c>
+      <c r="K359" t="n">
         <v>0.7652953380169926</v>
       </c>
     </row>
@@ -14117,6 +15196,9 @@
         </is>
       </c>
       <c r="J360" t="n">
+        <v>2</v>
+      </c>
+      <c r="K360" t="n">
         <v>0.7879041622875256</v>
       </c>
     </row>
@@ -14155,6 +15237,9 @@
         </is>
       </c>
       <c r="J361" t="n">
+        <v>2</v>
+      </c>
+      <c r="K361" t="n">
         <v>0.7948381054118256</v>
       </c>
     </row>
@@ -14193,6 +15278,9 @@
         </is>
       </c>
       <c r="J362" t="n">
+        <v>2</v>
+      </c>
+      <c r="K362" t="n">
         <v>0.8008270198686489</v>
       </c>
     </row>
@@ -14231,6 +15319,9 @@
         </is>
       </c>
       <c r="J363" t="n">
+        <v>2</v>
+      </c>
+      <c r="K363" t="n">
         <v>0.8008270198686489</v>
       </c>
     </row>
@@ -14269,6 +15360,9 @@
         </is>
       </c>
       <c r="J364" t="n">
+        <v>2</v>
+      </c>
+      <c r="K364" t="n">
         <v>0.9071142730898115</v>
       </c>
     </row>
@@ -14307,6 +15401,9 @@
         </is>
       </c>
       <c r="J365" t="n">
+        <v>2</v>
+      </c>
+      <c r="K365" t="n">
         <v>0.9371962548521828</v>
       </c>
     </row>
@@ -14345,6 +15442,9 @@
         </is>
       </c>
       <c r="J366" t="n">
+        <v>2</v>
+      </c>
+      <c r="K366" t="n">
         <v>0.9806302346185736</v>
       </c>
     </row>
@@ -14383,6 +15483,9 @@
         </is>
       </c>
       <c r="J367" t="n">
+        <v>2</v>
+      </c>
+      <c r="K367" t="n">
         <v>1.18993105406857</v>
       </c>
     </row>
@@ -14421,6 +15524,9 @@
         </is>
       </c>
       <c r="J368" t="n">
+        <v>2</v>
+      </c>
+      <c r="K368" t="n">
         <v>1.535397801819967</v>
       </c>
     </row>
@@ -14459,6 +15565,9 @@
         </is>
       </c>
       <c r="J369" t="n">
+        <v>2</v>
+      </c>
+      <c r="K369" t="n">
         <v>1.535397801819967</v>
       </c>
     </row>
@@ -14497,6 +15606,9 @@
         </is>
       </c>
       <c r="J370" t="n">
+        <v>2</v>
+      </c>
+      <c r="K370" t="n">
         <v>1.553875391696069</v>
       </c>
     </row>
@@ -14535,6 +15647,9 @@
         </is>
       </c>
       <c r="J371" t="n">
+        <v>2</v>
+      </c>
+      <c r="K371" t="n">
         <v>2.411414902595833</v>
       </c>
     </row>
@@ -14573,6 +15688,9 @@
         </is>
       </c>
       <c r="J372" t="n">
+        <v>2</v>
+      </c>
+      <c r="K372" t="n">
         <v>2.533026156967144</v>
       </c>
     </row>
@@ -14611,6 +15729,9 @@
         </is>
       </c>
       <c r="J373" t="n">
+        <v>2</v>
+      </c>
+      <c r="K373" t="n">
         <v>2.618550022342504</v>
       </c>
     </row>
@@ -14649,6 +15770,9 @@
         </is>
       </c>
       <c r="J374" t="n">
+        <v>2</v>
+      </c>
+      <c r="K374" t="n">
         <v>2.618550022342504</v>
       </c>
     </row>
@@ -14687,6 +15811,9 @@
         </is>
       </c>
       <c r="J375" t="n">
+        <v>2</v>
+      </c>
+      <c r="K375" t="n">
         <v>2.673863725819055</v>
       </c>
     </row>
@@ -14725,6 +15852,9 @@
         </is>
       </c>
       <c r="J376" t="n">
+        <v>2</v>
+      </c>
+      <c r="K376" t="n">
         <v>2.673863725819055</v>
       </c>
     </row>
@@ -14763,6 +15893,9 @@
         </is>
       </c>
       <c r="J377" t="n">
+        <v>2</v>
+      </c>
+      <c r="K377" t="n">
         <v>2.786270111621638</v>
       </c>
     </row>
@@ -14801,6 +15934,9 @@
         </is>
       </c>
       <c r="J378" t="n">
+        <v>2</v>
+      </c>
+      <c r="K378" t="n">
         <v>2.793844610713815</v>
       </c>
     </row>
@@ -14839,6 +15975,9 @@
         </is>
       </c>
       <c r="J379" t="n">
+        <v>2</v>
+      </c>
+      <c r="K379" t="n">
         <v>2.777480180868591</v>
       </c>
     </row>
@@ -14877,6 +16016,9 @@
         </is>
       </c>
       <c r="J380" t="n">
+        <v>2</v>
+      </c>
+      <c r="K380" t="n">
         <v>2.758451324092219</v>
       </c>
     </row>
@@ -14915,6 +16057,9 @@
         </is>
       </c>
       <c r="J381" t="n">
+        <v>2</v>
+      </c>
+      <c r="K381" t="n">
         <v>2.718308847238013</v>
       </c>
     </row>
@@ -14953,6 +16098,9 @@
         </is>
       </c>
       <c r="J382" t="n">
+        <v>2</v>
+      </c>
+      <c r="K382" t="n">
         <v>2.713405551329738</v>
       </c>
     </row>
@@ -14991,6 +16139,9 @@
         </is>
       </c>
       <c r="J383" t="n">
+        <v>2</v>
+      </c>
+      <c r="K383" t="n">
         <v>2.58595042968048</v>
       </c>
     </row>
@@ -15029,6 +16180,9 @@
         </is>
       </c>
       <c r="J384" t="n">
+        <v>2</v>
+      </c>
+      <c r="K384" t="n">
         <v>2.484596963201059</v>
       </c>
     </row>
@@ -15067,6 +16221,9 @@
         </is>
       </c>
       <c r="J385" t="n">
+        <v>2</v>
+      </c>
+      <c r="K385" t="n">
         <v>2.47913383187016</v>
       </c>
     </row>
@@ -15105,6 +16262,9 @@
         </is>
       </c>
       <c r="J386" t="n">
+        <v>2</v>
+      </c>
+      <c r="K386" t="n">
         <v>2.43478182435853</v>
       </c>
     </row>
@@ -15143,6 +16303,9 @@
         </is>
       </c>
       <c r="J387" t="n">
+        <v>2</v>
+      </c>
+      <c r="K387" t="n">
         <v>2.43478182435853</v>
       </c>
     </row>
@@ -15181,6 +16344,9 @@
         </is>
       </c>
       <c r="J388" t="n">
+        <v>2</v>
+      </c>
+      <c r="K388" t="n">
         <v>2.368843364186503</v>
       </c>
     </row>
@@ -15219,6 +16385,9 @@
         </is>
       </c>
       <c r="J389" t="n">
+        <v>2</v>
+      </c>
+      <c r="K389" t="n">
         <v>2.25214800643259</v>
       </c>
     </row>
@@ -15257,6 +16426,9 @@
         </is>
       </c>
       <c r="J390" t="n">
+        <v>2</v>
+      </c>
+      <c r="K390" t="n">
         <v>2.232363721869575</v>
       </c>
     </row>
@@ -15295,6 +16467,9 @@
         </is>
       </c>
       <c r="J391" t="n">
+        <v>2</v>
+      </c>
+      <c r="K391" t="n">
         <v>2.231837605688082</v>
       </c>
     </row>
@@ -15333,6 +16508,9 @@
         </is>
       </c>
       <c r="J392" t="n">
+        <v>2</v>
+      </c>
+      <c r="K392" t="n">
         <v>2.210318404191058</v>
       </c>
     </row>
@@ -15371,6 +16549,9 @@
         </is>
       </c>
       <c r="J393" t="n">
+        <v>2</v>
+      </c>
+      <c r="K393" t="n">
         <v>2.216671271017764</v>
       </c>
     </row>
@@ -15409,6 +16590,9 @@
         </is>
       </c>
       <c r="J394" t="n">
+        <v>2</v>
+      </c>
+      <c r="K394" t="n">
         <v>2.22988717299946</v>
       </c>
     </row>
@@ -15447,6 +16631,9 @@
         </is>
       </c>
       <c r="J395" t="n">
+        <v>2</v>
+      </c>
+      <c r="K395" t="n">
         <v>2.268759589262716</v>
       </c>
     </row>
@@ -15485,6 +16672,9 @@
         </is>
       </c>
       <c r="J396" t="n">
+        <v>2</v>
+      </c>
+      <c r="K396" t="n">
         <v>2.288662996731921</v>
       </c>
     </row>
@@ -15523,6 +16713,9 @@
         </is>
       </c>
       <c r="J397" t="n">
+        <v>2</v>
+      </c>
+      <c r="K397" t="n">
         <v>2.352475311109939</v>
       </c>
     </row>
@@ -15561,6 +16754,9 @@
         </is>
       </c>
       <c r="J398" t="n">
+        <v>2</v>
+      </c>
+      <c r="K398" t="n">
         <v>2.366001064509192</v>
       </c>
     </row>
@@ -15599,6 +16795,9 @@
         </is>
       </c>
       <c r="J399" t="n">
+        <v>2</v>
+      </c>
+      <c r="K399" t="n">
         <v>2.398216889432669</v>
       </c>
     </row>
@@ -15637,6 +16836,9 @@
         </is>
       </c>
       <c r="J400" t="n">
+        <v>2</v>
+      </c>
+      <c r="K400" t="n">
         <v>2.409412092032066</v>
       </c>
     </row>
@@ -15675,6 +16877,9 @@
         </is>
       </c>
       <c r="J401" t="n">
+        <v>2</v>
+      </c>
+      <c r="K401" t="n">
         <v>2.41857346489639</v>
       </c>
     </row>
@@ -15713,6 +16918,9 @@
         </is>
       </c>
       <c r="J402" t="n">
+        <v>2</v>
+      </c>
+      <c r="K402" t="n">
         <v>2.419658441947551</v>
       </c>
     </row>
@@ -15751,6 +16959,9 @@
         </is>
       </c>
       <c r="J403" t="n">
+        <v>2</v>
+      </c>
+      <c r="K403" t="n">
         <v>2.45495802551393</v>
       </c>
     </row>
@@ -15789,6 +17000,9 @@
         </is>
       </c>
       <c r="J404" t="n">
+        <v>2</v>
+      </c>
+      <c r="K404" t="n">
         <v>2.558467583368409</v>
       </c>
     </row>
@@ -15827,6 +17041,9 @@
         </is>
       </c>
       <c r="J405" t="n">
+        <v>2</v>
+      </c>
+      <c r="K405" t="n">
         <v>2.562260704488763</v>
       </c>
     </row>
@@ -15865,6 +17082,9 @@
         </is>
       </c>
       <c r="J406" t="n">
+        <v>2</v>
+      </c>
+      <c r="K406" t="n">
         <v>2.589655981420203</v>
       </c>
     </row>
@@ -15903,6 +17123,9 @@
         </is>
       </c>
       <c r="J407" t="n">
+        <v>2</v>
+      </c>
+      <c r="K407" t="n">
         <v>2.661773406777044</v>
       </c>
     </row>
@@ -15941,6 +17164,9 @@
         </is>
       </c>
       <c r="J408" t="n">
+        <v>2</v>
+      </c>
+      <c r="K408" t="n">
         <v>2.674091609927487</v>
       </c>
     </row>
@@ -15979,6 +17205,9 @@
         </is>
       </c>
       <c r="J409" t="n">
+        <v>2</v>
+      </c>
+      <c r="K409" t="n">
         <v>2.7195196322338</v>
       </c>
     </row>
@@ -16017,6 +17246,9 @@
         </is>
       </c>
       <c r="J410" t="n">
+        <v>2</v>
+      </c>
+      <c r="K410" t="n">
         <v>2.732876607136169</v>
       </c>
     </row>
@@ -16055,6 +17287,9 @@
         </is>
       </c>
       <c r="J411" t="n">
+        <v>2</v>
+      </c>
+      <c r="K411" t="n">
         <v>2.712655642454856</v>
       </c>
     </row>
@@ -16093,6 +17328,9 @@
         </is>
       </c>
       <c r="J412" t="n">
+        <v>2</v>
+      </c>
+      <c r="K412" t="n">
         <v>2.641424891311162</v>
       </c>
     </row>
@@ -16131,6 +17369,9 @@
         </is>
       </c>
       <c r="J413" t="n">
+        <v>2</v>
+      </c>
+      <c r="K413" t="n">
         <v>2.638655258854448</v>
       </c>
     </row>
@@ -16169,6 +17410,9 @@
         </is>
       </c>
       <c r="J414" t="n">
+        <v>2</v>
+      </c>
+      <c r="K414" t="n">
         <v>2.519634181471032</v>
       </c>
     </row>
@@ -16207,6 +17451,9 @@
         </is>
       </c>
       <c r="J415" t="n">
+        <v>2</v>
+      </c>
+      <c r="K415" t="n">
         <v>2.478782202290914</v>
       </c>
     </row>
@@ -16245,6 +17492,9 @@
         </is>
       </c>
       <c r="J416" t="n">
+        <v>2</v>
+      </c>
+      <c r="K416" t="n">
         <v>2.425357244639936</v>
       </c>
     </row>
@@ -16283,6 +17533,9 @@
         </is>
       </c>
       <c r="J417" t="n">
+        <v>2</v>
+      </c>
+      <c r="K417" t="n">
         <v>2.380914291096624</v>
       </c>
     </row>
@@ -16321,6 +17574,9 @@
         </is>
       </c>
       <c r="J418" t="n">
+        <v>2</v>
+      </c>
+      <c r="K418" t="n">
         <v>2.380914291096624</v>
       </c>
     </row>
@@ -16359,6 +17615,9 @@
         </is>
       </c>
       <c r="J419" t="n">
+        <v>2</v>
+      </c>
+      <c r="K419" t="n">
         <v>2.18176137762674</v>
       </c>
     </row>
@@ -16397,6 +17656,9 @@
         </is>
       </c>
       <c r="J420" t="n">
+        <v>2</v>
+      </c>
+      <c r="K420" t="n">
         <v>2.110580560016065</v>
       </c>
     </row>
@@ -16435,6 +17697,9 @@
         </is>
       </c>
       <c r="J421" t="n">
+        <v>2</v>
+      </c>
+      <c r="K421" t="n">
         <v>2.048863670413637</v>
       </c>
     </row>
@@ -16473,6 +17738,9 @@
         </is>
       </c>
       <c r="J422" t="n">
+        <v>2</v>
+      </c>
+      <c r="K422" t="n">
         <v>1.900395550248122</v>
       </c>
     </row>
@@ -16511,6 +17779,9 @@
         </is>
       </c>
       <c r="J423" t="n">
+        <v>2</v>
+      </c>
+      <c r="K423" t="n">
         <v>1.89629322626414</v>
       </c>
     </row>
@@ -16549,6 +17820,9 @@
         </is>
       </c>
       <c r="J424" t="n">
+        <v>2</v>
+      </c>
+      <c r="K424" t="n">
         <v>1.852671258716622</v>
       </c>
     </row>
@@ -16587,6 +17861,9 @@
         </is>
       </c>
       <c r="J425" t="n">
+        <v>2</v>
+      </c>
+      <c r="K425" t="n">
         <v>1.85087802246062</v>
       </c>
     </row>
@@ -16625,6 +17902,9 @@
         </is>
       </c>
       <c r="J426" t="n">
+        <v>2</v>
+      </c>
+      <c r="K426" t="n">
         <v>1.850670598952984</v>
       </c>
     </row>
@@ -16663,6 +17943,9 @@
         </is>
       </c>
       <c r="J427" t="n">
+        <v>2</v>
+      </c>
+      <c r="K427" t="n">
         <v>1.842365730565255</v>
       </c>
     </row>
@@ -16701,6 +17984,9 @@
         </is>
       </c>
       <c r="J428" t="n">
+        <v>2</v>
+      </c>
+      <c r="K428" t="n">
         <v>1.827780845747513</v>
       </c>
     </row>
@@ -16739,6 +18025,9 @@
         </is>
       </c>
       <c r="J429" t="n">
+        <v>2</v>
+      </c>
+      <c r="K429" t="n">
         <v>1.827780845747513</v>
       </c>
     </row>
@@ -16777,6 +18066,9 @@
         </is>
       </c>
       <c r="J430" t="n">
+        <v>2</v>
+      </c>
+      <c r="K430" t="n">
         <v>1.827780845747513</v>
       </c>
     </row>
@@ -16815,6 +18107,9 @@
         </is>
       </c>
       <c r="J431" t="n">
+        <v>2</v>
+      </c>
+      <c r="K431" t="n">
         <v>1.826016765575718</v>
       </c>
     </row>
@@ -16853,6 +18148,9 @@
         </is>
       </c>
       <c r="J432" t="n">
+        <v>2</v>
+      </c>
+      <c r="K432" t="n">
         <v>1.826016765575718</v>
       </c>
     </row>
@@ -16891,6 +18189,9 @@
         </is>
       </c>
       <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="n">
         <v>1.804538279676842</v>
       </c>
     </row>
@@ -16929,6 +18230,9 @@
         </is>
       </c>
       <c r="J434" t="n">
+        <v>2</v>
+      </c>
+      <c r="K434" t="n">
         <v>1.804538279676842</v>
       </c>
     </row>
@@ -16967,6 +18271,9 @@
         </is>
       </c>
       <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="n">
         <v>1.779365439684264</v>
       </c>
     </row>
@@ -17005,6 +18312,9 @@
         </is>
       </c>
       <c r="J436" t="n">
+        <v>2</v>
+      </c>
+      <c r="K436" t="n">
         <v>1.738874318272187</v>
       </c>
     </row>
@@ -17043,6 +18353,9 @@
         </is>
       </c>
       <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="n">
         <v>1.598467165609943</v>
       </c>
     </row>
@@ -17081,6 +18394,9 @@
         </is>
       </c>
       <c r="J438" t="n">
+        <v>2</v>
+      </c>
+      <c r="K438" t="n">
         <v>1.598467165609943</v>
       </c>
     </row>
@@ -17119,6 +18435,9 @@
         </is>
       </c>
       <c r="J439" t="n">
+        <v>2</v>
+      </c>
+      <c r="K439" t="n">
         <v>1.540642156830476</v>
       </c>
     </row>
@@ -17157,6 +18476,9 @@
         </is>
       </c>
       <c r="J440" t="n">
+        <v>2</v>
+      </c>
+      <c r="K440" t="n">
         <v>1.513901223512885</v>
       </c>
     </row>
@@ -17195,6 +18517,9 @@
         </is>
       </c>
       <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
         <v>1.545172147416411</v>
       </c>
     </row>
@@ -17233,6 +18558,9 @@
         </is>
       </c>
       <c r="J442" t="n">
+        <v>2</v>
+      </c>
+      <c r="K442" t="n">
         <v>1.549486063043763</v>
       </c>
     </row>
@@ -17271,6 +18599,9 @@
         </is>
       </c>
       <c r="J443" t="n">
+        <v>2</v>
+      </c>
+      <c r="K443" t="n">
         <v>1.549486063043763</v>
       </c>
     </row>
@@ -17309,6 +18640,9 @@
         </is>
       </c>
       <c r="J444" t="n">
+        <v>2</v>
+      </c>
+      <c r="K444" t="n">
         <v>1.899336618499538</v>
       </c>
     </row>
@@ -17347,6 +18681,9 @@
         </is>
       </c>
       <c r="J445" t="n">
+        <v>2</v>
+      </c>
+      <c r="K445" t="n">
         <v>2.224233700446169</v>
       </c>
     </row>
@@ -17385,6 +18722,9 @@
         </is>
       </c>
       <c r="J446" t="n">
+        <v>2</v>
+      </c>
+      <c r="K446" t="n">
         <v>2.330404289907134</v>
       </c>
     </row>
@@ -17423,6 +18763,9 @@
         </is>
       </c>
       <c r="J447" t="n">
+        <v>2</v>
+      </c>
+      <c r="K447" t="n">
         <v>2.550071688613345</v>
       </c>
     </row>
@@ -17461,6 +18804,9 @@
         </is>
       </c>
       <c r="J448" t="n">
+        <v>2</v>
+      </c>
+      <c r="K448" t="n">
         <v>2.550071688613345</v>
       </c>
     </row>
@@ -17499,6 +18845,9 @@
         </is>
       </c>
       <c r="J449" t="n">
+        <v>2</v>
+      </c>
+      <c r="K449" t="n">
         <v>2.586586784958124</v>
       </c>
     </row>
@@ -17537,6 +18886,9 @@
         </is>
       </c>
       <c r="J450" t="n">
+        <v>2</v>
+      </c>
+      <c r="K450" t="n">
         <v>2.61591183063859</v>
       </c>
     </row>
@@ -17575,6 +18927,9 @@
         </is>
       </c>
       <c r="J451" t="n">
+        <v>2</v>
+      </c>
+      <c r="K451" t="n">
         <v>2.537699778527874</v>
       </c>
     </row>
@@ -17613,6 +18968,9 @@
         </is>
       </c>
       <c r="J452" t="n">
+        <v>2</v>
+      </c>
+      <c r="K452" t="n">
         <v>2.474056520534348</v>
       </c>
     </row>
@@ -17651,6 +19009,9 @@
         </is>
       </c>
       <c r="J453" t="n">
+        <v>2</v>
+      </c>
+      <c r="K453" t="n">
         <v>2.474056520534348</v>
       </c>
     </row>
@@ -17689,6 +19050,9 @@
         </is>
       </c>
       <c r="J454" t="n">
+        <v>2</v>
+      </c>
+      <c r="K454" t="n">
         <v>2.474056520534348</v>
       </c>
     </row>
@@ -17727,6 +19091,9 @@
         </is>
       </c>
       <c r="J455" t="n">
+        <v>2</v>
+      </c>
+      <c r="K455" t="n">
         <v>2.332531343452457</v>
       </c>
     </row>
@@ -17765,6 +19132,9 @@
         </is>
       </c>
       <c r="J456" t="n">
+        <v>2</v>
+      </c>
+      <c r="K456" t="n">
         <v>2.321600695604415</v>
       </c>
     </row>
@@ -17803,6 +19173,9 @@
         </is>
       </c>
       <c r="J457" t="n">
+        <v>2</v>
+      </c>
+      <c r="K457" t="n">
         <v>2.257276063767127</v>
       </c>
     </row>
@@ -17841,6 +19214,9 @@
         </is>
       </c>
       <c r="J458" t="n">
+        <v>2</v>
+      </c>
+      <c r="K458" t="n">
         <v>2.069287627425231</v>
       </c>
     </row>
@@ -17879,6 +19255,9 @@
         </is>
       </c>
       <c r="J459" t="n">
+        <v>2</v>
+      </c>
+      <c r="K459" t="n">
         <v>2.06525299783925</v>
       </c>
     </row>
@@ -17917,6 +19296,9 @@
         </is>
       </c>
       <c r="J460" t="n">
+        <v>2</v>
+      </c>
+      <c r="K460" t="n">
         <v>2.06525299783925</v>
       </c>
     </row>
@@ -17955,6 +19337,9 @@
         </is>
       </c>
       <c r="J461" t="n">
+        <v>2</v>
+      </c>
+      <c r="K461" t="n">
         <v>2.05459525953189</v>
       </c>
     </row>
@@ -17993,6 +19378,9 @@
         </is>
       </c>
       <c r="J462" t="n">
+        <v>2</v>
+      </c>
+      <c r="K462" t="n">
         <v>2.056991536725648</v>
       </c>
     </row>
@@ -18031,6 +19419,9 @@
         </is>
       </c>
       <c r="J463" t="n">
+        <v>2</v>
+      </c>
+      <c r="K463" t="n">
         <v>2.064130175465934</v>
       </c>
     </row>
@@ -18069,6 +19460,9 @@
         </is>
       </c>
       <c r="J464" t="n">
+        <v>2</v>
+      </c>
+      <c r="K464" t="n">
         <v>2.214671060823963</v>
       </c>
     </row>
@@ -18107,6 +19501,9 @@
         </is>
       </c>
       <c r="J465" t="n">
+        <v>2</v>
+      </c>
+      <c r="K465" t="n">
         <v>2.22512500023652</v>
       </c>
     </row>
@@ -18145,6 +19542,9 @@
         </is>
       </c>
       <c r="J466" t="n">
+        <v>2</v>
+      </c>
+      <c r="K466" t="n">
         <v>2.289300410662081</v>
       </c>
     </row>
@@ -18183,6 +19583,9 @@
         </is>
       </c>
       <c r="J467" t="n">
+        <v>2</v>
+      </c>
+      <c r="K467" t="n">
         <v>2.382961362207613</v>
       </c>
     </row>
@@ -18221,6 +19624,9 @@
         </is>
       </c>
       <c r="J468" t="n">
+        <v>2</v>
+      </c>
+      <c r="K468" t="n">
         <v>2.462609261231583</v>
       </c>
     </row>
@@ -18259,6 +19665,9 @@
         </is>
       </c>
       <c r="J469" t="n">
+        <v>2</v>
+      </c>
+      <c r="K469" t="n">
         <v>2.659350941236433</v>
       </c>
     </row>
@@ -18297,6 +19706,9 @@
         </is>
       </c>
       <c r="J470" t="n">
+        <v>2</v>
+      </c>
+      <c r="K470" t="n">
         <v>2.912964018205849</v>
       </c>
     </row>
@@ -18335,6 +19747,9 @@
         </is>
       </c>
       <c r="J471" t="n">
+        <v>2</v>
+      </c>
+      <c r="K471" t="n">
         <v>2.922523816392022</v>
       </c>
     </row>
@@ -18373,6 +19788,9 @@
         </is>
       </c>
       <c r="J472" t="n">
+        <v>2</v>
+      </c>
+      <c r="K472" t="n">
         <v>2.977320288555501</v>
       </c>
     </row>
@@ -18411,6 +19829,9 @@
         </is>
       </c>
       <c r="J473" t="n">
+        <v>2</v>
+      </c>
+      <c r="K473" t="n">
         <v>2.987593593258851</v>
       </c>
     </row>
@@ -18449,6 +19870,9 @@
         </is>
       </c>
       <c r="J474" t="n">
+        <v>2</v>
+      </c>
+      <c r="K474" t="n">
         <v>2.822026428754017</v>
       </c>
     </row>
@@ -18487,6 +19911,9 @@
         </is>
       </c>
       <c r="J475" t="n">
+        <v>2</v>
+      </c>
+      <c r="K475" t="n">
         <v>2.806075475373767</v>
       </c>
     </row>
@@ -18525,6 +19952,9 @@
         </is>
       </c>
       <c r="J476" t="n">
+        <v>2</v>
+      </c>
+      <c r="K476" t="n">
         <v>2.806075475373767</v>
       </c>
     </row>
@@ -18563,6 +19993,9 @@
         </is>
       </c>
       <c r="J477" t="n">
+        <v>2</v>
+      </c>
+      <c r="K477" t="n">
         <v>2.712076875309097</v>
       </c>
     </row>
@@ -18601,6 +20034,9 @@
         </is>
       </c>
       <c r="J478" t="n">
+        <v>2</v>
+      </c>
+      <c r="K478" t="n">
         <v>2.376263836303047</v>
       </c>
     </row>
@@ -18639,6 +20075,9 @@
         </is>
       </c>
       <c r="J479" t="n">
+        <v>2</v>
+      </c>
+      <c r="K479" t="n">
         <v>2.376263836303047</v>
       </c>
     </row>
@@ -18677,6 +20116,9 @@
         </is>
       </c>
       <c r="J480" t="n">
+        <v>3</v>
+      </c>
+      <c r="K480" t="n">
         <v>2.30280530514413</v>
       </c>
     </row>
@@ -18715,6 +20157,9 @@
         </is>
       </c>
       <c r="J481" t="n">
+        <v>3</v>
+      </c>
+      <c r="K481" t="n">
         <v>2.250227729506013</v>
       </c>
     </row>
@@ -18753,6 +20198,9 @@
         </is>
       </c>
       <c r="J482" t="n">
+        <v>3</v>
+      </c>
+      <c r="K482" t="n">
         <v>2.215775943332024</v>
       </c>
     </row>
@@ -18791,6 +20239,9 @@
         </is>
       </c>
       <c r="J483" t="n">
+        <v>3</v>
+      </c>
+      <c r="K483" t="n">
         <v>2.215775943332024</v>
       </c>
     </row>
@@ -18829,6 +20280,9 @@
         </is>
       </c>
       <c r="J484" t="n">
+        <v>3</v>
+      </c>
+      <c r="K484" t="n">
         <v>2.232330959169365</v>
       </c>
     </row>
@@ -18867,6 +20321,9 @@
         </is>
       </c>
       <c r="J485" t="n">
+        <v>3</v>
+      </c>
+      <c r="K485" t="n">
         <v>2.256643808943577</v>
       </c>
     </row>
@@ -18905,6 +20362,9 @@
         </is>
       </c>
       <c r="J486" t="n">
+        <v>3</v>
+      </c>
+      <c r="K486" t="n">
         <v>2.261991090551478</v>
       </c>
     </row>
@@ -18943,6 +20403,9 @@
         </is>
       </c>
       <c r="J487" t="n">
+        <v>3</v>
+      </c>
+      <c r="K487" t="n">
         <v>2.301870039332318</v>
       </c>
     </row>
@@ -18981,6 +20444,9 @@
         </is>
       </c>
       <c r="J488" t="n">
+        <v>3</v>
+      </c>
+      <c r="K488" t="n">
         <v>2.367155198339137</v>
       </c>
     </row>
@@ -19019,6 +20485,9 @@
         </is>
       </c>
       <c r="J489" t="n">
+        <v>3</v>
+      </c>
+      <c r="K489" t="n">
         <v>2.377180243287329</v>
       </c>
     </row>
@@ -19057,6 +20526,9 @@
         </is>
       </c>
       <c r="J490" t="n">
+        <v>3</v>
+      </c>
+      <c r="K490" t="n">
         <v>2.510186054048462</v>
       </c>
     </row>
@@ -19095,6 +20567,9 @@
         </is>
       </c>
       <c r="J491" t="n">
+        <v>3</v>
+      </c>
+      <c r="K491" t="n">
         <v>2.557413986968126</v>
       </c>
     </row>
@@ -19133,6 +20608,9 @@
         </is>
       </c>
       <c r="J492" t="n">
+        <v>3</v>
+      </c>
+      <c r="K492" t="n">
         <v>2.648846174480814</v>
       </c>
     </row>
@@ -19171,6 +20649,9 @@
         </is>
       </c>
       <c r="J493" t="n">
+        <v>3</v>
+      </c>
+      <c r="K493" t="n">
         <v>2.662728291843294</v>
       </c>
     </row>
@@ -19209,6 +20690,9 @@
         </is>
       </c>
       <c r="J494" t="n">
+        <v>3</v>
+      </c>
+      <c r="K494" t="n">
         <v>2.649219924340479</v>
       </c>
     </row>
@@ -19247,6 +20731,9 @@
         </is>
       </c>
       <c r="J495" t="n">
+        <v>3</v>
+      </c>
+      <c r="K495" t="n">
         <v>2.59540559001166</v>
       </c>
     </row>
@@ -19285,6 +20772,9 @@
         </is>
       </c>
       <c r="J496" t="n">
+        <v>3</v>
+      </c>
+      <c r="K496" t="n">
         <v>2.560817984339082</v>
       </c>
     </row>
@@ -19323,6 +20813,9 @@
         </is>
       </c>
       <c r="J497" t="n">
+        <v>3</v>
+      </c>
+      <c r="K497" t="n">
         <v>2.501634689238714</v>
       </c>
     </row>
@@ -19361,6 +20854,9 @@
         </is>
       </c>
       <c r="J498" t="n">
+        <v>3</v>
+      </c>
+      <c r="K498" t="n">
         <v>2.432418258565894</v>
       </c>
     </row>
@@ -19399,6 +20895,9 @@
         </is>
       </c>
       <c r="J499" t="n">
+        <v>3</v>
+      </c>
+      <c r="K499" t="n">
         <v>2.40236383932226</v>
       </c>
     </row>
@@ -19437,6 +20936,9 @@
         </is>
       </c>
       <c r="J500" t="n">
+        <v>3</v>
+      </c>
+      <c r="K500" t="n">
         <v>2.39909747195935</v>
       </c>
     </row>
@@ -19475,6 +20977,9 @@
         </is>
       </c>
       <c r="J501" t="n">
+        <v>3</v>
+      </c>
+      <c r="K501" t="n">
         <v>2.474095389053848</v>
       </c>
     </row>
@@ -19513,6 +21018,9 @@
         </is>
       </c>
       <c r="J502" t="n">
+        <v>3</v>
+      </c>
+      <c r="K502" t="n">
         <v>2.474095389053848</v>
       </c>
     </row>
@@ -19551,6 +21059,9 @@
         </is>
       </c>
       <c r="J503" t="n">
+        <v>3</v>
+      </c>
+      <c r="K503" t="n">
         <v>2.595955455007303</v>
       </c>
     </row>
@@ -19589,6 +21100,9 @@
         </is>
       </c>
       <c r="J504" t="n">
+        <v>3</v>
+      </c>
+      <c r="K504" t="n">
         <v>2.595955455007303</v>
       </c>
     </row>
@@ -19627,6 +21141,9 @@
         </is>
       </c>
       <c r="J505" t="n">
+        <v>3</v>
+      </c>
+      <c r="K505" t="n">
         <v>2.72207002765784</v>
       </c>
     </row>
@@ -19665,6 +21182,9 @@
         </is>
       </c>
       <c r="J506" t="n">
+        <v>3</v>
+      </c>
+      <c r="K506" t="n">
         <v>2.72207002765784</v>
       </c>
     </row>
@@ -19703,6 +21223,9 @@
         </is>
       </c>
       <c r="J507" t="n">
+        <v>3</v>
+      </c>
+      <c r="K507" t="n">
         <v>2.788780703337199</v>
       </c>
     </row>
@@ -19741,6 +21264,9 @@
         </is>
       </c>
       <c r="J508" t="n">
+        <v>3</v>
+      </c>
+      <c r="K508" t="n">
         <v>2.788780703337199</v>
       </c>
     </row>
@@ -19779,6 +21305,9 @@
         </is>
       </c>
       <c r="J509" t="n">
+        <v>3</v>
+      </c>
+      <c r="K509" t="n">
         <v>2.97847013008986</v>
       </c>
     </row>
@@ -19817,6 +21346,9 @@
         </is>
       </c>
       <c r="J510" t="n">
+        <v>3</v>
+      </c>
+      <c r="K510" t="n">
         <v>2.97847013008986</v>
       </c>
     </row>
@@ -19855,6 +21387,9 @@
         </is>
       </c>
       <c r="J511" t="n">
+        <v>3</v>
+      </c>
+      <c r="K511" t="n">
         <v>3.01157986414617</v>
       </c>
     </row>
@@ -19893,6 +21428,9 @@
         </is>
       </c>
       <c r="J512" t="n">
+        <v>3</v>
+      </c>
+      <c r="K512" t="n">
         <v>3.01157986414617</v>
       </c>
     </row>
@@ -19931,6 +21469,9 @@
         </is>
       </c>
       <c r="J513" t="n">
+        <v>3</v>
+      </c>
+      <c r="K513" t="n">
         <v>3.039726491945422</v>
       </c>
     </row>
@@ -19969,6 +21510,9 @@
         </is>
       </c>
       <c r="J514" t="n">
+        <v>3</v>
+      </c>
+      <c r="K514" t="n">
         <v>3.019010457551972</v>
       </c>
     </row>
@@ -20007,6 +21551,9 @@
         </is>
       </c>
       <c r="J515" t="n">
+        <v>3</v>
+      </c>
+      <c r="K515" t="n">
         <v>2.862963616969401</v>
       </c>
     </row>
@@ -20045,6 +21592,9 @@
         </is>
       </c>
       <c r="J516" t="n">
+        <v>3</v>
+      </c>
+      <c r="K516" t="n">
         <v>2.862963616969401</v>
       </c>
     </row>
@@ -20083,6 +21633,9 @@
         </is>
       </c>
       <c r="J517" t="n">
+        <v>3</v>
+      </c>
+      <c r="K517" t="n">
         <v>2.859796011305207</v>
       </c>
     </row>
@@ -20121,6 +21674,9 @@
         </is>
       </c>
       <c r="J518" t="n">
+        <v>3</v>
+      </c>
+      <c r="K518" t="n">
         <v>2.841411184601648</v>
       </c>
     </row>
@@ -20159,6 +21715,9 @@
         </is>
       </c>
       <c r="J519" t="n">
+        <v>3</v>
+      </c>
+      <c r="K519" t="n">
         <v>2.841411184601648</v>
       </c>
     </row>
@@ -20197,6 +21756,9 @@
         </is>
       </c>
       <c r="J520" t="n">
+        <v>3</v>
+      </c>
+      <c r="K520" t="n">
         <v>2.863266209391949</v>
       </c>
     </row>
@@ -20235,6 +21797,9 @@
         </is>
       </c>
       <c r="J521" t="n">
+        <v>3</v>
+      </c>
+      <c r="K521" t="n">
         <v>2.888024879348644</v>
       </c>
     </row>
@@ -20273,6 +21838,9 @@
         </is>
       </c>
       <c r="J522" t="n">
+        <v>3</v>
+      </c>
+      <c r="K522" t="n">
         <v>2.888024879348644</v>
       </c>
     </row>
@@ -20311,6 +21879,9 @@
         </is>
       </c>
       <c r="J523" t="n">
+        <v>3</v>
+      </c>
+      <c r="K523" t="n">
         <v>2.825179314631639</v>
       </c>
     </row>
@@ -20349,6 +21920,9 @@
         </is>
       </c>
       <c r="J524" t="n">
+        <v>3</v>
+      </c>
+      <c r="K524" t="n">
         <v>2.627764807843734</v>
       </c>
     </row>
@@ -20387,6 +21961,9 @@
         </is>
       </c>
       <c r="J525" t="n">
+        <v>3</v>
+      </c>
+      <c r="K525" t="n">
         <v>2.627764807843734</v>
       </c>
     </row>
@@ -20425,6 +22002,9 @@
         </is>
       </c>
       <c r="J526" t="n">
+        <v>3</v>
+      </c>
+      <c r="K526" t="n">
         <v>2.54725174433134</v>
       </c>
     </row>
@@ -20463,6 +22043,9 @@
         </is>
       </c>
       <c r="J527" t="n">
+        <v>3</v>
+      </c>
+      <c r="K527" t="n">
         <v>2.550229610186616</v>
       </c>
     </row>
@@ -20501,6 +22084,9 @@
         </is>
       </c>
       <c r="J528" t="n">
+        <v>3</v>
+      </c>
+      <c r="K528" t="n">
         <v>2.644362600916906</v>
       </c>
     </row>
@@ -20539,6 +22125,9 @@
         </is>
       </c>
       <c r="J529" t="n">
+        <v>3</v>
+      </c>
+      <c r="K529" t="n">
         <v>3.224048162476565</v>
       </c>
     </row>
@@ -20577,6 +22166,9 @@
         </is>
       </c>
       <c r="J530" t="n">
+        <v>3</v>
+      </c>
+      <c r="K530" t="n">
         <v>3.224048162476565</v>
       </c>
     </row>
@@ -20615,6 +22207,9 @@
         </is>
       </c>
       <c r="J531" t="n">
+        <v>3</v>
+      </c>
+      <c r="K531" t="n">
         <v>3.598305332340881</v>
       </c>
     </row>
@@ -20653,6 +22248,9 @@
         </is>
       </c>
       <c r="J532" t="n">
+        <v>3</v>
+      </c>
+      <c r="K532" t="n">
         <v>3.713474251746511</v>
       </c>
     </row>
@@ -20691,6 +22289,9 @@
         </is>
       </c>
       <c r="J533" t="n">
+        <v>3</v>
+      </c>
+      <c r="K533" t="n">
         <v>3.852246060264426</v>
       </c>
     </row>
@@ -20729,6 +22330,9 @@
         </is>
       </c>
       <c r="J534" t="n">
+        <v>3</v>
+      </c>
+      <c r="K534" t="n">
         <v>3.852246060264426</v>
       </c>
     </row>
@@ -20767,6 +22371,9 @@
         </is>
       </c>
       <c r="J535" t="n">
+        <v>3</v>
+      </c>
+      <c r="K535" t="n">
         <v>3.893659775089872</v>
       </c>
     </row>
@@ -20805,6 +22412,9 @@
         </is>
       </c>
       <c r="J536" t="n">
+        <v>3</v>
+      </c>
+      <c r="K536" t="n">
         <v>3.893659775089872</v>
       </c>
     </row>
@@ -20843,6 +22453,9 @@
         </is>
       </c>
       <c r="J537" t="n">
+        <v>3</v>
+      </c>
+      <c r="K537" t="n">
         <v>3.893659775089872</v>
       </c>
     </row>
@@ -20881,6 +22494,9 @@
         </is>
       </c>
       <c r="J538" t="n">
+        <v>3</v>
+      </c>
+      <c r="K538" t="n">
         <v>3.816978752115189</v>
       </c>
     </row>
@@ -20919,6 +22535,9 @@
         </is>
       </c>
       <c r="J539" t="n">
+        <v>3</v>
+      </c>
+      <c r="K539" t="n">
         <v>3.816978752115189</v>
       </c>
     </row>
@@ -20957,6 +22576,9 @@
         </is>
       </c>
       <c r="J540" t="n">
+        <v>3</v>
+      </c>
+      <c r="K540" t="n">
         <v>3.777794437671376</v>
       </c>
     </row>
@@ -20995,6 +22617,9 @@
         </is>
       </c>
       <c r="J541" t="n">
+        <v>3</v>
+      </c>
+      <c r="K541" t="n">
         <v>3.771957833551445</v>
       </c>
     </row>
@@ -21033,6 +22658,9 @@
         </is>
       </c>
       <c r="J542" t="n">
+        <v>3</v>
+      </c>
+      <c r="K542" t="n">
         <v>3.740814557077054</v>
       </c>
     </row>
@@ -21071,6 +22699,9 @@
         </is>
       </c>
       <c r="J543" t="n">
+        <v>3</v>
+      </c>
+      <c r="K543" t="n">
         <v>3.722757542332938</v>
       </c>
     </row>
@@ -21109,6 +22740,9 @@
         </is>
       </c>
       <c r="J544" t="n">
+        <v>3</v>
+      </c>
+      <c r="K544" t="n">
         <v>3.722757542332938</v>
       </c>
     </row>
@@ -21147,6 +22781,9 @@
         </is>
       </c>
       <c r="J545" t="n">
+        <v>3</v>
+      </c>
+      <c r="K545" t="n">
         <v>3.722614145366322</v>
       </c>
     </row>
@@ -21185,6 +22822,9 @@
         </is>
       </c>
       <c r="J546" t="n">
+        <v>3</v>
+      </c>
+      <c r="K546" t="n">
         <v>3.722614145366322</v>
       </c>
     </row>
@@ -21223,6 +22863,9 @@
         </is>
       </c>
       <c r="J547" t="n">
+        <v>3</v>
+      </c>
+      <c r="K547" t="n">
         <v>3.72091113297808</v>
       </c>
     </row>
@@ -21261,6 +22904,9 @@
         </is>
       </c>
       <c r="J548" t="n">
+        <v>3</v>
+      </c>
+      <c r="K548" t="n">
         <v>3.729350083519563</v>
       </c>
     </row>
@@ -21299,6 +22945,9 @@
         </is>
       </c>
       <c r="J549" t="n">
+        <v>3</v>
+      </c>
+      <c r="K549" t="n">
         <v>3.750723599828893</v>
       </c>
     </row>
@@ -21337,6 +22986,9 @@
         </is>
       </c>
       <c r="J550" t="n">
+        <v>3</v>
+      </c>
+      <c r="K550" t="n">
         <v>3.779628580035076</v>
       </c>
     </row>
@@ -21375,6 +23027,9 @@
         </is>
       </c>
       <c r="J551" t="n">
+        <v>3</v>
+      </c>
+      <c r="K551" t="n">
         <v>4.051357667744662</v>
       </c>
     </row>
@@ -21413,6 +23068,9 @@
         </is>
       </c>
       <c r="J552" t="n">
+        <v>3</v>
+      </c>
+      <c r="K552" t="n">
         <v>4.063584428200659</v>
       </c>
     </row>
@@ -21451,6 +23109,9 @@
         </is>
       </c>
       <c r="J553" t="n">
+        <v>3</v>
+      </c>
+      <c r="K553" t="n">
         <v>4.159805490030706</v>
       </c>
     </row>
@@ -21489,6 +23150,9 @@
         </is>
       </c>
       <c r="J554" t="n">
+        <v>3</v>
+      </c>
+      <c r="K554" t="n">
         <v>4.16159612051079</v>
       </c>
     </row>
@@ -21527,6 +23191,9 @@
         </is>
       </c>
       <c r="J555" t="n">
+        <v>3</v>
+      </c>
+      <c r="K555" t="n">
         <v>4.159103137144754</v>
       </c>
     </row>
@@ -21565,6 +23232,9 @@
         </is>
       </c>
       <c r="J556" t="n">
+        <v>3</v>
+      </c>
+      <c r="K556" t="n">
         <v>4.143805075357495</v>
       </c>
     </row>
@@ -21603,6 +23273,9 @@
         </is>
       </c>
       <c r="J557" t="n">
+        <v>3</v>
+      </c>
+      <c r="K557" t="n">
         <v>4.12884095766673</v>
       </c>
     </row>
@@ -21641,6 +23314,9 @@
         </is>
       </c>
       <c r="J558" t="n">
+        <v>3</v>
+      </c>
+      <c r="K558" t="n">
         <v>4.12455310443984</v>
       </c>
     </row>
@@ -21679,6 +23355,9 @@
         </is>
       </c>
       <c r="J559" t="n">
+        <v>3</v>
+      </c>
+      <c r="K559" t="n">
         <v>4.087388290903759</v>
       </c>
     </row>
@@ -21717,6 +23396,9 @@
         </is>
       </c>
       <c r="J560" t="n">
+        <v>3</v>
+      </c>
+      <c r="K560" t="n">
         <v>4.044968575389446</v>
       </c>
     </row>
@@ -21755,6 +23437,9 @@
         </is>
       </c>
       <c r="J561" t="n">
+        <v>3</v>
+      </c>
+      <c r="K561" t="n">
         <v>3.977637725962148</v>
       </c>
     </row>
@@ -21793,6 +23478,9 @@
         </is>
       </c>
       <c r="J562" t="n">
+        <v>3</v>
+      </c>
+      <c r="K562" t="n">
         <v>3.912419575923587</v>
       </c>
     </row>
@@ -21831,6 +23519,9 @@
         </is>
       </c>
       <c r="J563" t="n">
+        <v>3</v>
+      </c>
+      <c r="K563" t="n">
         <v>3.912419575923587</v>
       </c>
     </row>
@@ -21869,6 +23560,9 @@
         </is>
       </c>
       <c r="J564" t="n">
+        <v>3</v>
+      </c>
+      <c r="K564" t="n">
         <v>3.809613153755713</v>
       </c>
     </row>
@@ -21907,6 +23601,9 @@
         </is>
       </c>
       <c r="J565" t="n">
+        <v>3</v>
+      </c>
+      <c r="K565" t="n">
         <v>3.773534856961286</v>
       </c>
     </row>
@@ -21945,6 +23642,9 @@
         </is>
       </c>
       <c r="J566" t="n">
+        <v>3</v>
+      </c>
+      <c r="K566" t="n">
         <v>3.738548552469321</v>
       </c>
     </row>
@@ -21983,6 +23683,9 @@
         </is>
       </c>
       <c r="J567" t="n">
+        <v>3</v>
+      </c>
+      <c r="K567" t="n">
         <v>3.726771371055897</v>
       </c>
     </row>
@@ -22021,6 +23724,9 @@
         </is>
       </c>
       <c r="J568" t="n">
+        <v>3</v>
+      </c>
+      <c r="K568" t="n">
         <v>3.641986224342939</v>
       </c>
     </row>
@@ -22059,6 +23765,9 @@
         </is>
       </c>
       <c r="J569" t="n">
+        <v>3</v>
+      </c>
+      <c r="K569" t="n">
         <v>3.637904397151695</v>
       </c>
     </row>
@@ -22097,6 +23806,9 @@
         </is>
       </c>
       <c r="J570" t="n">
+        <v>3</v>
+      </c>
+      <c r="K570" t="n">
         <v>3.639793545672112</v>
       </c>
     </row>
@@ -22135,6 +23847,9 @@
         </is>
       </c>
       <c r="J571" t="n">
+        <v>3</v>
+      </c>
+      <c r="K571" t="n">
         <v>3.727322442089522</v>
       </c>
     </row>
@@ -22173,6 +23888,9 @@
         </is>
       </c>
       <c r="J572" t="n">
+        <v>3</v>
+      </c>
+      <c r="K572" t="n">
         <v>3.727322442089522</v>
       </c>
     </row>
@@ -22211,6 +23929,9 @@
         </is>
       </c>
       <c r="J573" t="n">
+        <v>3</v>
+      </c>
+      <c r="K573" t="n">
         <v>3.727322442089522</v>
       </c>
     </row>
@@ -22249,6 +23970,9 @@
         </is>
       </c>
       <c r="J574" t="n">
+        <v>3</v>
+      </c>
+      <c r="K574" t="n">
         <v>3.696780061471487</v>
       </c>
     </row>
@@ -22287,6 +24011,9 @@
         </is>
       </c>
       <c r="J575" t="n">
+        <v>3</v>
+      </c>
+      <c r="K575" t="n">
         <v>3.648887556502674</v>
       </c>
     </row>
@@ -22325,6 +24052,9 @@
         </is>
       </c>
       <c r="J576" t="n">
+        <v>3</v>
+      </c>
+      <c r="K576" t="n">
         <v>3.648887556502674</v>
       </c>
     </row>
@@ -22363,6 +24093,9 @@
         </is>
       </c>
       <c r="J577" t="n">
+        <v>3</v>
+      </c>
+      <c r="K577" t="n">
         <v>3.580716454266587</v>
       </c>
     </row>
@@ -22401,6 +24134,9 @@
         </is>
       </c>
       <c r="J578" t="n">
+        <v>3</v>
+      </c>
+      <c r="K578" t="n">
         <v>3.580716454266587</v>
       </c>
     </row>
@@ -22439,6 +24175,9 @@
         </is>
       </c>
       <c r="J579" t="n">
+        <v>3</v>
+      </c>
+      <c r="K579" t="n">
         <v>3.400574246844875</v>
       </c>
     </row>
@@ -22477,6 +24216,9 @@
         </is>
       </c>
       <c r="J580" t="n">
+        <v>3</v>
+      </c>
+      <c r="K580" t="n">
         <v>3.331795405673061</v>
       </c>
     </row>
@@ -22515,6 +24257,9 @@
         </is>
       </c>
       <c r="J581" t="n">
+        <v>3</v>
+      </c>
+      <c r="K581" t="n">
         <v>3.322258425256809</v>
       </c>
     </row>
@@ -22553,6 +24298,9 @@
         </is>
       </c>
       <c r="J582" t="n">
+        <v>3</v>
+      </c>
+      <c r="K582" t="n">
         <v>3.141595763257749</v>
       </c>
     </row>
@@ -22591,6 +24339,9 @@
         </is>
       </c>
       <c r="J583" t="n">
+        <v>3</v>
+      </c>
+      <c r="K583" t="n">
         <v>3.160898782349284</v>
       </c>
     </row>
@@ -22629,6 +24380,9 @@
         </is>
       </c>
       <c r="J584" t="n">
+        <v>3</v>
+      </c>
+      <c r="K584" t="n">
         <v>3.166803215221587</v>
       </c>
     </row>
@@ -22667,6 +24421,9 @@
         </is>
       </c>
       <c r="J585" t="n">
+        <v>3</v>
+      </c>
+      <c r="K585" t="n">
         <v>3.203183585331309</v>
       </c>
     </row>
@@ -22705,6 +24462,9 @@
         </is>
       </c>
       <c r="J586" t="n">
+        <v>3</v>
+      </c>
+      <c r="K586" t="n">
         <v>3.452014293068538</v>
       </c>
     </row>
@@ -22743,6 +24503,9 @@
         </is>
       </c>
       <c r="J587" t="n">
+        <v>3</v>
+      </c>
+      <c r="K587" t="n">
         <v>3.574337471173696</v>
       </c>
     </row>
@@ -22781,6 +24544,9 @@
         </is>
       </c>
       <c r="J588" t="n">
+        <v>3</v>
+      </c>
+      <c r="K588" t="n">
         <v>3.648174591356619</v>
       </c>
     </row>
@@ -22819,6 +24585,9 @@
         </is>
       </c>
       <c r="J589" t="n">
+        <v>3</v>
+      </c>
+      <c r="K589" t="n">
         <v>3.685613172857863</v>
       </c>
     </row>
@@ -22857,6 +24626,9 @@
         </is>
       </c>
       <c r="J590" t="n">
+        <v>3</v>
+      </c>
+      <c r="K590" t="n">
         <v>3.738505277220195</v>
       </c>
     </row>
@@ -22895,6 +24667,9 @@
         </is>
       </c>
       <c r="J591" t="n">
+        <v>3</v>
+      </c>
+      <c r="K591" t="n">
         <v>3.810277718818141</v>
       </c>
     </row>
@@ -22933,6 +24708,9 @@
         </is>
       </c>
       <c r="J592" t="n">
+        <v>3</v>
+      </c>
+      <c r="K592" t="n">
         <v>3.810277718818141</v>
       </c>
     </row>
@@ -22971,6 +24749,9 @@
         </is>
       </c>
       <c r="J593" t="n">
+        <v>3</v>
+      </c>
+      <c r="K593" t="n">
         <v>3.79961834668442</v>
       </c>
     </row>
@@ -23009,6 +24790,9 @@
         </is>
       </c>
       <c r="J594" t="n">
+        <v>3</v>
+      </c>
+      <c r="K594" t="n">
         <v>3.829308753991201</v>
       </c>
     </row>
@@ -23047,6 +24831,9 @@
         </is>
       </c>
       <c r="J595" t="n">
+        <v>3</v>
+      </c>
+      <c r="K595" t="n">
         <v>3.903204952569961</v>
       </c>
     </row>
@@ -23085,6 +24872,9 @@
         </is>
       </c>
       <c r="J596" t="n">
+        <v>3</v>
+      </c>
+      <c r="K596" t="n">
         <v>3.91461405714379</v>
       </c>
     </row>
@@ -23123,6 +24913,9 @@
         </is>
       </c>
       <c r="J597" t="n">
+        <v>3</v>
+      </c>
+      <c r="K597" t="n">
         <v>3.942299363667987</v>
       </c>
     </row>
@@ -23161,6 +24954,9 @@
         </is>
       </c>
       <c r="J598" t="n">
+        <v>3</v>
+      </c>
+      <c r="K598" t="n">
         <v>3.978058997701828</v>
       </c>
     </row>
@@ -23199,6 +24995,9 @@
         </is>
       </c>
       <c r="J599" t="n">
+        <v>3</v>
+      </c>
+      <c r="K599" t="n">
         <v>3.978058997701828</v>
       </c>
     </row>
@@ -23237,6 +25036,9 @@
         </is>
       </c>
       <c r="J600" t="n">
+        <v>3</v>
+      </c>
+      <c r="K600" t="n">
         <v>3.923686260811308</v>
       </c>
     </row>
@@ -23275,6 +25077,9 @@
         </is>
       </c>
       <c r="J601" t="n">
+        <v>3</v>
+      </c>
+      <c r="K601" t="n">
         <v>3.872735511609227</v>
       </c>
     </row>
@@ -23313,6 +25118,9 @@
         </is>
       </c>
       <c r="J602" t="n">
+        <v>3</v>
+      </c>
+      <c r="K602" t="n">
         <v>3.804517660543222</v>
       </c>
     </row>
@@ -23351,6 +25159,9 @@
         </is>
       </c>
       <c r="J603" t="n">
+        <v>3</v>
+      </c>
+      <c r="K603" t="n">
         <v>3.614568201969552</v>
       </c>
     </row>
@@ -23389,6 +25200,9 @@
         </is>
       </c>
       <c r="J604" t="n">
+        <v>3</v>
+      </c>
+      <c r="K604" t="n">
         <v>3.587134043046796</v>
       </c>
     </row>
@@ -23427,6 +25241,9 @@
         </is>
       </c>
       <c r="J605" t="n">
+        <v>3</v>
+      </c>
+      <c r="K605" t="n">
         <v>3.585188671498764</v>
       </c>
     </row>
@@ -23465,6 +25282,9 @@
         </is>
       </c>
       <c r="J606" t="n">
+        <v>3</v>
+      </c>
+      <c r="K606" t="n">
         <v>3.594209574588128</v>
       </c>
     </row>
@@ -23503,6 +25323,9 @@
         </is>
       </c>
       <c r="J607" t="n">
+        <v>3</v>
+      </c>
+      <c r="K607" t="n">
         <v>3.594209574588128</v>
       </c>
     </row>
@@ -23541,6 +25364,9 @@
         </is>
       </c>
       <c r="J608" t="n">
+        <v>3</v>
+      </c>
+      <c r="K608" t="n">
         <v>3.613969064175789</v>
       </c>
     </row>
@@ -23579,6 +25405,9 @@
         </is>
       </c>
       <c r="J609" t="n">
+        <v>3</v>
+      </c>
+      <c r="K609" t="n">
         <v>3.627757478111978</v>
       </c>
     </row>
@@ -23617,6 +25446,9 @@
         </is>
       </c>
       <c r="J610" t="n">
+        <v>3</v>
+      </c>
+      <c r="K610" t="n">
         <v>3.613084587547306</v>
       </c>
     </row>
@@ -23655,6 +25487,9 @@
         </is>
       </c>
       <c r="J611" t="n">
+        <v>3</v>
+      </c>
+      <c r="K611" t="n">
         <v>3.547460659883082</v>
       </c>
     </row>
@@ -23693,6 +25528,9 @@
         </is>
       </c>
       <c r="J612" t="n">
+        <v>3</v>
+      </c>
+      <c r="K612" t="n">
         <v>3.547460659883082</v>
       </c>
     </row>
@@ -23731,6 +25569,9 @@
         </is>
       </c>
       <c r="J613" t="n">
+        <v>3</v>
+      </c>
+      <c r="K613" t="n">
         <v>3.521405444870771</v>
       </c>
     </row>
@@ -23769,6 +25610,9 @@
         </is>
       </c>
       <c r="J614" t="n">
+        <v>3</v>
+      </c>
+      <c r="K614" t="n">
         <v>3.521405444870771</v>
       </c>
     </row>
@@ -23807,6 +25651,9 @@
         </is>
       </c>
       <c r="J615" t="n">
+        <v>3</v>
+      </c>
+      <c r="K615" t="n">
         <v>3.497761886664333</v>
       </c>
     </row>
@@ -23845,6 +25692,9 @@
         </is>
       </c>
       <c r="J616" t="n">
+        <v>3</v>
+      </c>
+      <c r="K616" t="n">
         <v>3.506548633564904</v>
       </c>
     </row>
@@ -23883,6 +25733,9 @@
         </is>
       </c>
       <c r="J617" t="n">
+        <v>3</v>
+      </c>
+      <c r="K617" t="n">
         <v>3.399702733378625</v>
       </c>
     </row>
@@ -23921,6 +25774,9 @@
         </is>
       </c>
       <c r="J618" t="n">
+        <v>3</v>
+      </c>
+      <c r="K618" t="n">
         <v>3.298684359939724</v>
       </c>
     </row>
@@ -23959,6 +25815,9 @@
         </is>
       </c>
       <c r="J619" t="n">
+        <v>3</v>
+      </c>
+      <c r="K619" t="n">
         <v>3.291953468671688</v>
       </c>
     </row>
@@ -23997,6 +25856,9 @@
         </is>
       </c>
       <c r="J620" t="n">
+        <v>3</v>
+      </c>
+      <c r="K620" t="n">
         <v>3.260284983130716</v>
       </c>
     </row>
@@ -24035,6 +25897,9 @@
         </is>
       </c>
       <c r="J621" t="n">
+        <v>3</v>
+      </c>
+      <c r="K621" t="n">
         <v>3.27344869049019</v>
       </c>
     </row>
@@ -24073,6 +25938,9 @@
         </is>
       </c>
       <c r="J622" t="n">
+        <v>3</v>
+      </c>
+      <c r="K622" t="n">
         <v>3.27344869049019</v>
       </c>
     </row>
@@ -24111,6 +25979,9 @@
         </is>
       </c>
       <c r="J623" t="n">
+        <v>3</v>
+      </c>
+      <c r="K623" t="n">
         <v>3.27519779776497</v>
       </c>
     </row>
@@ -24149,6 +26020,9 @@
         </is>
       </c>
       <c r="J624" t="n">
+        <v>3</v>
+      </c>
+      <c r="K624" t="n">
         <v>3.301263738147957</v>
       </c>
     </row>
@@ -24187,6 +26061,9 @@
         </is>
       </c>
       <c r="J625" t="n">
+        <v>3</v>
+      </c>
+      <c r="K625" t="n">
         <v>3.301263738147957</v>
       </c>
     </row>
@@ -24225,6 +26102,9 @@
         </is>
       </c>
       <c r="J626" t="n">
+        <v>3</v>
+      </c>
+      <c r="K626" t="n">
         <v>3.289410319604709</v>
       </c>
     </row>
@@ -24263,6 +26143,9 @@
         </is>
       </c>
       <c r="J627" t="n">
+        <v>3</v>
+      </c>
+      <c r="K627" t="n">
         <v>3.208301282896448</v>
       </c>
     </row>
@@ -24301,6 +26184,9 @@
         </is>
       </c>
       <c r="J628" t="n">
+        <v>3</v>
+      </c>
+      <c r="K628" t="n">
         <v>3.18654657786798</v>
       </c>
     </row>
@@ -24339,6 +26225,9 @@
         </is>
       </c>
       <c r="J629" t="n">
+        <v>3</v>
+      </c>
+      <c r="K629" t="n">
         <v>3.181394693844502</v>
       </c>
     </row>
@@ -24377,6 +26266,9 @@
         </is>
       </c>
       <c r="J630" t="n">
+        <v>3</v>
+      </c>
+      <c r="K630" t="n">
         <v>3.191953177748146</v>
       </c>
     </row>
@@ -24415,6 +26307,9 @@
         </is>
       </c>
       <c r="J631" t="n">
+        <v>3</v>
+      </c>
+      <c r="K631" t="n">
         <v>3.209944922811141</v>
       </c>
     </row>
@@ -24453,6 +26348,9 @@
         </is>
       </c>
       <c r="J632" t="n">
+        <v>3</v>
+      </c>
+      <c r="K632" t="n">
         <v>3.263353336253617</v>
       </c>
     </row>
@@ -24491,6 +26389,9 @@
         </is>
       </c>
       <c r="J633" t="n">
+        <v>3</v>
+      </c>
+      <c r="K633" t="n">
         <v>3.337831290092738</v>
       </c>
     </row>
@@ -24529,6 +26430,9 @@
         </is>
       </c>
       <c r="J634" t="n">
+        <v>3</v>
+      </c>
+      <c r="K634" t="n">
         <v>3.363580644358798</v>
       </c>
     </row>
@@ -24567,6 +26471,9 @@
         </is>
       </c>
       <c r="J635" t="n">
+        <v>3</v>
+      </c>
+      <c r="K635" t="n">
         <v>3.401967929630747</v>
       </c>
     </row>
@@ -24605,6 +26512,9 @@
         </is>
       </c>
       <c r="J636" t="n">
+        <v>3</v>
+      </c>
+      <c r="K636" t="n">
         <v>3.465703123588942</v>
       </c>
     </row>
@@ -24643,6 +26553,9 @@
         </is>
       </c>
       <c r="J637" t="n">
+        <v>3</v>
+      </c>
+      <c r="K637" t="n">
         <v>3.465703123588942</v>
       </c>
     </row>
@@ -24681,6 +26594,9 @@
         </is>
       </c>
       <c r="J638" t="n">
+        <v>3</v>
+      </c>
+      <c r="K638" t="n">
         <v>3.469812617773127</v>
       </c>
     </row>
@@ -24719,6 +26635,9 @@
         </is>
       </c>
       <c r="J639" t="n">
+        <v>3</v>
+      </c>
+      <c r="K639" t="n">
         <v>3.516233206805755</v>
       </c>
     </row>
@@ -24757,6 +26676,9 @@
         </is>
       </c>
       <c r="J640" t="n">
+        <v>3</v>
+      </c>
+      <c r="K640" t="n">
         <v>3.547168334934347</v>
       </c>
     </row>
@@ -24795,6 +26717,9 @@
         </is>
       </c>
       <c r="J641" t="n">
+        <v>3</v>
+      </c>
+      <c r="K641" t="n">
         <v>3.567610492370573</v>
       </c>
     </row>
@@ -24833,6 +26758,9 @@
         </is>
       </c>
       <c r="J642" t="n">
+        <v>3</v>
+      </c>
+      <c r="K642" t="n">
         <v>3.543565877588542</v>
       </c>
     </row>
@@ -24871,6 +26799,9 @@
         </is>
       </c>
       <c r="J643" t="n">
+        <v>3</v>
+      </c>
+      <c r="K643" t="n">
         <v>3.497853436442588</v>
       </c>
     </row>
@@ -24909,6 +26840,9 @@
         </is>
       </c>
       <c r="J644" t="n">
+        <v>3</v>
+      </c>
+      <c r="K644" t="n">
         <v>3.464758678334794</v>
       </c>
     </row>
@@ -24947,6 +26881,9 @@
         </is>
       </c>
       <c r="J645" t="n">
+        <v>3</v>
+      </c>
+      <c r="K645" t="n">
         <v>3.474236902706298</v>
       </c>
     </row>
@@ -24985,6 +26922,9 @@
         </is>
       </c>
       <c r="J646" t="n">
+        <v>3</v>
+      </c>
+      <c r="K646" t="n">
         <v>3.53247599786009</v>
       </c>
     </row>
@@ -25023,6 +26963,9 @@
         </is>
       </c>
       <c r="J647" t="n">
+        <v>3</v>
+      </c>
+      <c r="K647" t="n">
         <v>3.703058491773652</v>
       </c>
     </row>
@@ -25061,6 +27004,9 @@
         </is>
       </c>
       <c r="J648" t="n">
+        <v>3</v>
+      </c>
+      <c r="K648" t="n">
         <v>3.775875263652584</v>
       </c>
     </row>
@@ -25099,6 +27045,9 @@
         </is>
       </c>
       <c r="J649" t="n">
+        <v>3</v>
+      </c>
+      <c r="K649" t="n">
         <v>3.775875263652584</v>
       </c>
     </row>
@@ -25137,6 +27086,9 @@
         </is>
       </c>
       <c r="J650" t="n">
+        <v>3</v>
+      </c>
+      <c r="K650" t="n">
         <v>3.775875263652584</v>
       </c>
     </row>
@@ -25175,6 +27127,9 @@
         </is>
       </c>
       <c r="J651" t="n">
+        <v>3</v>
+      </c>
+      <c r="K651" t="n">
         <v>3.931452018409427</v>
       </c>
     </row>
@@ -25213,6 +27168,9 @@
         </is>
       </c>
       <c r="J652" t="n">
+        <v>3</v>
+      </c>
+      <c r="K652" t="n">
         <v>3.982667614685595</v>
       </c>
     </row>
@@ -25251,6 +27209,9 @@
         </is>
       </c>
       <c r="J653" t="n">
+        <v>3</v>
+      </c>
+      <c r="K653" t="n">
         <v>4.002782577201176</v>
       </c>
     </row>
@@ -25289,6 +27250,9 @@
         </is>
       </c>
       <c r="J654" t="n">
+        <v>3</v>
+      </c>
+      <c r="K654" t="n">
         <v>4.114682607796798</v>
       </c>
     </row>
@@ -25327,6 +27291,9 @@
         </is>
       </c>
       <c r="J655" t="n">
+        <v>3</v>
+      </c>
+      <c r="K655" t="n">
         <v>4.114682607796798</v>
       </c>
     </row>
@@ -25365,6 +27332,9 @@
         </is>
       </c>
       <c r="J656" t="n">
+        <v>3</v>
+      </c>
+      <c r="K656" t="n">
         <v>4.114682607796798</v>
       </c>
     </row>
@@ -25403,6 +27373,9 @@
         </is>
       </c>
       <c r="J657" t="n">
+        <v>3</v>
+      </c>
+      <c r="K657" t="n">
         <v>4.179457048694251</v>
       </c>
     </row>
@@ -25441,6 +27414,9 @@
         </is>
       </c>
       <c r="J658" t="n">
+        <v>3</v>
+      </c>
+      <c r="K658" t="n">
         <v>4.227356761953456</v>
       </c>
     </row>
@@ -25479,6 +27455,9 @@
         </is>
       </c>
       <c r="J659" t="n">
+        <v>3</v>
+      </c>
+      <c r="K659" t="n">
         <v>4.348700606631981</v>
       </c>
     </row>
@@ -25517,6 +27496,9 @@
         </is>
       </c>
       <c r="J660" t="n">
+        <v>3</v>
+      </c>
+      <c r="K660" t="n">
         <v>4.521183869121915</v>
       </c>
     </row>
@@ -25555,6 +27537,9 @@
         </is>
       </c>
       <c r="J661" t="n">
+        <v>3</v>
+      </c>
+      <c r="K661" t="n">
         <v>4.500583131286295</v>
       </c>
     </row>
@@ -25593,6 +27578,9 @@
         </is>
       </c>
       <c r="J662" t="n">
+        <v>3</v>
+      </c>
+      <c r="K662" t="n">
         <v>4.440990973619624</v>
       </c>
     </row>
@@ -25631,6 +27619,9 @@
         </is>
       </c>
       <c r="J663" t="n">
+        <v>3</v>
+      </c>
+      <c r="K663" t="n">
         <v>4.422617725795629</v>
       </c>
     </row>
@@ -25669,6 +27660,9 @@
         </is>
       </c>
       <c r="J664" t="n">
+        <v>3</v>
+      </c>
+      <c r="K664" t="n">
         <v>4.42108450919492</v>
       </c>
     </row>
@@ -25707,6 +27701,9 @@
         </is>
       </c>
       <c r="J665" t="n">
+        <v>3</v>
+      </c>
+      <c r="K665" t="n">
         <v>4.376839312327779</v>
       </c>
     </row>
@@ -25745,6 +27742,9 @@
         </is>
       </c>
       <c r="J666" t="n">
+        <v>3</v>
+      </c>
+      <c r="K666" t="n">
         <v>4.366531490052812</v>
       </c>
     </row>
@@ -25783,6 +27783,9 @@
         </is>
       </c>
       <c r="J667" t="n">
+        <v>3</v>
+      </c>
+      <c r="K667" t="n">
         <v>4.366531490052812</v>
       </c>
     </row>
@@ -25821,6 +27824,9 @@
         </is>
       </c>
       <c r="J668" t="n">
+        <v>3</v>
+      </c>
+      <c r="K668" t="n">
         <v>4.289627799319583</v>
       </c>
     </row>
@@ -25859,6 +27865,9 @@
         </is>
       </c>
       <c r="J669" t="n">
+        <v>3</v>
+      </c>
+      <c r="K669" t="n">
         <v>4.215443368471973</v>
       </c>
     </row>
@@ -25897,6 +27906,9 @@
         </is>
       </c>
       <c r="J670" t="n">
+        <v>3</v>
+      </c>
+      <c r="K670" t="n">
         <v>4.141064684913851</v>
       </c>
     </row>
@@ -25935,6 +27947,9 @@
         </is>
       </c>
       <c r="J671" t="n">
+        <v>3</v>
+      </c>
+      <c r="K671" t="n">
         <v>3.966351004065593</v>
       </c>
     </row>
@@ -25973,6 +27988,9 @@
         </is>
       </c>
       <c r="J672" t="n">
+        <v>3</v>
+      </c>
+      <c r="K672" t="n">
         <v>3.88080202022502</v>
       </c>
     </row>
@@ -26011,6 +28029,9 @@
         </is>
       </c>
       <c r="J673" t="n">
+        <v>3</v>
+      </c>
+      <c r="K673" t="n">
         <v>3.850941208949669</v>
       </c>
     </row>
@@ -26049,6 +28070,9 @@
         </is>
       </c>
       <c r="J674" t="n">
+        <v>3</v>
+      </c>
+      <c r="K674" t="n">
         <v>3.850941208949669</v>
       </c>
     </row>
@@ -26087,6 +28111,9 @@
         </is>
       </c>
       <c r="J675" t="n">
+        <v>3</v>
+      </c>
+      <c r="K675" t="n">
         <v>3.811480648489826</v>
       </c>
     </row>
@@ -26125,6 +28152,9 @@
         </is>
       </c>
       <c r="J676" t="n">
+        <v>3</v>
+      </c>
+      <c r="K676" t="n">
         <v>3.762419281057994</v>
       </c>
     </row>
@@ -26163,6 +28193,9 @@
         </is>
       </c>
       <c r="J677" t="n">
+        <v>3</v>
+      </c>
+      <c r="K677" t="n">
         <v>3.762419281057994</v>
       </c>
     </row>
@@ -26201,6 +28234,9 @@
         </is>
       </c>
       <c r="J678" t="n">
+        <v>3</v>
+      </c>
+      <c r="K678" t="n">
         <v>3.698222083745885</v>
       </c>
     </row>
@@ -26239,6 +28275,9 @@
         </is>
       </c>
       <c r="J679" t="n">
+        <v>3</v>
+      </c>
+      <c r="K679" t="n">
         <v>3.684853168547362</v>
       </c>
     </row>
@@ -26277,6 +28316,9 @@
         </is>
       </c>
       <c r="J680" t="n">
+        <v>3</v>
+      </c>
+      <c r="K680" t="n">
         <v>3.662098804452061</v>
       </c>
     </row>
@@ -26315,6 +28357,9 @@
         </is>
       </c>
       <c r="J681" t="n">
+        <v>3</v>
+      </c>
+      <c r="K681" t="n">
         <v>3.662098804452061</v>
       </c>
     </row>
@@ -26353,6 +28398,9 @@
         </is>
       </c>
       <c r="J682" t="n">
+        <v>3</v>
+      </c>
+      <c r="K682" t="n">
         <v>3.61623451407822</v>
       </c>
     </row>
@@ -26391,6 +28439,9 @@
         </is>
       </c>
       <c r="J683" t="n">
+        <v>3</v>
+      </c>
+      <c r="K683" t="n">
         <v>3.670640138196266</v>
       </c>
     </row>
@@ -26429,6 +28480,9 @@
         </is>
       </c>
       <c r="J684" t="n">
+        <v>3</v>
+      </c>
+      <c r="K684" t="n">
         <v>3.670640138196266</v>
       </c>
     </row>
@@ -26467,6 +28521,9 @@
         </is>
       </c>
       <c r="J685" t="n">
+        <v>3</v>
+      </c>
+      <c r="K685" t="n">
         <v>3.670640138196266</v>
       </c>
     </row>
@@ -26505,6 +28562,9 @@
         </is>
       </c>
       <c r="J686" t="n">
+        <v>3</v>
+      </c>
+      <c r="K686" t="n">
         <v>3.77296637088824</v>
       </c>
     </row>
@@ -26543,6 +28603,9 @@
         </is>
       </c>
       <c r="J687" t="n">
+        <v>3</v>
+      </c>
+      <c r="K687" t="n">
         <v>4.367673490085361</v>
       </c>
     </row>
@@ -26581,6 +28644,9 @@
         </is>
       </c>
       <c r="J688" t="n">
+        <v>3</v>
+      </c>
+      <c r="K688" t="n">
         <v>4.750769397264579</v>
       </c>
     </row>
@@ -26619,6 +28685,9 @@
         </is>
       </c>
       <c r="J689" t="n">
+        <v>3</v>
+      </c>
+      <c r="K689" t="n">
         <v>3.867519880845868</v>
       </c>
     </row>
@@ -26657,6 +28726,9 @@
         </is>
       </c>
       <c r="J690" t="n">
+        <v>3</v>
+      </c>
+      <c r="K690" t="n">
         <v>3.867519880845868</v>
       </c>
     </row>
@@ -26695,6 +28767,9 @@
         </is>
       </c>
       <c r="J691" t="n">
+        <v>3</v>
+      </c>
+      <c r="K691" t="n">
         <v>3.078655280970453</v>
       </c>
     </row>
@@ -26733,6 +28808,9 @@
         </is>
       </c>
       <c r="J692" t="n">
+        <v>3</v>
+      </c>
+      <c r="K692" t="n">
         <v>1.328337265668739</v>
       </c>
     </row>
@@ -26771,6 +28849,9 @@
         </is>
       </c>
       <c r="J693" t="n">
+        <v>3</v>
+      </c>
+      <c r="K693" t="n">
         <v>1.15908494429521</v>
       </c>
     </row>
@@ -26809,6 +28890,9 @@
         </is>
       </c>
       <c r="J694" t="n">
+        <v>3</v>
+      </c>
+      <c r="K694" t="n">
         <v>1.15908494429521</v>
       </c>
     </row>
@@ -26847,6 +28931,9 @@
         </is>
       </c>
       <c r="J695" t="n">
+        <v>3</v>
+      </c>
+      <c r="K695" t="n">
         <v>1.364781195035363</v>
       </c>
     </row>
@@ -26885,6 +28972,9 @@
         </is>
       </c>
       <c r="J696" t="n">
+        <v>3</v>
+      </c>
+      <c r="K696" t="n">
         <v>1.53639448201659</v>
       </c>
     </row>
@@ -26923,6 +29013,9 @@
         </is>
       </c>
       <c r="J697" t="n">
+        <v>3</v>
+      </c>
+      <c r="K697" t="n">
         <v>1.887002571168518</v>
       </c>
     </row>
@@ -26961,6 +29054,9 @@
         </is>
       </c>
       <c r="J698" t="n">
+        <v>3</v>
+      </c>
+      <c r="K698" t="n">
         <v>2.323128897170909</v>
       </c>
     </row>
@@ -26999,6 +29095,9 @@
         </is>
       </c>
       <c r="J699" t="n">
+        <v>3</v>
+      </c>
+      <c r="K699" t="n">
         <v>2.323128897170909</v>
       </c>
     </row>
@@ -27037,6 +29136,9 @@
         </is>
       </c>
       <c r="J700" t="n">
+        <v>3</v>
+      </c>
+      <c r="K700" t="n">
         <v>2.450743265661965</v>
       </c>
     </row>
@@ -27075,6 +29177,9 @@
         </is>
       </c>
       <c r="J701" t="n">
+        <v>3</v>
+      </c>
+      <c r="K701" t="n">
         <v>2.450743265661965</v>
       </c>
     </row>
@@ -27113,6 +29218,9 @@
         </is>
       </c>
       <c r="J702" t="n">
+        <v>3</v>
+      </c>
+      <c r="K702" t="n">
         <v>2.475254261949296</v>
       </c>
     </row>
@@ -27151,6 +29259,9 @@
         </is>
       </c>
       <c r="J703" t="n">
+        <v>3</v>
+      </c>
+      <c r="K703" t="n">
         <v>2.475254261949296</v>
       </c>
     </row>
@@ -27189,6 +29300,9 @@
         </is>
       </c>
       <c r="J704" t="n">
+        <v>3</v>
+      </c>
+      <c r="K704" t="n">
         <v>2.459227771244468</v>
       </c>
     </row>
@@ -27227,6 +29341,9 @@
         </is>
       </c>
       <c r="J705" t="n">
+        <v>3</v>
+      </c>
+      <c r="K705" t="n">
         <v>2.459227771244468</v>
       </c>
     </row>
@@ -27265,6 +29382,9 @@
         </is>
       </c>
       <c r="J706" t="n">
+        <v>3</v>
+      </c>
+      <c r="K706" t="n">
         <v>2.43461815898368</v>
       </c>
     </row>
@@ -27303,6 +29423,9 @@
         </is>
       </c>
       <c r="J707" t="n">
+        <v>3</v>
+      </c>
+      <c r="K707" t="n">
         <v>2.326200551573592</v>
       </c>
     </row>
@@ -27341,6 +29464,9 @@
         </is>
       </c>
       <c r="J708" t="n">
+        <v>3</v>
+      </c>
+      <c r="K708" t="n">
         <v>2.264299598695442</v>
       </c>
     </row>
@@ -27379,6 +29505,9 @@
         </is>
       </c>
       <c r="J709" t="n">
+        <v>3</v>
+      </c>
+      <c r="K709" t="n">
         <v>2.264299598695442</v>
       </c>
     </row>
@@ -27417,6 +29546,9 @@
         </is>
       </c>
       <c r="J710" t="n">
+        <v>3</v>
+      </c>
+      <c r="K710" t="n">
         <v>1.967348237245286</v>
       </c>
     </row>
@@ -27455,6 +29587,9 @@
         </is>
       </c>
       <c r="J711" t="n">
+        <v>3</v>
+      </c>
+      <c r="K711" t="n">
         <v>1.967348237245286</v>
       </c>
     </row>
@@ -27493,6 +29628,9 @@
         </is>
       </c>
       <c r="J712" t="n">
+        <v>3</v>
+      </c>
+      <c r="K712" t="n">
         <v>1.86013837832737</v>
       </c>
     </row>
@@ -27531,6 +29669,9 @@
         </is>
       </c>
       <c r="J713" t="n">
+        <v>3</v>
+      </c>
+      <c r="K713" t="n">
         <v>1.708920233583261</v>
       </c>
     </row>
@@ -27569,6 +29710,9 @@
         </is>
       </c>
       <c r="J714" t="n">
+        <v>3</v>
+      </c>
+      <c r="K714" t="n">
         <v>1.708920233583261</v>
       </c>
     </row>
@@ -27607,6 +29751,9 @@
         </is>
       </c>
       <c r="J715" t="n">
+        <v>3</v>
+      </c>
+      <c r="K715" t="n">
         <v>1.708920233583261</v>
       </c>
     </row>
@@ -27645,6 +29792,9 @@
         </is>
       </c>
       <c r="J716" t="n">
+        <v>3</v>
+      </c>
+      <c r="K716" t="n">
         <v>1.644876511437556</v>
       </c>
     </row>
@@ -27683,6 +29833,9 @@
         </is>
       </c>
       <c r="J717" t="n">
+        <v>3</v>
+      </c>
+      <c r="K717" t="n">
         <v>1.644876511437556</v>
       </c>
     </row>
@@ -27721,6 +29874,9 @@
         </is>
       </c>
       <c r="J718" t="n">
+        <v>3</v>
+      </c>
+      <c r="K718" t="n">
         <v>1.588400297438308</v>
       </c>
     </row>
@@ -27759,6 +29915,9 @@
         </is>
       </c>
       <c r="J719" t="n">
+        <v>3</v>
+      </c>
+      <c r="K719" t="n">
         <v>1.56213921201233</v>
       </c>
     </row>
@@ -27797,6 +29956,9 @@
         </is>
       </c>
       <c r="J720" t="n">
+        <v>3</v>
+      </c>
+      <c r="K720" t="n">
         <v>1.49043004624687</v>
       </c>
     </row>
@@ -27835,6 +29997,9 @@
         </is>
       </c>
       <c r="J721" t="n">
+        <v>3</v>
+      </c>
+      <c r="K721" t="n">
         <v>1.49043004624687</v>
       </c>
     </row>
@@ -27873,6 +30038,9 @@
         </is>
       </c>
       <c r="J722" t="n">
+        <v>3</v>
+      </c>
+      <c r="K722" t="n">
         <v>1.454721901079359</v>
       </c>
     </row>
@@ -27911,6 +30079,9 @@
         </is>
       </c>
       <c r="J723" t="n">
+        <v>3</v>
+      </c>
+      <c r="K723" t="n">
         <v>1.416444895233653</v>
       </c>
     </row>
@@ -27949,6 +30120,9 @@
         </is>
       </c>
       <c r="J724" t="n">
+        <v>3</v>
+      </c>
+      <c r="K724" t="n">
         <v>1.361824591920848</v>
       </c>
     </row>
@@ -27987,6 +30161,9 @@
         </is>
       </c>
       <c r="J725" t="n">
+        <v>3</v>
+      </c>
+      <c r="K725" t="n">
         <v>1.357822264239969</v>
       </c>
     </row>
@@ -28025,6 +30202,9 @@
         </is>
       </c>
       <c r="J726" t="n">
+        <v>3</v>
+      </c>
+      <c r="K726" t="n">
         <v>1.387877769991956</v>
       </c>
     </row>
@@ -28063,6 +30243,9 @@
         </is>
       </c>
       <c r="J727" t="n">
+        <v>3</v>
+      </c>
+      <c r="K727" t="n">
         <v>1.474383223676014</v>
       </c>
     </row>
@@ -28101,6 +30284,9 @@
         </is>
       </c>
       <c r="J728" t="n">
+        <v>3</v>
+      </c>
+      <c r="K728" t="n">
         <v>1.528205210346673</v>
       </c>
     </row>
@@ -28139,6 +30325,9 @@
         </is>
       </c>
       <c r="J729" t="n">
+        <v>3</v>
+      </c>
+      <c r="K729" t="n">
         <v>1.528205210346673</v>
       </c>
     </row>
@@ -28177,6 +30366,9 @@
         </is>
       </c>
       <c r="J730" t="n">
+        <v>3</v>
+      </c>
+      <c r="K730" t="n">
         <v>1.583339945519227</v>
       </c>
     </row>
@@ -28215,6 +30407,9 @@
         </is>
       </c>
       <c r="J731" t="n">
+        <v>3</v>
+      </c>
+      <c r="K731" t="n">
         <v>1.701033919475326</v>
       </c>
     </row>
@@ -28253,6 +30448,9 @@
         </is>
       </c>
       <c r="J732" t="n">
+        <v>3</v>
+      </c>
+      <c r="K732" t="n">
         <v>1.701033919475326</v>
       </c>
     </row>
@@ -28291,6 +30489,9 @@
         </is>
       </c>
       <c r="J733" t="n">
+        <v>3</v>
+      </c>
+      <c r="K733" t="n">
         <v>1.856092099585409</v>
       </c>
     </row>
@@ -28329,6 +30530,9 @@
         </is>
       </c>
       <c r="J734" t="n">
+        <v>3</v>
+      </c>
+      <c r="K734" t="n">
         <v>1.931189381095863</v>
       </c>
     </row>
@@ -28367,6 +30571,9 @@
         </is>
       </c>
       <c r="J735" t="n">
+        <v>3</v>
+      </c>
+      <c r="K735" t="n">
         <v>2.003662893191851</v>
       </c>
     </row>
@@ -28405,6 +30612,9 @@
         </is>
       </c>
       <c r="J736" t="n">
+        <v>3</v>
+      </c>
+      <c r="K736" t="n">
         <v>1.964593875611641</v>
       </c>
     </row>
@@ -28443,6 +30653,9 @@
         </is>
       </c>
       <c r="J737" t="n">
+        <v>3</v>
+      </c>
+      <c r="K737" t="n">
         <v>1.964593875611641</v>
       </c>
     </row>
@@ -28481,6 +30694,9 @@
         </is>
       </c>
       <c r="J738" t="n">
+        <v>3</v>
+      </c>
+      <c r="K738" t="n">
         <v>1.754517992862946</v>
       </c>
     </row>
@@ -28519,6 +30735,9 @@
         </is>
       </c>
       <c r="J739" t="n">
+        <v>3</v>
+      </c>
+      <c r="K739" t="n">
         <v>1.628068560037562</v>
       </c>
     </row>
@@ -28557,6 +30776,9 @@
         </is>
       </c>
       <c r="J740" t="n">
+        <v>3</v>
+      </c>
+      <c r="K740" t="n">
         <v>1.411330553839739</v>
       </c>
     </row>
@@ -28595,6 +30817,9 @@
         </is>
       </c>
       <c r="J741" t="n">
+        <v>3</v>
+      </c>
+      <c r="K741" t="n">
         <v>1.411330553839739</v>
       </c>
     </row>
@@ -28633,6 +30858,9 @@
         </is>
       </c>
       <c r="J742" t="n">
+        <v>3</v>
+      </c>
+      <c r="K742" t="n">
         <v>1.463640379107531</v>
       </c>
     </row>
@@ -28671,6 +30899,9 @@
         </is>
       </c>
       <c r="J743" t="n">
+        <v>3</v>
+      </c>
+      <c r="K743" t="n">
         <v>1.463640379107531</v>
       </c>
     </row>
@@ -28709,6 +30940,9 @@
         </is>
       </c>
       <c r="J744" t="n">
+        <v>3</v>
+      </c>
+      <c r="K744" t="n">
         <v>1.542850296116594</v>
       </c>
     </row>
@@ -28747,6 +30981,9 @@
         </is>
       </c>
       <c r="J745" t="n">
+        <v>3</v>
+      </c>
+      <c r="K745" t="n">
         <v>1.542850296116594</v>
       </c>
     </row>
@@ -28785,6 +31022,9 @@
         </is>
       </c>
       <c r="J746" t="n">
+        <v>3</v>
+      </c>
+      <c r="K746" t="n">
         <v>1.56972057377767</v>
       </c>
     </row>
@@ -28823,6 +31063,9 @@
         </is>
       </c>
       <c r="J747" t="n">
+        <v>3</v>
+      </c>
+      <c r="K747" t="n">
         <v>1.588168873634134</v>
       </c>
     </row>
@@ -28861,6 +31104,9 @@
         </is>
       </c>
       <c r="J748" t="n">
+        <v>3</v>
+      </c>
+      <c r="K748" t="n">
         <v>1.59698593109862</v>
       </c>
     </row>
@@ -28899,6 +31145,9 @@
         </is>
       </c>
       <c r="J749" t="n">
+        <v>3</v>
+      </c>
+      <c r="K749" t="n">
         <v>1.612466123059784</v>
       </c>
     </row>
@@ -28937,6 +31186,9 @@
         </is>
       </c>
       <c r="J750" t="n">
+        <v>3</v>
+      </c>
+      <c r="K750" t="n">
         <v>1.612466123059784</v>
       </c>
     </row>
@@ -28975,6 +31227,9 @@
         </is>
       </c>
       <c r="J751" t="n">
+        <v>3</v>
+      </c>
+      <c r="K751" t="n">
         <v>1.610180754619413</v>
       </c>
     </row>
@@ -29013,6 +31268,9 @@
         </is>
       </c>
       <c r="J752" t="n">
+        <v>3</v>
+      </c>
+      <c r="K752" t="n">
         <v>1.623648222273373</v>
       </c>
     </row>
@@ -29051,6 +31309,9 @@
         </is>
       </c>
       <c r="J753" t="n">
+        <v>3</v>
+      </c>
+      <c r="K753" t="n">
         <v>1.623648222273373</v>
       </c>
     </row>
@@ -29089,6 +31350,9 @@
         </is>
       </c>
       <c r="J754" t="n">
+        <v>3</v>
+      </c>
+      <c r="K754" t="n">
         <v>1.622013018675033</v>
       </c>
     </row>
@@ -29127,6 +31391,9 @@
         </is>
       </c>
       <c r="J755" t="n">
+        <v>3</v>
+      </c>
+      <c r="K755" t="n">
         <v>1.535534834485925</v>
       </c>
     </row>
@@ -29165,6 +31432,9 @@
         </is>
       </c>
       <c r="J756" t="n">
+        <v>3</v>
+      </c>
+      <c r="K756" t="n">
         <v>1.535534834485925</v>
       </c>
     </row>
@@ -29203,6 +31473,9 @@
         </is>
       </c>
       <c r="J757" t="n">
+        <v>3</v>
+      </c>
+      <c r="K757" t="n">
         <v>1.535534834485925</v>
       </c>
     </row>
@@ -29241,6 +31514,9 @@
         </is>
       </c>
       <c r="J758" t="n">
+        <v>3</v>
+      </c>
+      <c r="K758" t="n">
         <v>1.518363871998768</v>
       </c>
     </row>
@@ -29279,6 +31555,9 @@
         </is>
       </c>
       <c r="J759" t="n">
+        <v>3</v>
+      </c>
+      <c r="K759" t="n">
         <v>1.437142010422004</v>
       </c>
     </row>
@@ -29317,6 +31596,9 @@
         </is>
       </c>
       <c r="J760" t="n">
+        <v>3</v>
+      </c>
+      <c r="K760" t="n">
         <v>1.416938535151454</v>
       </c>
     </row>
@@ -29355,6 +31637,9 @@
         </is>
       </c>
       <c r="J761" t="n">
+        <v>3</v>
+      </c>
+      <c r="K761" t="n">
         <v>1.4059865388659</v>
       </c>
     </row>
@@ -29393,6 +31678,9 @@
         </is>
       </c>
       <c r="J762" t="n">
+        <v>3</v>
+      </c>
+      <c r="K762" t="n">
         <v>1.389829268916629</v>
       </c>
     </row>
@@ -29431,6 +31719,9 @@
         </is>
       </c>
       <c r="J763" t="n">
+        <v>3</v>
+      </c>
+      <c r="K763" t="n">
         <v>1.457731679114018</v>
       </c>
     </row>
@@ -29469,6 +31760,9 @@
         </is>
       </c>
       <c r="J764" t="n">
+        <v>3</v>
+      </c>
+      <c r="K764" t="n">
         <v>1.457731679114018</v>
       </c>
     </row>
@@ -29507,6 +31801,9 @@
         </is>
       </c>
       <c r="J765" t="n">
+        <v>3</v>
+      </c>
+      <c r="K765" t="n">
         <v>1.602765195103935</v>
       </c>
     </row>
@@ -29545,6 +31842,9 @@
         </is>
       </c>
       <c r="J766" t="n">
+        <v>3</v>
+      </c>
+      <c r="K766" t="n">
         <v>1.645938856782272</v>
       </c>
     </row>
@@ -29583,6 +31883,9 @@
         </is>
       </c>
       <c r="J767" t="n">
+        <v>3</v>
+      </c>
+      <c r="K767" t="n">
         <v>1.65086205045192</v>
       </c>
     </row>
@@ -29621,6 +31924,9 @@
         </is>
       </c>
       <c r="J768" t="n">
+        <v>3</v>
+      </c>
+      <c r="K768" t="n">
         <v>1.656882688899178</v>
       </c>
     </row>
@@ -29659,6 +31965,9 @@
         </is>
       </c>
       <c r="J769" t="n">
+        <v>3</v>
+      </c>
+      <c r="K769" t="n">
         <v>1.658299181951782</v>
       </c>
     </row>
@@ -29697,6 +32006,9 @@
         </is>
       </c>
       <c r="J770" t="n">
+        <v>3</v>
+      </c>
+      <c r="K770" t="n">
         <v>1.621214772240193</v>
       </c>
     </row>
@@ -29735,6 +32047,9 @@
         </is>
       </c>
       <c r="J771" t="n">
+        <v>3</v>
+      </c>
+      <c r="K771" t="n">
         <v>1.626111691365553</v>
       </c>
     </row>
@@ -29773,6 +32088,9 @@
         </is>
       </c>
       <c r="J772" t="n">
+        <v>3</v>
+      </c>
+      <c r="K772" t="n">
         <v>1.600083268497904</v>
       </c>
     </row>
@@ -29811,6 +32129,9 @@
         </is>
       </c>
       <c r="J773" t="n">
+        <v>3</v>
+      </c>
+      <c r="K773" t="n">
         <v>1.597658316370406</v>
       </c>
     </row>
@@ -29849,6 +32170,9 @@
         </is>
       </c>
       <c r="J774" t="n">
+        <v>3</v>
+      </c>
+      <c r="K774" t="n">
         <v>1.573484351772946</v>
       </c>
     </row>
@@ -29887,6 +32211,9 @@
         </is>
       </c>
       <c r="J775" t="n">
+        <v>3</v>
+      </c>
+      <c r="K775" t="n">
         <v>1.550149124987181</v>
       </c>
     </row>
@@ -29925,6 +32252,9 @@
         </is>
       </c>
       <c r="J776" t="n">
+        <v>3</v>
+      </c>
+      <c r="K776" t="n">
         <v>1.550149124987181</v>
       </c>
     </row>
@@ -29963,6 +32293,9 @@
         </is>
       </c>
       <c r="J777" t="n">
+        <v>3</v>
+      </c>
+      <c r="K777" t="n">
         <v>1.535490989039913</v>
       </c>
     </row>
@@ -30001,6 +32334,9 @@
         </is>
       </c>
       <c r="J778" t="n">
+        <v>3</v>
+      </c>
+      <c r="K778" t="n">
         <v>1.610683562545311</v>
       </c>
     </row>
@@ -30039,6 +32375,9 @@
         </is>
       </c>
       <c r="J779" t="n">
+        <v>3</v>
+      </c>
+      <c r="K779" t="n">
         <v>1.610683562545311</v>
       </c>
     </row>
@@ -30077,6 +32416,9 @@
         </is>
       </c>
       <c r="J780" t="n">
+        <v>3</v>
+      </c>
+      <c r="K780" t="n">
         <v>1.610683562545311</v>
       </c>
     </row>
@@ -30115,6 +32457,9 @@
         </is>
       </c>
       <c r="J781" t="n">
+        <v>3</v>
+      </c>
+      <c r="K781" t="n">
         <v>1.65052031808787</v>
       </c>
     </row>
@@ -30153,6 +32498,9 @@
         </is>
       </c>
       <c r="J782" t="n">
+        <v>3</v>
+      </c>
+      <c r="K782" t="n">
         <v>1.663352898553057</v>
       </c>
     </row>
@@ -30191,6 +32539,9 @@
         </is>
       </c>
       <c r="J783" t="n">
+        <v>3</v>
+      </c>
+      <c r="K783" t="n">
         <v>1.639169584595099</v>
       </c>
     </row>
@@ -30229,6 +32580,9 @@
         </is>
       </c>
       <c r="J784" t="n">
+        <v>3</v>
+      </c>
+      <c r="K784" t="n">
         <v>1.639169584595099</v>
       </c>
     </row>
@@ -30267,6 +32621,9 @@
         </is>
       </c>
       <c r="J785" t="n">
+        <v>3</v>
+      </c>
+      <c r="K785" t="n">
         <v>1.639169584595099</v>
       </c>
     </row>
@@ -30305,6 +32662,9 @@
         </is>
       </c>
       <c r="J786" t="n">
+        <v>3</v>
+      </c>
+      <c r="K786" t="n">
         <v>1.466846655279628</v>
       </c>
     </row>
@@ -30343,6 +32703,9 @@
         </is>
       </c>
       <c r="J787" t="n">
+        <v>3</v>
+      </c>
+      <c r="K787" t="n">
         <v>1.424481712947825</v>
       </c>
     </row>
@@ -30381,6 +32744,9 @@
         </is>
       </c>
       <c r="J788" t="n">
+        <v>3</v>
+      </c>
+      <c r="K788" t="n">
         <v>1.426674946458663</v>
       </c>
     </row>
@@ -30419,6 +32785,9 @@
         </is>
       </c>
       <c r="J789" t="n">
+        <v>3</v>
+      </c>
+      <c r="K789" t="n">
         <v>1.388737677464995</v>
       </c>
     </row>
@@ -30457,6 +32826,9 @@
         </is>
       </c>
       <c r="J790" t="n">
+        <v>3</v>
+      </c>
+      <c r="K790" t="n">
         <v>1.388737677464995</v>
       </c>
     </row>
@@ -30495,6 +32867,9 @@
         </is>
       </c>
       <c r="J791" t="n">
+        <v>3</v>
+      </c>
+      <c r="K791" t="n">
         <v>1.315851809743908</v>
       </c>
     </row>
@@ -30533,6 +32908,9 @@
         </is>
       </c>
       <c r="J792" t="n">
+        <v>3</v>
+      </c>
+      <c r="K792" t="n">
         <v>1.315851809743908</v>
       </c>
     </row>
@@ -30571,6 +32949,9 @@
         </is>
       </c>
       <c r="J793" t="n">
+        <v>3</v>
+      </c>
+      <c r="K793" t="n">
         <v>1.315851809743908</v>
       </c>
     </row>
@@ -30609,6 +32990,9 @@
         </is>
       </c>
       <c r="J794" t="n">
+        <v>3</v>
+      </c>
+      <c r="K794" t="n">
         <v>1.21119443862518</v>
       </c>
     </row>
@@ -30647,6 +33031,9 @@
         </is>
       </c>
       <c r="J795" t="n">
+        <v>3</v>
+      </c>
+      <c r="K795" t="n">
         <v>1.191174190868714</v>
       </c>
     </row>
@@ -30685,6 +33072,9 @@
         </is>
       </c>
       <c r="J796" t="n">
+        <v>3</v>
+      </c>
+      <c r="K796" t="n">
         <v>1.255408596812928</v>
       </c>
     </row>
@@ -30723,6 +33113,9 @@
         </is>
       </c>
       <c r="J797" t="n">
+        <v>3</v>
+      </c>
+      <c r="K797" t="n">
         <v>1.255408596812928</v>
       </c>
     </row>
@@ -30761,6 +33154,9 @@
         </is>
       </c>
       <c r="J798" t="n">
+        <v>3</v>
+      </c>
+      <c r="K798" t="n">
         <v>1.30004727814302</v>
       </c>
     </row>
@@ -30799,6 +33195,9 @@
         </is>
       </c>
       <c r="J799" t="n">
+        <v>3</v>
+      </c>
+      <c r="K799" t="n">
         <v>1.409982395079707</v>
       </c>
     </row>
@@ -30837,6 +33236,9 @@
         </is>
       </c>
       <c r="J800" t="n">
+        <v>3</v>
+      </c>
+      <c r="K800" t="n">
         <v>1.447687291787138</v>
       </c>
     </row>
@@ -30875,6 +33277,9 @@
         </is>
       </c>
       <c r="J801" t="n">
+        <v>3</v>
+      </c>
+      <c r="K801" t="n">
         <v>1.484278946352729</v>
       </c>
     </row>
@@ -30913,6 +33318,9 @@
         </is>
       </c>
       <c r="J802" t="n">
+        <v>3</v>
+      </c>
+      <c r="K802" t="n">
         <v>1.513130508765279</v>
       </c>
     </row>
@@ -30951,6 +33359,9 @@
         </is>
       </c>
       <c r="J803" t="n">
+        <v>3</v>
+      </c>
+      <c r="K803" t="n">
         <v>1.526360999900184</v>
       </c>
     </row>
@@ -30989,6 +33400,9 @@
         </is>
       </c>
       <c r="J804" t="n">
+        <v>3</v>
+      </c>
+      <c r="K804" t="n">
         <v>1.668973296776535</v>
       </c>
     </row>
@@ -31027,6 +33441,9 @@
         </is>
       </c>
       <c r="J805" t="n">
+        <v>3</v>
+      </c>
+      <c r="K805" t="n">
         <v>1.731309012041773</v>
       </c>
     </row>
@@ -31065,6 +33482,9 @@
         </is>
       </c>
       <c r="J806" t="n">
+        <v>3</v>
+      </c>
+      <c r="K806" t="n">
         <v>1.781540024534186</v>
       </c>
     </row>
@@ -31103,6 +33523,9 @@
         </is>
       </c>
       <c r="J807" t="n">
+        <v>3</v>
+      </c>
+      <c r="K807" t="n">
         <v>1.781540024534186</v>
       </c>
     </row>
@@ -31141,6 +33564,9 @@
         </is>
       </c>
       <c r="J808" t="n">
+        <v>3</v>
+      </c>
+      <c r="K808" t="n">
         <v>1.781540024534186</v>
       </c>
     </row>
@@ -31179,6 +33605,9 @@
         </is>
       </c>
       <c r="J809" t="n">
+        <v>3</v>
+      </c>
+      <c r="K809" t="n">
         <v>1.5038282806164</v>
       </c>
     </row>
@@ -31217,6 +33646,9 @@
         </is>
       </c>
       <c r="J810" t="n">
+        <v>3</v>
+      </c>
+      <c r="K810" t="n">
         <v>1.245663507909112</v>
       </c>
     </row>
@@ -31255,6 +33687,9 @@
         </is>
       </c>
       <c r="J811" t="n">
+        <v>3</v>
+      </c>
+      <c r="K811" t="n">
         <v>1.037827792884522</v>
       </c>
     </row>
@@ -31293,6 +33728,9 @@
         </is>
       </c>
       <c r="J812" t="n">
+        <v>3</v>
+      </c>
+      <c r="K812" t="n">
         <v>0.9383552217234602</v>
       </c>
     </row>
@@ -31331,6 +33769,9 @@
         </is>
       </c>
       <c r="J813" t="n">
+        <v>3</v>
+      </c>
+      <c r="K813" t="n">
         <v>0.8736400230626112</v>
       </c>
     </row>
@@ -31369,6 +33810,9 @@
         </is>
       </c>
       <c r="J814" t="n">
+        <v>3</v>
+      </c>
+      <c r="K814" t="n">
         <v>0.8363483773273188</v>
       </c>
     </row>
@@ -31407,6 +33851,9 @@
         </is>
       </c>
       <c r="J815" t="n">
+        <v>3</v>
+      </c>
+      <c r="K815" t="n">
         <v>0.7976886523627105</v>
       </c>
     </row>
@@ -31445,6 +33892,9 @@
         </is>
       </c>
       <c r="J816" t="n">
+        <v>3</v>
+      </c>
+      <c r="K816" t="n">
         <v>0.7976886523627105</v>
       </c>
     </row>
@@ -31483,6 +33933,9 @@
         </is>
       </c>
       <c r="J817" t="n">
+        <v>3</v>
+      </c>
+      <c r="K817" t="n">
         <v>0.7524597540443071</v>
       </c>
     </row>
@@ -31521,6 +33974,9 @@
         </is>
       </c>
       <c r="J818" t="n">
+        <v>3</v>
+      </c>
+      <c r="K818" t="n">
         <v>0.7550536054579302</v>
       </c>
     </row>
@@ -31559,6 +34015,9 @@
         </is>
       </c>
       <c r="J819" t="n">
+        <v>3</v>
+      </c>
+      <c r="K819" t="n">
         <v>0.7550536054579302</v>
       </c>
     </row>
@@ -31597,6 +34056,9 @@
         </is>
       </c>
       <c r="J820" t="n">
+        <v>3</v>
+      </c>
+      <c r="K820" t="n">
         <v>0.761867319251107</v>
       </c>
     </row>
@@ -31635,6 +34097,9 @@
         </is>
       </c>
       <c r="J821" t="n">
+        <v>3</v>
+      </c>
+      <c r="K821" t="n">
         <v>0.761867319251107</v>
       </c>
     </row>
@@ -31673,6 +34138,9 @@
         </is>
       </c>
       <c r="J822" t="n">
+        <v>3</v>
+      </c>
+      <c r="K822" t="n">
         <v>0.761867319251107</v>
       </c>
     </row>
@@ -31711,6 +34179,9 @@
         </is>
       </c>
       <c r="J823" t="n">
+        <v>3</v>
+      </c>
+      <c r="K823" t="n">
         <v>0.761867319251107</v>
       </c>
     </row>
@@ -31749,6 +34220,9 @@
         </is>
       </c>
       <c r="J824" t="n">
+        <v>3</v>
+      </c>
+      <c r="K824" t="n">
         <v>0.7372526854463468</v>
       </c>
     </row>
@@ -31787,6 +34261,9 @@
         </is>
       </c>
       <c r="J825" t="n">
+        <v>3</v>
+      </c>
+      <c r="K825" t="n">
         <v>0.6918143305450244</v>
       </c>
     </row>
@@ -31825,6 +34302,9 @@
         </is>
       </c>
       <c r="J826" t="n">
+        <v>3</v>
+      </c>
+      <c r="K826" t="n">
         <v>0.6253216690507472</v>
       </c>
     </row>
@@ -31863,6 +34343,9 @@
         </is>
       </c>
       <c r="J827" t="n">
+        <v>3</v>
+      </c>
+      <c r="K827" t="n">
         <v>0.4513025567209175</v>
       </c>
     </row>
@@ -31901,6 +34384,9 @@
         </is>
       </c>
       <c r="J828" t="n">
+        <v>3</v>
+      </c>
+      <c r="K828" t="n">
         <v>0.3317775833481664</v>
       </c>
     </row>
@@ -31939,6 +34425,9 @@
         </is>
       </c>
       <c r="J829" t="n">
+        <v>3</v>
+      </c>
+      <c r="K829" t="n">
         <v>0.2973576002577951</v>
       </c>
     </row>
@@ -31977,6 +34466,9 @@
         </is>
       </c>
       <c r="J830" t="n">
+        <v>3</v>
+      </c>
+      <c r="K830" t="n">
         <v>0.2637201247108184</v>
       </c>
     </row>
@@ -32015,6 +34507,9 @@
         </is>
       </c>
       <c r="J831" t="n">
+        <v>3</v>
+      </c>
+      <c r="K831" t="n">
         <v>0.2103350914282464</v>
       </c>
     </row>
@@ -32053,6 +34548,9 @@
         </is>
       </c>
       <c r="J832" t="n">
+        <v>3</v>
+      </c>
+      <c r="K832" t="n">
         <v>0.2271430704265892</v>
       </c>
     </row>
@@ -32091,6 +34589,9 @@
         </is>
       </c>
       <c r="J833" t="n">
+        <v>3</v>
+      </c>
+      <c r="K833" t="n">
         <v>0.2416766239145968</v>
       </c>
     </row>
@@ -32129,6 +34630,9 @@
         </is>
       </c>
       <c r="J834" t="n">
+        <v>3</v>
+      </c>
+      <c r="K834" t="n">
         <v>0.2942158157727213</v>
       </c>
     </row>
@@ -32167,6 +34671,9 @@
         </is>
       </c>
       <c r="J835" t="n">
+        <v>3</v>
+      </c>
+      <c r="K835" t="n">
         <v>0.2609192312848662</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B02_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B02_Normal_2.xlsx
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>34.19156206107118</v>
+        <v>34.1859209565437</v>
       </c>
     </row>
     <row r="4">
@@ -603,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
     </row>
     <row r="5">
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07391314257579</v>
+        <v>10.08259890354299</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>9.086312375561954</v>
+        <v>9.090161634267119</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>8.746824124790566</v>
+        <v>8.749064301757452</v>
       </c>
     </row>
     <row r="9">
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>8.218179902291242</v>
+        <v>8.220849820326881</v>
       </c>
     </row>
     <row r="10">
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>7.836770619901664</v>
+        <v>7.837917333184313</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>7.162722102583384</v>
+        <v>7.28780610133979</v>
       </c>
     </row>
     <row r="12">
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>7.310981061882006</v>
+        <v>7.210862258994188</v>
       </c>
     </row>
     <row r="13">
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
     </row>
     <row r="14">
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
     </row>
     <row r="15">
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>7.35339106782276</v>
+        <v>17.22696896356402</v>
       </c>
     </row>
     <row r="16">
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>7.583117327938817</v>
+        <v>7.270309372825452</v>
       </c>
     </row>
     <row r="17">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>7.242916983385382</v>
+        <v>7.270543615673769</v>
       </c>
     </row>
     <row r="18">
@@ -1177,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>7.242916983385382</v>
+        <v>7.270543615673769</v>
       </c>
     </row>
     <row r="19">
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>7.029415156162294</v>
+        <v>7.008973149808762</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>6.865852157295507</v>
+        <v>6.973157199438797</v>
       </c>
     </row>
     <row r="21">
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>11.25822716312403</v>
+        <v>9.490528308723993</v>
       </c>
     </row>
     <row r="22">
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>11.25822716312403</v>
+        <v>9.490528308723993</v>
       </c>
     </row>
     <row r="23">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>11.31967180213814</v>
+        <v>16.33017360615492</v>
       </c>
     </row>
     <row r="24">
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>11.31967180213814</v>
+        <v>16.33017360615492</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>9.340757367394243</v>
+        <v>15.63468266799135</v>
       </c>
     </row>
     <row r="26">
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>7.37504271750718</v>
+        <v>7.579439653571177</v>
       </c>
     </row>
     <row r="27">
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>7.00396769655076</v>
+        <v>6.847275900202534</v>
       </c>
     </row>
     <row r="28">
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>6.246385418365628</v>
+        <v>6.078693823559957</v>
       </c>
     </row>
     <row r="29">
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.961063861809979</v>
+        <v>5.078110712764101</v>
       </c>
     </row>
     <row r="30">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>4.810927717997912</v>
+        <v>4.893299108414093</v>
       </c>
     </row>
     <row r="31">
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.604746195129942</v>
+        <v>4.640810818294582</v>
       </c>
     </row>
     <row r="32">
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.604144266601407</v>
+        <v>4.582668950740796</v>
       </c>
     </row>
     <row r="33">
@@ -1792,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.604144266601407</v>
+        <v>4.582668950740796</v>
       </c>
     </row>
     <row r="34">
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>4.520964526493206</v>
+        <v>4.539974735294399</v>
       </c>
     </row>
     <row r="35">
@@ -1874,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>4.52056512164341</v>
+        <v>4.508379952304781</v>
       </c>
     </row>
     <row r="36">
@@ -1915,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>4.525642865811913</v>
+        <v>4.539328482298349</v>
       </c>
     </row>
     <row r="37">
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>4.604866533467261</v>
+        <v>4.625416128143794</v>
       </c>
     </row>
     <row r="38">
@@ -1997,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>4.652057169465017</v>
+        <v>4.625553249308343</v>
       </c>
     </row>
     <row r="39">
@@ -2038,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.652749876206823</v>
+        <v>4.672171250499557</v>
       </c>
     </row>
     <row r="40">
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>4.696696339864014</v>
+        <v>4.71888105633191</v>
       </c>
     </row>
     <row r="41">
@@ -2120,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.748860831718122</v>
+        <v>4.718982221702433</v>
       </c>
     </row>
     <row r="42">
@@ -2161,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>4.811573344793401</v>
+        <v>4.802381688602699</v>
       </c>
     </row>
     <row r="43">
@@ -2202,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>4.816660468128911</v>
+        <v>4.816018498115797</v>
       </c>
     </row>
     <row r="44">
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>4.814067453605086</v>
+        <v>4.816031047574088</v>
       </c>
     </row>
     <row r="45">
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>4.719044901501696</v>
+        <v>4.739298177006575</v>
       </c>
     </row>
     <row r="46">
@@ -2325,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>4.719044901501696</v>
+        <v>4.739298177006575</v>
       </c>
     </row>
     <row r="47">
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>4.690335297446286</v>
+        <v>4.689687245031716</v>
       </c>
     </row>
     <row r="48">
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>4.828542917916744</v>
+        <v>4.803318258879694</v>
       </c>
     </row>
     <row r="49">
@@ -2448,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>4.96164872873551</v>
+        <v>4.944164013392266</v>
       </c>
     </row>
     <row r="50">
@@ -2489,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>5.039110666438193</v>
+        <v>5.01709054456937</v>
       </c>
     </row>
     <row r="51">
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>5.074606316374426</v>
+        <v>5.070323380835259</v>
       </c>
     </row>
     <row r="52">
@@ -2571,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>5.065709663904308</v>
+        <v>5.070319322571292</v>
       </c>
     </row>
     <row r="53">
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>5.065709663904308</v>
+        <v>5.070319322571292</v>
       </c>
     </row>
     <row r="54">
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>5.054404024498178</v>
+        <v>5.059395884467778</v>
       </c>
     </row>
     <row r="55">
@@ -2694,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>5.039667093960332</v>
+        <v>5.025040183482493</v>
       </c>
     </row>
     <row r="56">
@@ -2735,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>5.039667093960332</v>
+        <v>5.025040183482493</v>
       </c>
     </row>
     <row r="57">
@@ -2776,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>4.903338995259718</v>
+        <v>4.899983972883373</v>
       </c>
     </row>
     <row r="58">
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>4.894737213849557</v>
+        <v>4.899944990099695</v>
       </c>
     </row>
     <row r="59">
@@ -2858,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>4.894640885829854</v>
+        <v>4.897716585716153</v>
       </c>
     </row>
     <row r="60">
@@ -2899,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>5.227704118554311</v>
+        <v>5.270982888112388</v>
       </c>
     </row>
     <row r="61">
@@ -2940,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>5.471537998053314</v>
+        <v>5.437688557207697</v>
       </c>
     </row>
     <row r="62">
@@ -2981,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>5.507123672228847</v>
+        <v>5.492502995708345</v>
       </c>
     </row>
     <row r="63">
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>5.518110861263691</v>
+        <v>5.521382290028781</v>
       </c>
     </row>
     <row r="64">
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>5.518110861263691</v>
+        <v>5.5096194815948</v>
       </c>
     </row>
     <row r="65">
@@ -3104,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>5.49335846138426</v>
+        <v>5.475858440602038</v>
       </c>
     </row>
     <row r="66">
@@ -3145,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>5.44725507868274</v>
+        <v>5.42861002879475</v>
       </c>
     </row>
     <row r="67">
@@ -3186,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>5.337330240029654</v>
+        <v>5.350175927538107</v>
       </c>
     </row>
     <row r="68">
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>5.272110875401731</v>
+        <v>5.288293697352125</v>
       </c>
     </row>
     <row r="69">
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>5.271395152924137</v>
+        <v>5.258576627449099</v>
       </c>
     </row>
     <row r="70">
@@ -3309,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>5.243135627754994</v>
+        <v>5.232855269546413</v>
       </c>
     </row>
     <row r="71">
@@ -3350,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>5.219658813463474</v>
+        <v>5.20419886643455</v>
       </c>
     </row>
     <row r="72">
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>5.219658813463474</v>
+        <v>5.20419886643455</v>
       </c>
     </row>
     <row r="73">
@@ -3432,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>5.17805189203108</v>
+        <v>5.204036538613784</v>
       </c>
     </row>
     <row r="74">
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>5.110164223168892</v>
+        <v>5.148056164184557</v>
       </c>
     </row>
     <row r="75">
@@ -3514,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>5.108337636734058</v>
+        <v>5.077589674143514</v>
       </c>
     </row>
     <row r="76">
@@ -3555,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>4.984118224760408</v>
+        <v>5.014590851412569</v>
       </c>
     </row>
     <row r="77">
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>4.982660549268322</v>
+        <v>4.955261043530146</v>
       </c>
     </row>
     <row r="78">
@@ -3637,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>4.919601068125682</v>
+        <v>4.895724950392556</v>
       </c>
     </row>
     <row r="79">
@@ -3678,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>4.888790180696684</v>
+        <v>4.878994738205914</v>
       </c>
     </row>
     <row r="80">
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>4.889922425709138</v>
+        <v>4.910858911511318</v>
       </c>
     </row>
     <row r="81">
@@ -3760,7 +3760,7 @@
         <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>5.068979998549168</v>
+        <v>5.092338927515219</v>
       </c>
     </row>
     <row r="82">
@@ -3801,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>5.2087856985976</v>
+        <v>5.224700115429861</v>
       </c>
     </row>
     <row r="83">
@@ -3842,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>5.2419450880851</v>
+        <v>5.224930814486805</v>
       </c>
     </row>
     <row r="84">
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>5.399676500771488</v>
+        <v>5.370654829342651</v>
       </c>
     </row>
     <row r="85">
@@ -3924,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="86">
@@ -3965,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="87">
@@ -4006,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="88">
@@ -4047,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="89">
@@ -4088,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="90">
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="91">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="92">
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="93">
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="94">
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>5.447998957898347</v>
+        <v>5.459725497657463</v>
       </c>
     </row>
     <row r="95">
@@ -4334,7 +4334,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>5.441091362290202</v>
+        <v>5.472004778938752</v>
       </c>
     </row>
     <row r="96">
@@ -4375,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>5.350149106817893</v>
+        <v>5.367137991270061</v>
       </c>
     </row>
     <row r="97">
@@ -4416,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>5.350149106817893</v>
+        <v>5.367137991270061</v>
       </c>
     </row>
     <row r="98">
@@ -4457,7 +4457,7 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>5.321137760810805</v>
+        <v>5.334687513112182</v>
       </c>
     </row>
     <row r="99">
@@ -4498,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>5.293142593572973</v>
+        <v>5.307429917425845</v>
       </c>
     </row>
     <row r="100">
@@ -4539,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>5.29220258959118</v>
+        <v>5.276660314023142</v>
       </c>
     </row>
     <row r="101">
@@ -4580,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>5.182799095741214</v>
+        <v>5.190458978713157</v>
       </c>
     </row>
     <row r="102">
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>5.184480786233429</v>
+        <v>5.178377032779323</v>
       </c>
     </row>
     <row r="103">
@@ -4662,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>5.261606117541525</v>
+        <v>5.274335099361529</v>
       </c>
     </row>
     <row r="104">
@@ -4703,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>5.281654855398788</v>
+        <v>5.282509576176824</v>
       </c>
     </row>
     <row r="105">
@@ -4744,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>5.274356776317311</v>
+        <v>5.279323913528716</v>
       </c>
     </row>
     <row r="106">
@@ -4785,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>5.273946144825915</v>
+        <v>5.265887217698685</v>
       </c>
     </row>
     <row r="107">
@@ -4826,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>5.255614022299906</v>
+        <v>5.265777154940177</v>
       </c>
     </row>
     <row r="108">
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>5.168052363573718</v>
+        <v>5.130949051644043</v>
       </c>
     </row>
     <row r="109">
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>4.978265744667874</v>
+        <v>5.03206763923099</v>
       </c>
     </row>
     <row r="110">
@@ -4949,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>4.857686321864007</v>
+        <v>4.805311375183411</v>
       </c>
     </row>
     <row r="111">
@@ -4990,7 +4990,7 @@
         <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>4.570408572191353</v>
+        <v>4.594725584768327</v>
       </c>
     </row>
     <row r="112">
@@ -5031,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>4.47667289145723</v>
+        <v>4.495669318259377</v>
       </c>
     </row>
     <row r="113">
@@ -5072,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>4.475535920170302</v>
+        <v>4.465137676597499</v>
       </c>
     </row>
     <row r="114">
@@ -5113,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>4.481449958104311</v>
+        <v>4.473702506001848</v>
       </c>
     </row>
     <row r="115">
@@ -5154,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="K115" t="n">
-        <v>4.48827868502149</v>
+        <v>4.486574491138813</v>
       </c>
     </row>
     <row r="116">
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>4.48827868502149</v>
+        <v>4.486574491138813</v>
       </c>
     </row>
     <row r="117">
@@ -5236,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>4.448927252778354</v>
+        <v>4.423583906831822</v>
       </c>
     </row>
     <row r="118">
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>4.390655537686455</v>
+        <v>4.423213841793482</v>
       </c>
     </row>
     <row r="119">
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>4.388062611826737</v>
+        <v>4.352346910329056</v>
       </c>
     </row>
     <row r="120">
@@ -5359,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>4.159196111622991</v>
+        <v>4.195586490922535</v>
       </c>
     </row>
     <row r="121">
@@ -5400,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>4.025915884462803</v>
+        <v>4.055642416475845</v>
       </c>
     </row>
     <row r="122">
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>3.955044089417568</v>
+        <v>3.918161151828539</v>
       </c>
     </row>
     <row r="123">
@@ -5482,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>3.879389486560219</v>
+        <v>3.855231851788348</v>
       </c>
     </row>
     <row r="124">
@@ -5523,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>3.720063683783769</v>
+        <v>3.749192884046315</v>
       </c>
     </row>
     <row r="125">
@@ -5564,7 +5564,7 @@
         <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>3.663142399112596</v>
+        <v>3.639398465110372</v>
       </c>
     </row>
     <row r="126">
@@ -5605,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>3.616880369179896</v>
+        <v>3.639079138886223</v>
       </c>
     </row>
     <row r="127">
@@ -5646,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="K127" t="n">
-        <v>3.483863781539523</v>
+        <v>3.525438025648213</v>
       </c>
     </row>
     <row r="128">
@@ -5687,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>3.272254965340389</v>
+        <v>3.22235703303638</v>
       </c>
     </row>
     <row r="129">
@@ -5728,7 +5728,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>3.163508701007812</v>
+        <v>3.115015882556881</v>
       </c>
     </row>
     <row r="130">
@@ -5769,7 +5769,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>2.897312546155748</v>
+        <v>2.880139197562468</v>
       </c>
     </row>
     <row r="131">
@@ -5810,7 +5810,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>2.897312546155748</v>
+        <v>2.880139197562468</v>
       </c>
     </row>
     <row r="132">
@@ -5851,7 +5851,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>2.86197877602613</v>
+        <v>2.879866559016563</v>
       </c>
     </row>
     <row r="133">
@@ -5892,7 +5892,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>2.86197877602613</v>
+        <v>2.879866559016563</v>
       </c>
     </row>
     <row r="134">
@@ -5933,7 +5933,7 @@
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>2.777572678505286</v>
+        <v>2.77017701567136</v>
       </c>
     </row>
     <row r="135">
@@ -5974,7 +5974,7 @@
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>3.105921000356857</v>
+        <v>3.158926216905006</v>
       </c>
     </row>
     <row r="136">
@@ -6015,7 +6015,7 @@
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>3.105921000356857</v>
+        <v>3.158926216905006</v>
       </c>
     </row>
     <row r="137">
@@ -6056,7 +6056,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>3.105921000356857</v>
+        <v>3.158926216905006</v>
       </c>
     </row>
     <row r="138">
@@ -6097,7 +6097,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>3.208083762654137</v>
+        <v>3.159710666679143</v>
       </c>
     </row>
     <row r="139">
@@ -6138,7 +6138,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>3.314667267949773</v>
+        <v>3.360664663973619</v>
       </c>
     </row>
     <row r="140">
@@ -6179,7 +6179,7 @@
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>3.40206481722016</v>
+        <v>3.361313307448213</v>
       </c>
     </row>
     <row r="141">
@@ -6220,7 +6220,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>3.720614311620269</v>
+        <v>3.66398637480461</v>
       </c>
     </row>
     <row r="142">
@@ -6261,7 +6261,7 @@
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>3.863251215112728</v>
+        <v>3.938967842243254</v>
       </c>
     </row>
     <row r="143">
@@ -6302,7 +6302,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>4.598825145385264</v>
+        <v>4.684620036630979</v>
       </c>
     </row>
     <row r="144">
@@ -6343,7 +6343,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>4.965709738323598</v>
+        <v>5.053572377677743</v>
       </c>
     </row>
     <row r="145">
@@ -6384,7 +6384,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>5.431995942669801</v>
+        <v>5.368967458869811</v>
       </c>
     </row>
     <row r="146">
@@ -6425,7 +6425,7 @@
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>5.438284597218944</v>
+        <v>5.500698107098984</v>
       </c>
     </row>
     <row r="147">
@@ -6466,7 +6466,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>5.569106366252102</v>
+        <v>5.632889883841238</v>
       </c>
     </row>
     <row r="148">
@@ -6507,7 +6507,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>5.693965434565409</v>
+        <v>5.633942007854012</v>
       </c>
     </row>
     <row r="149">
@@ -6548,7 +6548,7 @@
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>5.693965434565409</v>
+        <v>5.633942007854012</v>
       </c>
     </row>
     <row r="150">
@@ -6589,7 +6589,7 @@
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>5.957387896354917</v>
+        <v>6.013101904854868</v>
       </c>
     </row>
     <row r="151">
@@ -6630,7 +6630,7 @@
         <v>2</v>
       </c>
       <c r="K151" t="n">
-        <v>6.0632511406987</v>
+        <v>6.014010180212854</v>
       </c>
     </row>
     <row r="152">
@@ -6671,7 +6671,7 @@
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>6.278040427638199</v>
+        <v>6.251228566256218</v>
       </c>
     </row>
     <row r="153">
@@ -6712,7 +6712,7 @@
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>6.331158442464466</v>
+        <v>6.308953278439919</v>
       </c>
     </row>
     <row r="154">
@@ -6753,7 +6753,7 @@
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>6.33339832003768</v>
+        <v>6.354888057278446</v>
       </c>
     </row>
     <row r="155">
@@ -6794,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>6.374496999724887</v>
+        <v>6.394195543504178</v>
       </c>
     </row>
     <row r="156">
@@ -6835,7 +6835,7 @@
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>6.511712565723965</v>
+        <v>6.495789248596938</v>
       </c>
     </row>
     <row r="157">
@@ -6876,7 +6876,7 @@
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>6.511712565723965</v>
+        <v>6.495789248596938</v>
       </c>
     </row>
     <row r="158">
@@ -6917,7 +6917,7 @@
         <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>6.511712565723965</v>
+        <v>6.495789248596938</v>
       </c>
     </row>
     <row r="159">
@@ -6958,7 +6958,7 @@
         <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>6.598321683178505</v>
+        <v>6.58954460570865</v>
       </c>
     </row>
     <row r="160">
@@ -6999,7 +6999,7 @@
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>6.599548682223191</v>
+        <v>6.612881890672702</v>
       </c>
     </row>
     <row r="161">
@@ -7040,7 +7040,7 @@
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>6.61136411332074</v>
+        <v>6.613028745289984</v>
       </c>
     </row>
     <row r="162">
@@ -7081,7 +7081,7 @@
         <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>6.588846186423175</v>
+        <v>6.56029613691188</v>
       </c>
     </row>
     <row r="163">
@@ -7122,7 +7122,7 @@
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>6.448243618522249</v>
+        <v>6.379750009497984</v>
       </c>
     </row>
     <row r="164">
@@ -7163,7 +7163,7 @@
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>6.448243618522249</v>
+        <v>6.379750009497984</v>
       </c>
     </row>
     <row r="165">
@@ -7204,7 +7204,7 @@
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>6.276555442004401</v>
+        <v>6.287416845453978</v>
       </c>
     </row>
     <row r="166">
@@ -7245,7 +7245,7 @@
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>6.187751350891288</v>
+        <v>6.229377328733649</v>
       </c>
     </row>
     <row r="167">
@@ -7286,7 +7286,7 @@
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>6.187751350891288</v>
+        <v>6.229377328733649</v>
       </c>
     </row>
     <row r="168">
@@ -7327,7 +7327,7 @@
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>6.187751350891288</v>
+        <v>6.229377328733649</v>
       </c>
     </row>
     <row r="169">
@@ -7368,7 +7368,7 @@
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>5.968090253986067</v>
+        <v>6.015062046679968</v>
       </c>
     </row>
     <row r="170">
@@ -7409,7 +7409,7 @@
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>5.968090253986067</v>
+        <v>6.013992226620964</v>
       </c>
     </row>
     <row r="171">
@@ -7450,7 +7450,7 @@
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>5.962401649014894</v>
+        <v>5.902340605173209</v>
       </c>
     </row>
     <row r="172">
@@ -7491,7 +7491,7 @@
         <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>5.625522615893285</v>
+        <v>5.676432994654808</v>
       </c>
     </row>
     <row r="173">
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="K173" t="n">
-        <v>5.625522615893285</v>
+        <v>5.675379568932839</v>
       </c>
     </row>
     <row r="174">
@@ -7573,7 +7573,7 @@
         <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>5.625522615893285</v>
+        <v>5.675379568932839</v>
       </c>
     </row>
     <row r="175">
@@ -7614,7 +7614,7 @@
         <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>5.618642598431981</v>
+        <v>5.55167275080102</v>
       </c>
     </row>
     <row r="176">
@@ -7655,7 +7655,7 @@
         <v>2</v>
       </c>
       <c r="K176" t="n">
-        <v>5.48374073803944</v>
+        <v>5.424821561095598</v>
       </c>
     </row>
     <row r="177">
@@ -7696,7 +7696,7 @@
         <v>2</v>
       </c>
       <c r="K177" t="n">
-        <v>5.48374073803944</v>
+        <v>5.424821561095598</v>
       </c>
     </row>
     <row r="178">
@@ -7737,7 +7737,7 @@
         <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>5.261902283668141</v>
+        <v>5.308306754174406</v>
       </c>
     </row>
     <row r="179">
@@ -7778,7 +7778,7 @@
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>5.261902283668141</v>
+        <v>5.308306754174406</v>
       </c>
     </row>
     <row r="180">
@@ -7819,7 +7819,7 @@
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>5.256868421934375</v>
+        <v>5.209796074127928</v>
       </c>
     </row>
     <row r="181">
@@ -7860,7 +7860,7 @@
         <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>5.173479699263016</v>
+        <v>5.208983242580309</v>
       </c>
     </row>
     <row r="182">
@@ -7901,7 +7901,7 @@
         <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>5.16871136317628</v>
+        <v>5.124011728546912</v>
       </c>
     </row>
     <row r="183">
@@ -7942,7 +7942,7 @@
         <v>2</v>
       </c>
       <c r="K183" t="n">
-        <v>4.94467320691931</v>
+        <v>4.963158716313521</v>
       </c>
     </row>
     <row r="184">
@@ -7983,7 +7983,7 @@
         <v>2</v>
       </c>
       <c r="K184" t="n">
-        <v>4.942257118594265</v>
+        <v>4.916477608510247</v>
       </c>
     </row>
     <row r="185">
@@ -8024,7 +8024,7 @@
         <v>2</v>
       </c>
       <c r="K185" t="n">
-        <v>4.942257118594265</v>
+        <v>4.916477608510247</v>
       </c>
     </row>
     <row r="186">
@@ -8065,7 +8065,7 @@
         <v>2</v>
       </c>
       <c r="K186" t="n">
-        <v>4.898274204949511</v>
+        <v>4.916047102869229</v>
       </c>
     </row>
     <row r="187">
@@ -8106,7 +8106,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="n">
-        <v>4.898274204949511</v>
+        <v>4.916047102869229</v>
       </c>
     </row>
     <row r="188">
@@ -8147,7 +8147,7 @@
         <v>2</v>
       </c>
       <c r="K188" t="n">
-        <v>4.826177102010751</v>
+        <v>4.824188511134929</v>
       </c>
     </row>
     <row r="189">
@@ -8188,7 +8188,7 @@
         <v>2</v>
       </c>
       <c r="K189" t="n">
-        <v>4.814986343211633</v>
+        <v>4.811855865877853</v>
       </c>
     </row>
     <row r="190">
@@ -8229,7 +8229,7 @@
         <v>2</v>
       </c>
       <c r="K190" t="n">
-        <v>4.797564938606851</v>
+        <v>4.793091629040455</v>
       </c>
     </row>
     <row r="191">
@@ -8270,7 +8270,7 @@
         <v>2</v>
       </c>
       <c r="K191" t="n">
-        <v>4.794697441321851</v>
+        <v>4.793017019719676</v>
       </c>
     </row>
     <row r="192">
@@ -8311,7 +8311,7 @@
         <v>2</v>
       </c>
       <c r="K192" t="n">
-        <v>4.794697441321851</v>
+        <v>4.793017019719676</v>
       </c>
     </row>
     <row r="193">
@@ -8352,7 +8352,7 @@
         <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>4.737079268416625</v>
+        <v>4.741675656184414</v>
       </c>
     </row>
     <row r="194">
@@ -8393,7 +8393,7 @@
         <v>2</v>
       </c>
       <c r="K194" t="n">
-        <v>4.737079268416625</v>
+        <v>4.741675656184414</v>
       </c>
     </row>
     <row r="195">
@@ -8434,7 +8434,7 @@
         <v>2</v>
       </c>
       <c r="K195" t="n">
-        <v>4.724954951187553</v>
+        <v>4.725797888101858</v>
       </c>
     </row>
     <row r="196">
@@ -8475,7 +8475,7 @@
         <v>2</v>
       </c>
       <c r="K196" t="n">
-        <v>4.726859722683427</v>
+        <v>4.725821664604954</v>
       </c>
     </row>
     <row r="197">
@@ -8516,7 +8516,7 @@
         <v>2</v>
       </c>
       <c r="K197" t="n">
-        <v>4.729177276649879</v>
+        <v>4.722232269924745</v>
       </c>
     </row>
     <row r="198">
@@ -8557,7 +8557,7 @@
         <v>2</v>
       </c>
       <c r="K198" t="n">
-        <v>4.675958750136996</v>
+        <v>4.650701773062534</v>
       </c>
     </row>
     <row r="199">
@@ -8598,7 +8598,7 @@
         <v>2</v>
       </c>
       <c r="K199" t="n">
-        <v>4.624668674974948</v>
+        <v>4.650202384520832</v>
       </c>
     </row>
     <row r="200">
@@ -8639,7 +8639,7 @@
         <v>2</v>
       </c>
       <c r="K200" t="n">
-        <v>4.567298609375684</v>
+        <v>4.538509329690392</v>
       </c>
     </row>
     <row r="201">
@@ -8680,7 +8680,7 @@
         <v>2</v>
       </c>
       <c r="K201" t="n">
-        <v>4.515915213569598</v>
+        <v>4.537957960902179</v>
       </c>
     </row>
     <row r="202">
@@ -8721,7 +8721,7 @@
         <v>2</v>
       </c>
       <c r="K202" t="n">
-        <v>4.46402541828445</v>
+        <v>4.487705346350308</v>
       </c>
     </row>
     <row r="203">
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="K203" t="n">
-        <v>4.46402541828445</v>
+        <v>4.487705346350308</v>
       </c>
     </row>
     <row r="204">
@@ -8803,7 +8803,7 @@
         <v>2</v>
       </c>
       <c r="K204" t="n">
-        <v>4.46402541828445</v>
+        <v>4.487705346350308</v>
       </c>
     </row>
     <row r="205">
@@ -8844,7 +8844,7 @@
         <v>2</v>
       </c>
       <c r="K205" t="n">
-        <v>4.303009345775528</v>
+        <v>4.260075626246029</v>
       </c>
     </row>
     <row r="206">
@@ -8885,7 +8885,7 @@
         <v>2</v>
       </c>
       <c r="K206" t="n">
-        <v>4.22495659035648</v>
+        <v>4.259238237636114</v>
       </c>
     </row>
     <row r="207">
@@ -8926,7 +8926,7 @@
         <v>2</v>
       </c>
       <c r="K207" t="n">
-        <v>4.016251878796528</v>
+        <v>4.040412002836544</v>
       </c>
     </row>
     <row r="208">
@@ -8967,7 +8967,7 @@
         <v>2</v>
       </c>
       <c r="K208" t="n">
-        <v>4.016251878796528</v>
+        <v>4.040412002836544</v>
       </c>
     </row>
     <row r="209">
@@ -9008,7 +9008,7 @@
         <v>2</v>
       </c>
       <c r="K209" t="n">
-        <v>3.958532894978139</v>
+        <v>3.982476946955523</v>
       </c>
     </row>
     <row r="210">
@@ -9049,7 +9049,7 @@
         <v>2</v>
       </c>
       <c r="K210" t="n">
-        <v>3.807466580617577</v>
+        <v>3.776916445985304</v>
       </c>
     </row>
     <row r="211">
@@ -9090,7 +9090,7 @@
         <v>2</v>
       </c>
       <c r="K211" t="n">
-        <v>3.650102275673494</v>
+        <v>3.690809450264939</v>
       </c>
     </row>
     <row r="212">
@@ -9131,7 +9131,7 @@
         <v>2</v>
       </c>
       <c r="K212" t="n">
-        <v>3.429924988763214</v>
+        <v>3.477353593925336</v>
       </c>
     </row>
     <row r="213">
@@ -9172,7 +9172,7 @@
         <v>2</v>
       </c>
       <c r="K213" t="n">
-        <v>3.330474963041382</v>
+        <v>3.367764782785333</v>
       </c>
     </row>
     <row r="214">
@@ -9213,7 +9213,7 @@
         <v>2</v>
       </c>
       <c r="K214" t="n">
-        <v>3.169558168301719</v>
+        <v>3.131701722391127</v>
       </c>
     </row>
     <row r="215">
@@ -9254,7 +9254,7 @@
         <v>2</v>
       </c>
       <c r="K215" t="n">
-        <v>2.985057474354541</v>
+        <v>2.961096050293527</v>
       </c>
     </row>
     <row r="216">
@@ -9295,7 +9295,7 @@
         <v>2</v>
       </c>
       <c r="K216" t="n">
-        <v>2.940968310050378</v>
+        <v>2.960561032807758</v>
       </c>
     </row>
     <row r="217">
@@ -9336,7 +9336,7 @@
         <v>2</v>
       </c>
       <c r="K217" t="n">
-        <v>2.940968310050378</v>
+        <v>2.960561032807758</v>
       </c>
     </row>
     <row r="218">
@@ -9377,7 +9377,7 @@
         <v>2</v>
       </c>
       <c r="K218" t="n">
-        <v>2.851443090899801</v>
+        <v>2.844180552195906</v>
       </c>
     </row>
     <row r="219">
@@ -9418,7 +9418,7 @@
         <v>2</v>
       </c>
       <c r="K219" t="n">
-        <v>2.845670807942637</v>
+        <v>2.844127042632901</v>
       </c>
     </row>
     <row r="220">
@@ -9459,7 +9459,7 @@
         <v>2</v>
       </c>
       <c r="K220" t="n">
-        <v>2.867113795850832</v>
+        <v>2.856505556015017</v>
       </c>
     </row>
     <row r="221">
@@ -9500,7 +9500,7 @@
         <v>2</v>
       </c>
       <c r="K221" t="n">
-        <v>2.938893995496655</v>
+        <v>2.956935104163465</v>
       </c>
     </row>
     <row r="222">
@@ -9541,7 +9541,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="n">
-        <v>2.969078485441361</v>
+        <v>2.957293215673106</v>
       </c>
     </row>
     <row r="223">
@@ -9582,7 +9582,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="n">
-        <v>3.002244687587088</v>
+        <v>3.018409339680312</v>
       </c>
     </row>
     <row r="224">
@@ -9623,7 +9623,7 @@
         <v>2</v>
       </c>
       <c r="K224" t="n">
-        <v>3.062525075900084</v>
+        <v>3.050161770512292</v>
       </c>
     </row>
     <row r="225">
@@ -9664,7 +9664,7 @@
         <v>2</v>
       </c>
       <c r="K225" t="n">
-        <v>3.135601813749316</v>
+        <v>3.149712756420083</v>
       </c>
     </row>
     <row r="226">
@@ -9705,7 +9705,7 @@
         <v>2</v>
       </c>
       <c r="K226" t="n">
-        <v>3.177930662845831</v>
+        <v>3.171276597684044</v>
       </c>
     </row>
     <row r="227">
@@ -9746,7 +9746,7 @@
         <v>2</v>
       </c>
       <c r="K227" t="n">
-        <v>3.17889225180968</v>
+        <v>3.184804113587545</v>
       </c>
     </row>
     <row r="228">
@@ -9787,7 +9787,7 @@
         <v>2</v>
       </c>
       <c r="K228" t="n">
-        <v>3.151715080389572</v>
+        <v>3.145861642909809</v>
       </c>
     </row>
     <row r="229">
@@ -9828,7 +9828,7 @@
         <v>2</v>
       </c>
       <c r="K229" t="n">
-        <v>3.14031107926097</v>
+        <v>3.131307839186716</v>
       </c>
     </row>
     <row r="230">
@@ -9869,7 +9869,7 @@
         <v>2</v>
       </c>
       <c r="K230" t="n">
-        <v>3.14031107926097</v>
+        <v>3.131307839186716</v>
       </c>
     </row>
     <row r="231">
@@ -9910,7 +9910,7 @@
         <v>2</v>
       </c>
       <c r="K231" t="n">
-        <v>3.033140300212055</v>
+        <v>3.05732417364547</v>
       </c>
     </row>
     <row r="232">
@@ -9951,7 +9951,7 @@
         <v>2</v>
       </c>
       <c r="K232" t="n">
-        <v>2.968311100292726</v>
+        <v>2.992743918614478</v>
       </c>
     </row>
     <row r="233">
@@ -9992,7 +9992,7 @@
         <v>2</v>
       </c>
       <c r="K233" t="n">
-        <v>2.843726701817145</v>
+        <v>2.81666626255317</v>
       </c>
     </row>
     <row r="234">
@@ -10033,7 +10033,7 @@
         <v>2</v>
       </c>
       <c r="K234" t="n">
-        <v>2.791348310464368</v>
+        <v>2.761249658896045</v>
       </c>
     </row>
     <row r="235">
@@ -10074,7 +10074,7 @@
         <v>2</v>
       </c>
       <c r="K235" t="n">
-        <v>2.730300795632749</v>
+        <v>2.694721926922448</v>
       </c>
     </row>
     <row r="236">
@@ -10115,7 +10115,7 @@
         <v>2</v>
       </c>
       <c r="K236" t="n">
-        <v>2.61432654124052</v>
+        <v>2.603097030754232</v>
       </c>
     </row>
     <row r="237">
@@ -10156,7 +10156,7 @@
         <v>2</v>
       </c>
       <c r="K237" t="n">
-        <v>2.598344416882548</v>
+        <v>2.597538187048621</v>
       </c>
     </row>
     <row r="238">
@@ -10197,7 +10197,7 @@
         <v>2</v>
       </c>
       <c r="K238" t="n">
-        <v>2.595497597082085</v>
+        <v>2.589086796692909</v>
       </c>
     </row>
     <row r="239">
@@ -10238,7 +10238,7 @@
         <v>2</v>
       </c>
       <c r="K239" t="n">
-        <v>2.583829018613124</v>
+        <v>2.579163836690785</v>
       </c>
     </row>
     <row r="240">
@@ -10279,7 +10279,7 @@
         <v>2</v>
       </c>
       <c r="K240" t="n">
-        <v>2.59189536848193</v>
+        <v>2.591028911133469</v>
       </c>
     </row>
     <row r="241">
@@ -10320,7 +10320,7 @@
         <v>2</v>
       </c>
       <c r="K241" t="n">
-        <v>2.589407019765873</v>
+        <v>2.590974365682108</v>
       </c>
     </row>
     <row r="242">
@@ -10361,7 +10361,7 @@
         <v>2</v>
       </c>
       <c r="K242" t="n">
-        <v>2.589687907277124</v>
+        <v>2.594609211340158</v>
       </c>
     </row>
     <row r="243">
@@ -10402,7 +10402,7 @@
         <v>2</v>
       </c>
       <c r="K243" t="n">
-        <v>2.612943531877011</v>
+        <v>2.607727181128883</v>
       </c>
     </row>
     <row r="244">
@@ -10443,7 +10443,7 @@
         <v>2</v>
       </c>
       <c r="K244" t="n">
-        <v>2.652526773658721</v>
+        <v>2.654293968856617</v>
       </c>
     </row>
     <row r="245">
@@ -10484,7 +10484,7 @@
         <v>2</v>
       </c>
       <c r="K245" t="n">
-        <v>2.653387069045559</v>
+        <v>2.648985107217981</v>
       </c>
     </row>
     <row r="246">
@@ -10525,7 +10525,7 @@
         <v>2</v>
       </c>
       <c r="K246" t="n">
-        <v>2.603708822001785</v>
+        <v>2.592350508499896</v>
       </c>
     </row>
     <row r="247">
@@ -10566,7 +10566,7 @@
         <v>2</v>
       </c>
       <c r="K247" t="n">
-        <v>2.58124486085573</v>
+        <v>2.592350508499896</v>
       </c>
     </row>
     <row r="248">
@@ -10607,7 +10607,7 @@
         <v>2</v>
       </c>
       <c r="K248" t="n">
-        <v>2.58124486085573</v>
+        <v>2.592005442207908</v>
       </c>
     </row>
     <row r="249">
@@ -10648,7 +10648,7 @@
         <v>2</v>
       </c>
       <c r="K249" t="n">
-        <v>2.394174116912976</v>
+        <v>2.360510347336178</v>
       </c>
     </row>
     <row r="250">
@@ -10689,7 +10689,7 @@
         <v>2</v>
       </c>
       <c r="K250" t="n">
-        <v>2.323527404257891</v>
+        <v>2.359571769645778</v>
       </c>
     </row>
     <row r="251">
@@ -10730,7 +10730,7 @@
         <v>2</v>
       </c>
       <c r="K251" t="n">
-        <v>2.323527404257891</v>
+        <v>2.283645915497759</v>
       </c>
     </row>
     <row r="252">
@@ -10771,7 +10771,7 @@
         <v>2</v>
       </c>
       <c r="K252" t="n">
-        <v>2.323527404257891</v>
+        <v>2.283645915497759</v>
       </c>
     </row>
     <row r="253">
@@ -10812,7 +10812,7 @@
         <v>2</v>
       </c>
       <c r="K253" t="n">
-        <v>2.178512263367727</v>
+        <v>2.203448610295183</v>
       </c>
     </row>
     <row r="254">
@@ -10853,7 +10853,7 @@
         <v>2</v>
       </c>
       <c r="K254" t="n">
-        <v>2.107295626771773</v>
+        <v>2.132053924832972</v>
       </c>
     </row>
     <row r="255">
@@ -10894,7 +10894,7 @@
         <v>2</v>
       </c>
       <c r="K255" t="n">
-        <v>1.987483692471464</v>
+        <v>2.005220836644964</v>
       </c>
     </row>
     <row r="256">
@@ -10935,7 +10935,7 @@
         <v>2</v>
       </c>
       <c r="K256" t="n">
-        <v>1.932824086218656</v>
+        <v>1.927133620867814</v>
       </c>
     </row>
     <row r="257">
@@ -10976,7 +10976,7 @@
         <v>2</v>
       </c>
       <c r="K257" t="n">
-        <v>1.923623634721696</v>
+        <v>1.927133620867814</v>
       </c>
     </row>
     <row r="258">
@@ -11017,7 +11017,7 @@
         <v>2</v>
       </c>
       <c r="K258" t="n">
-        <v>1.957517531078011</v>
+        <v>1.947097006381363</v>
       </c>
     </row>
     <row r="259">
@@ -11058,7 +11058,7 @@
         <v>2</v>
       </c>
       <c r="K259" t="n">
-        <v>1.95965017891482</v>
+        <v>1.947097006381363</v>
       </c>
     </row>
     <row r="260">
@@ -11099,7 +11099,7 @@
         <v>2</v>
       </c>
       <c r="K260" t="n">
-        <v>1.983190562722504</v>
+        <v>1.9731527391432</v>
       </c>
     </row>
     <row r="261">
@@ -11140,7 +11140,7 @@
         <v>2</v>
       </c>
       <c r="K261" t="n">
-        <v>1.985341968832413</v>
+        <v>1.99984082582976</v>
       </c>
     </row>
     <row r="262">
@@ -11181,7 +11181,7 @@
         <v>2</v>
       </c>
       <c r="K262" t="n">
-        <v>2.076671745171828</v>
+        <v>2.089680018378422</v>
       </c>
     </row>
     <row r="263">
@@ -11222,7 +11222,7 @@
         <v>2</v>
       </c>
       <c r="K263" t="n">
-        <v>2.076671745171828</v>
+        <v>2.089680018378422</v>
       </c>
     </row>
     <row r="264">
@@ -11263,7 +11263,7 @@
         <v>2</v>
       </c>
       <c r="K264" t="n">
-        <v>2.076671745171828</v>
+        <v>2.089680018378422</v>
       </c>
     </row>
     <row r="265">
@@ -11304,7 +11304,7 @@
         <v>2</v>
       </c>
       <c r="K265" t="n">
-        <v>2.076671745171828</v>
+        <v>2.089680018378422</v>
       </c>
     </row>
     <row r="266">
@@ -11345,7 +11345,7 @@
         <v>2</v>
       </c>
       <c r="K266" t="n">
-        <v>2.103609451171724</v>
+        <v>2.12657170631664</v>
       </c>
     </row>
     <row r="267">
@@ -11386,7 +11386,7 @@
         <v>2</v>
       </c>
       <c r="K267" t="n">
-        <v>2.207109187052492</v>
+        <v>2.234826934113172</v>
       </c>
     </row>
     <row r="268">
@@ -11427,7 +11427,7 @@
         <v>2</v>
       </c>
       <c r="K268" t="n">
-        <v>2.365192607018854</v>
+        <v>2.345602638848604</v>
       </c>
     </row>
     <row r="269">
@@ -11468,7 +11468,7 @@
         <v>2</v>
       </c>
       <c r="K269" t="n">
-        <v>2.435866690199535</v>
+        <v>2.427859323671435</v>
       </c>
     </row>
     <row r="270">
@@ -11509,7 +11509,7 @@
         <v>2</v>
       </c>
       <c r="K270" t="n">
-        <v>2.425409032074808</v>
+        <v>2.433171408789176</v>
       </c>
     </row>
     <row r="271">
@@ -11550,7 +11550,7 @@
         <v>2</v>
       </c>
       <c r="K271" t="n">
-        <v>2.396543736374894</v>
+        <v>2.374189130713043</v>
       </c>
     </row>
     <row r="272">
@@ -11591,7 +11591,7 @@
         <v>2</v>
       </c>
       <c r="K272" t="n">
-        <v>2.350263467785271</v>
+        <v>2.373481002268754</v>
       </c>
     </row>
     <row r="273">
@@ -11632,7 +11632,7 @@
         <v>2</v>
       </c>
       <c r="K273" t="n">
-        <v>2.129465962429183</v>
+        <v>2.064640075608685</v>
       </c>
     </row>
     <row r="274">
@@ -11673,7 +11673,7 @@
         <v>2</v>
       </c>
       <c r="K274" t="n">
-        <v>2.129465962429183</v>
+        <v>2.064640075608685</v>
       </c>
     </row>
     <row r="275">
@@ -11714,7 +11714,7 @@
         <v>2</v>
       </c>
       <c r="K275" t="n">
-        <v>2.004075915674061</v>
+        <v>1.945059613322375</v>
       </c>
     </row>
     <row r="276">
@@ -11755,7 +11755,7 @@
         <v>2</v>
       </c>
       <c r="K276" t="n">
-        <v>1.625975143562268</v>
+        <v>1.649168749114154</v>
       </c>
     </row>
     <row r="277">
@@ -11796,7 +11796,7 @@
         <v>2</v>
       </c>
       <c r="K277" t="n">
-        <v>1.570960415991205</v>
+        <v>1.590045760526336</v>
       </c>
     </row>
     <row r="278">
@@ -11837,7 +11837,7 @@
         <v>2</v>
       </c>
       <c r="K278" t="n">
-        <v>1.524866571415489</v>
+        <v>1.508845728796601</v>
       </c>
     </row>
     <row r="279">
@@ -11878,7 +11878,7 @@
         <v>2</v>
       </c>
       <c r="K279" t="n">
-        <v>1.488686264258009</v>
+        <v>1.490853952590325</v>
       </c>
     </row>
     <row r="280">
@@ -11919,7 +11919,7 @@
         <v>2</v>
       </c>
       <c r="K280" t="n">
-        <v>1.497804894034293</v>
+        <v>1.507547901184912</v>
       </c>
     </row>
     <row r="281">
@@ -11960,7 +11960,7 @@
         <v>2</v>
       </c>
       <c r="K281" t="n">
-        <v>1.579994554165848</v>
+        <v>1.563124829323313</v>
       </c>
     </row>
     <row r="282">
@@ -12001,7 +12001,7 @@
         <v>2</v>
       </c>
       <c r="K282" t="n">
-        <v>1.590866122184887</v>
+        <v>1.591658341694528</v>
       </c>
     </row>
     <row r="283">
@@ -12042,7 +12042,7 @@
         <v>2</v>
       </c>
       <c r="K283" t="n">
-        <v>1.58925863011308</v>
+        <v>1.564006151563562</v>
       </c>
     </row>
     <row r="284">
@@ -12083,7 +12083,7 @@
         <v>2</v>
       </c>
       <c r="K284" t="n">
-        <v>1.529737080909861</v>
+        <v>1.556331506783077</v>
       </c>
     </row>
     <row r="285">
@@ -12124,7 +12124,7 @@
         <v>2</v>
       </c>
       <c r="K285" t="n">
-        <v>1.577381506298685</v>
+        <v>1.557144168040907</v>
       </c>
     </row>
     <row r="286">
@@ -12165,7 +12165,7 @@
         <v>2</v>
       </c>
       <c r="K286" t="n">
-        <v>1.583267166688227</v>
+        <v>1.625708875797123</v>
       </c>
     </row>
     <row r="287">
@@ -12206,7 +12206,7 @@
         <v>2</v>
       </c>
       <c r="K287" t="n">
-        <v>1.583267166688227</v>
+        <v>1.625708875797123</v>
       </c>
     </row>
     <row r="288">
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>1.851146747346766</v>
+        <v>1.815447844895817</v>
       </c>
     </row>
     <row r="289">
@@ -12288,7 +12288,7 @@
         <v>2</v>
       </c>
       <c r="K289" t="n">
-        <v>1.851146747346766</v>
+        <v>1.815447844895817</v>
       </c>
     </row>
     <row r="290">
@@ -12329,7 +12329,7 @@
         <v>2</v>
       </c>
       <c r="K290" t="n">
-        <v>2.041712023511712</v>
+        <v>2.028241141662841</v>
       </c>
     </row>
     <row r="291">
@@ -12370,7 +12370,7 @@
         <v>2</v>
       </c>
       <c r="K291" t="n">
-        <v>2.07079530130531</v>
+        <v>2.079136566814629</v>
       </c>
     </row>
     <row r="292">
@@ -12411,7 +12411,7 @@
         <v>2</v>
       </c>
       <c r="K292" t="n">
-        <v>2.083321248488577</v>
+        <v>2.077761276555842</v>
       </c>
     </row>
     <row r="293">
@@ -12452,7 +12452,7 @@
         <v>2</v>
       </c>
       <c r="K293" t="n">
-        <v>2.055674428269336</v>
+        <v>2.061375519128817</v>
       </c>
     </row>
     <row r="294">
@@ -12493,7 +12493,7 @@
         <v>2</v>
       </c>
       <c r="K294" t="n">
-        <v>2.055674428269336</v>
+        <v>2.061129401343041</v>
       </c>
     </row>
     <row r="295">
@@ -12534,7 +12534,7 @@
         <v>2</v>
       </c>
       <c r="K295" t="n">
-        <v>2.055674428269336</v>
+        <v>2.061129401343041</v>
       </c>
     </row>
     <row r="296">
@@ -12575,7 +12575,7 @@
         <v>2</v>
       </c>
       <c r="K296" t="n">
-        <v>2.047996450400295</v>
+        <v>2.051335729955625</v>
       </c>
     </row>
     <row r="297">
@@ -12616,7 +12616,7 @@
         <v>2</v>
       </c>
       <c r="K297" t="n">
-        <v>2.116974228969603</v>
+        <v>2.10456636868157</v>
       </c>
     </row>
     <row r="298">
@@ -12657,7 +12657,7 @@
         <v>2</v>
       </c>
       <c r="K298" t="n">
-        <v>2.147156255293087</v>
+        <v>2.171043288205575</v>
       </c>
     </row>
     <row r="299">
@@ -12698,7 +12698,7 @@
         <v>2</v>
       </c>
       <c r="K299" t="n">
-        <v>2.323137655304029</v>
+        <v>2.300325478151882</v>
       </c>
     </row>
     <row r="300">
@@ -12739,7 +12739,7 @@
         <v>2</v>
       </c>
       <c r="K300" t="n">
-        <v>2.329056026964639</v>
+        <v>2.363001519048092</v>
       </c>
     </row>
     <row r="301">
@@ -12780,7 +12780,7 @@
         <v>2</v>
       </c>
       <c r="K301" t="n">
-        <v>2.685241237967792</v>
+        <v>2.647672711769677</v>
       </c>
     </row>
     <row r="302">
@@ -12821,7 +12821,7 @@
         <v>2</v>
       </c>
       <c r="K302" t="n">
-        <v>2.695146953387487</v>
+        <v>2.647672711769677</v>
       </c>
     </row>
     <row r="303">
@@ -12862,7 +12862,7 @@
         <v>2</v>
       </c>
       <c r="K303" t="n">
-        <v>3.011581810556982</v>
+        <v>3.013390555588016</v>
       </c>
     </row>
     <row r="304">
@@ -12903,7 +12903,7 @@
         <v>2</v>
       </c>
       <c r="K304" t="n">
-        <v>3.011581810556982</v>
+        <v>3.013390555588016</v>
       </c>
     </row>
     <row r="305">
@@ -12944,7 +12944,7 @@
         <v>2</v>
       </c>
       <c r="K305" t="n">
-        <v>2.994110865192332</v>
+        <v>2.977324496580792</v>
       </c>
     </row>
     <row r="306">
@@ -12985,7 +12985,7 @@
         <v>2</v>
       </c>
       <c r="K306" t="n">
-        <v>2.87321663544604</v>
+        <v>2.887216623420684</v>
       </c>
     </row>
     <row r="307">
@@ -13026,7 +13026,7 @@
         <v>2</v>
       </c>
       <c r="K307" t="n">
-        <v>2.827988175400171</v>
+        <v>2.834417595436259</v>
       </c>
     </row>
     <row r="308">
@@ -13067,7 +13067,7 @@
         <v>2</v>
       </c>
       <c r="K308" t="n">
-        <v>2.825759508280099</v>
+        <v>2.834417595436259</v>
       </c>
     </row>
     <row r="309">
@@ -13108,7 +13108,7 @@
         <v>2</v>
       </c>
       <c r="K309" t="n">
-        <v>2.79583204026963</v>
+        <v>2.798397998462547</v>
       </c>
     </row>
     <row r="310">
@@ -13149,7 +13149,7 @@
         <v>2</v>
       </c>
       <c r="K310" t="n">
-        <v>2.802735030441299</v>
+        <v>2.797172048861603</v>
       </c>
     </row>
     <row r="311">
@@ -13190,7 +13190,7 @@
         <v>2</v>
       </c>
       <c r="K311" t="n">
-        <v>3.107462356651375</v>
+        <v>3.068630262205844</v>
       </c>
     </row>
     <row r="312">
@@ -13231,7 +13231,7 @@
         <v>2</v>
       </c>
       <c r="K312" t="n">
-        <v>3.107462356651375</v>
+        <v>3.070295826940626</v>
       </c>
     </row>
     <row r="313">
@@ -13272,7 +13272,7 @@
         <v>2</v>
       </c>
       <c r="K313" t="n">
-        <v>3.118220316946035</v>
+        <v>3.070295826940626</v>
       </c>
     </row>
     <row r="314">
@@ -13313,7 +13313,7 @@
         <v>2</v>
       </c>
       <c r="K314" t="n">
-        <v>3.334659903431462</v>
+        <v>3.386753331054442</v>
       </c>
     </row>
     <row r="315">
@@ -13354,7 +13354,7 @@
         <v>2</v>
       </c>
       <c r="K315" t="n">
-        <v>3.551931890928346</v>
+        <v>3.537172678616645</v>
       </c>
     </row>
     <row r="316">
@@ -13395,7 +13395,7 @@
         <v>2</v>
       </c>
       <c r="K316" t="n">
-        <v>3.561210762418601</v>
+        <v>3.556937424388053</v>
       </c>
     </row>
     <row r="317">
@@ -13436,7 +13436,7 @@
         <v>2</v>
       </c>
       <c r="K317" t="n">
-        <v>3.561210762418601</v>
+        <v>3.556937424388053</v>
       </c>
     </row>
     <row r="318">
@@ -13477,7 +13477,7 @@
         <v>2</v>
       </c>
       <c r="K318" t="n">
-        <v>3.443396611788092</v>
+        <v>3.400905321031463</v>
       </c>
     </row>
     <row r="319">
@@ -13518,7 +13518,7 @@
         <v>2</v>
       </c>
       <c r="K319" t="n">
-        <v>3.443396611788092</v>
+        <v>3.400905321031463</v>
       </c>
     </row>
     <row r="320">
@@ -13559,7 +13559,7 @@
         <v>2</v>
       </c>
       <c r="K320" t="n">
-        <v>3.443396611788092</v>
+        <v>3.400905321031463</v>
       </c>
     </row>
     <row r="321">
@@ -13600,7 +13600,7 @@
         <v>2</v>
       </c>
       <c r="K321" t="n">
-        <v>3.274698364995402</v>
+        <v>3.309812526109261</v>
       </c>
     </row>
     <row r="322">
@@ -13641,7 +13641,7 @@
         <v>2</v>
       </c>
       <c r="K322" t="n">
-        <v>3.264246930979694</v>
+        <v>3.20409210004554</v>
       </c>
     </row>
     <row r="323">
@@ -13682,7 +13682,7 @@
         <v>2</v>
       </c>
       <c r="K323" t="n">
-        <v>2.835115915339944</v>
+        <v>2.740216867872284</v>
       </c>
     </row>
     <row r="324">
@@ -13723,7 +13723,7 @@
         <v>2</v>
       </c>
       <c r="K324" t="n">
-        <v>2.682210342487319</v>
+        <v>2.737362784243723</v>
       </c>
     </row>
     <row r="325">
@@ -13764,7 +13764,7 @@
         <v>2</v>
       </c>
       <c r="K325" t="n">
-        <v>2.510223013898961</v>
+        <v>2.565831730419513</v>
       </c>
     </row>
     <row r="326">
@@ -13805,7 +13805,7 @@
         <v>2</v>
       </c>
       <c r="K326" t="n">
-        <v>2.510223013898961</v>
+        <v>2.565831730419513</v>
       </c>
     </row>
     <row r="327">
@@ -13846,7 +13846,7 @@
         <v>2</v>
       </c>
       <c r="K327" t="n">
-        <v>2.179595404042975</v>
+        <v>2.242509320629229</v>
       </c>
     </row>
     <row r="328">
@@ -13887,7 +13887,7 @@
         <v>2</v>
       </c>
       <c r="K328" t="n">
-        <v>2.179595404042975</v>
+        <v>2.242509320629229</v>
       </c>
     </row>
     <row r="329">
@@ -13928,7 +13928,7 @@
         <v>2</v>
       </c>
       <c r="K329" t="n">
-        <v>2.02957950664275</v>
+        <v>1.949951939924804</v>
       </c>
     </row>
     <row r="330">
@@ -13969,7 +13969,7 @@
         <v>2</v>
       </c>
       <c r="K330" t="n">
-        <v>1.806605692162661</v>
+        <v>1.839566450892908</v>
       </c>
     </row>
     <row r="331">
@@ -14010,7 +14010,7 @@
         <v>2</v>
       </c>
       <c r="K331" t="n">
-        <v>1.710193047933979</v>
+        <v>1.744037387657952</v>
       </c>
     </row>
     <row r="332">
@@ -14051,7 +14051,7 @@
         <v>2</v>
       </c>
       <c r="K332" t="n">
-        <v>1.647682429716306</v>
+        <v>1.67056012984967</v>
       </c>
     </row>
     <row r="333">
@@ -14092,7 +14092,7 @@
         <v>2</v>
       </c>
       <c r="K333" t="n">
-        <v>1.583792832529507</v>
+        <v>1.60275812448503</v>
       </c>
     </row>
     <row r="334">
@@ -14133,7 +14133,7 @@
         <v>2</v>
       </c>
       <c r="K334" t="n">
-        <v>1.578009875877034</v>
+        <v>1.551028494952821</v>
       </c>
     </row>
     <row r="335">
@@ -14174,7 +14174,7 @@
         <v>2</v>
       </c>
       <c r="K335" t="n">
-        <v>1.537359691172308</v>
+        <v>1.531263266012064</v>
       </c>
     </row>
     <row r="336">
@@ -14215,7 +14215,7 @@
         <v>2</v>
       </c>
       <c r="K336" t="n">
-        <v>1.67174808184305</v>
+        <v>1.643013891764543</v>
       </c>
     </row>
     <row r="337">
@@ -14256,7 +14256,7 @@
         <v>2</v>
       </c>
       <c r="K337" t="n">
-        <v>1.67174808184305</v>
+        <v>1.644468377961135</v>
       </c>
     </row>
     <row r="338">
@@ -14297,7 +14297,7 @@
         <v>2</v>
       </c>
       <c r="K338" t="n">
-        <v>1.67174808184305</v>
+        <v>1.644468377961135</v>
       </c>
     </row>
     <row r="339">
@@ -14338,7 +14338,7 @@
         <v>2</v>
       </c>
       <c r="K339" t="n">
-        <v>1.839021882331904</v>
+        <v>1.81134337093881</v>
       </c>
     </row>
     <row r="340">
@@ -14379,7 +14379,7 @@
         <v>2</v>
       </c>
       <c r="K340" t="n">
-        <v>1.839021882331904</v>
+        <v>1.812795043742264</v>
       </c>
     </row>
     <row r="341">
@@ -14420,7 +14420,7 @@
         <v>2</v>
       </c>
       <c r="K341" t="n">
-        <v>1.970393288605207</v>
+        <v>1.996995252351959</v>
       </c>
     </row>
     <row r="342">
@@ -14461,7 +14461,7 @@
         <v>2</v>
       </c>
       <c r="K342" t="n">
-        <v>1.970393288605207</v>
+        <v>1.996995252351959</v>
       </c>
     </row>
     <row r="343">
@@ -14502,7 +14502,7 @@
         <v>2</v>
       </c>
       <c r="K343" t="n">
-        <v>2.051132064713035</v>
+        <v>2.039943795015625</v>
       </c>
     </row>
     <row r="344">
@@ -14543,7 +14543,7 @@
         <v>2</v>
       </c>
       <c r="K344" t="n">
-        <v>2.082241251394405</v>
+        <v>2.084369519722634</v>
       </c>
     </row>
     <row r="345">
@@ -14584,7 +14584,7 @@
         <v>2</v>
       </c>
       <c r="K345" t="n">
-        <v>2.069344040356683</v>
+        <v>2.074856813454626</v>
       </c>
     </row>
     <row r="346">
@@ -14625,7 +14625,7 @@
         <v>2</v>
       </c>
       <c r="K346" t="n">
-        <v>2.069344040356683</v>
+        <v>2.074856813454626</v>
       </c>
     </row>
     <row r="347">
@@ -14666,7 +14666,7 @@
         <v>2</v>
       </c>
       <c r="K347" t="n">
-        <v>1.88896439373089</v>
+        <v>1.914436832883101</v>
       </c>
     </row>
     <row r="348">
@@ -14707,7 +14707,7 @@
         <v>2</v>
       </c>
       <c r="K348" t="n">
-        <v>1.737308038584745</v>
+        <v>1.687567619243136</v>
       </c>
     </row>
     <row r="349">
@@ -14748,7 +14748,7 @@
         <v>2</v>
       </c>
       <c r="K349" t="n">
-        <v>1.55804413722387</v>
+        <v>1.591015466972437</v>
       </c>
     </row>
     <row r="350">
@@ -14789,7 +14789,7 @@
         <v>2</v>
       </c>
       <c r="K350" t="n">
-        <v>1.546199783804783</v>
+        <v>1.481931392871862</v>
       </c>
     </row>
     <row r="351">
@@ -14830,7 +14830,7 @@
         <v>2</v>
       </c>
       <c r="K351" t="n">
-        <v>1.114379929383587</v>
+        <v>1.144241640115339</v>
       </c>
     </row>
     <row r="352">
@@ -14871,7 +14871,7 @@
         <v>2</v>
       </c>
       <c r="K352" t="n">
-        <v>1.114379929383587</v>
+        <v>1.142523848088314</v>
       </c>
     </row>
     <row r="353">
@@ -14912,7 +14912,7 @@
         <v>2</v>
       </c>
       <c r="K353" t="n">
-        <v>0.8896705009585302</v>
+        <v>0.9094495344556303</v>
       </c>
     </row>
     <row r="354">
@@ -14953,7 +14953,7 @@
         <v>2</v>
       </c>
       <c r="K354" t="n">
-        <v>0.8896705009585302</v>
+        <v>0.9094495344556303</v>
       </c>
     </row>
     <row r="355">
@@ -14994,7 +14994,7 @@
         <v>2</v>
       </c>
       <c r="K355" t="n">
-        <v>0.8896705009585302</v>
+        <v>0.9094495344556303</v>
       </c>
     </row>
     <row r="356">
@@ -15035,7 +15035,7 @@
         <v>2</v>
       </c>
       <c r="K356" t="n">
-        <v>0.8829607995543933</v>
+        <v>0.8518089074691501</v>
       </c>
     </row>
     <row r="357">
@@ -15076,7 +15076,7 @@
         <v>2</v>
       </c>
       <c r="K357" t="n">
-        <v>0.8363701103621043</v>
+        <v>0.8509105544496371</v>
       </c>
     </row>
     <row r="358">
@@ -15117,7 +15117,7 @@
         <v>2</v>
       </c>
       <c r="K358" t="n">
-        <v>0.7542362999802886</v>
+        <v>0.760553938754903</v>
       </c>
     </row>
     <row r="359">
@@ -15158,7 +15158,7 @@
         <v>2</v>
       </c>
       <c r="K359" t="n">
-        <v>0.7652953380169926</v>
+        <v>0.7608305282425646</v>
       </c>
     </row>
     <row r="360">
@@ -15199,7 +15199,7 @@
         <v>2</v>
       </c>
       <c r="K360" t="n">
-        <v>0.7879041622875256</v>
+        <v>0.785209543327506</v>
       </c>
     </row>
     <row r="361">
@@ -15240,7 +15240,7 @@
         <v>2</v>
       </c>
       <c r="K361" t="n">
-        <v>0.7948381054118256</v>
+        <v>0.7929662925061476</v>
       </c>
     </row>
     <row r="362">
@@ -15281,7 +15281,7 @@
         <v>2</v>
       </c>
       <c r="K362" t="n">
-        <v>0.8008270198686489</v>
+        <v>0.8101019346377301</v>
       </c>
     </row>
     <row r="363">
@@ -15322,7 +15322,7 @@
         <v>2</v>
       </c>
       <c r="K363" t="n">
-        <v>0.8008270198686489</v>
+        <v>0.8101019346377301</v>
       </c>
     </row>
     <row r="364">
@@ -15363,7 +15363,7 @@
         <v>2</v>
       </c>
       <c r="K364" t="n">
-        <v>0.9071142730898115</v>
+        <v>0.8980486956782454</v>
       </c>
     </row>
     <row r="365">
@@ -15404,7 +15404,7 @@
         <v>2</v>
       </c>
       <c r="K365" t="n">
-        <v>0.9371962548521828</v>
+        <v>0.9281875202663622</v>
       </c>
     </row>
     <row r="366">
@@ -15445,7 +15445,7 @@
         <v>2</v>
       </c>
       <c r="K366" t="n">
-        <v>0.9806302346185736</v>
+        <v>0.9654707043051051</v>
       </c>
     </row>
     <row r="367">
@@ -15486,7 +15486,7 @@
         <v>2</v>
       </c>
       <c r="K367" t="n">
-        <v>1.18993105406857</v>
+        <v>1.258361856401009</v>
       </c>
     </row>
     <row r="368">
@@ -15527,7 +15527,7 @@
         <v>2</v>
       </c>
       <c r="K368" t="n">
-        <v>1.535397801819967</v>
+        <v>1.496685612555984</v>
       </c>
     </row>
     <row r="369">
@@ -15568,7 +15568,7 @@
         <v>2</v>
       </c>
       <c r="K369" t="n">
-        <v>1.535397801819967</v>
+        <v>1.496685612555984</v>
       </c>
     </row>
     <row r="370">
@@ -15609,7 +15609,7 @@
         <v>2</v>
       </c>
       <c r="K370" t="n">
-        <v>1.553875391696069</v>
+        <v>1.498924711948705</v>
       </c>
     </row>
     <row r="371">
@@ -15650,7 +15650,7 @@
         <v>2</v>
       </c>
       <c r="K371" t="n">
-        <v>2.411414902595833</v>
+        <v>2.373001547544835</v>
       </c>
     </row>
     <row r="372">
@@ -15691,7 +15691,7 @@
         <v>2</v>
       </c>
       <c r="K372" t="n">
-        <v>2.533026156967144</v>
+        <v>2.583614802286179</v>
       </c>
     </row>
     <row r="373">
@@ -15732,7 +15732,7 @@
         <v>2</v>
       </c>
       <c r="K373" t="n">
-        <v>2.618550022342504</v>
+        <v>2.652821379658106</v>
       </c>
     </row>
     <row r="374">
@@ -15773,7 +15773,7 @@
         <v>2</v>
       </c>
       <c r="K374" t="n">
-        <v>2.618550022342504</v>
+        <v>2.652821379658106</v>
       </c>
     </row>
     <row r="375">
@@ -15814,7 +15814,7 @@
         <v>2</v>
       </c>
       <c r="K375" t="n">
-        <v>2.673863725819055</v>
+        <v>2.699468682898502</v>
       </c>
     </row>
     <row r="376">
@@ -15855,7 +15855,7 @@
         <v>2</v>
       </c>
       <c r="K376" t="n">
-        <v>2.673863725819055</v>
+        <v>2.699468682898502</v>
       </c>
     </row>
     <row r="377">
@@ -15896,7 +15896,7 @@
         <v>2</v>
       </c>
       <c r="K377" t="n">
-        <v>2.786270111621638</v>
+        <v>2.778243865174317</v>
       </c>
     </row>
     <row r="378">
@@ -15937,7 +15937,7 @@
         <v>2</v>
       </c>
       <c r="K378" t="n">
-        <v>2.793844610713815</v>
+        <v>2.795143882673092</v>
       </c>
     </row>
     <row r="379">
@@ -15978,7 +15978,7 @@
         <v>2</v>
       </c>
       <c r="K379" t="n">
-        <v>2.777480180868591</v>
+        <v>2.767794713231985</v>
       </c>
     </row>
     <row r="380">
@@ -16019,7 +16019,7 @@
         <v>2</v>
       </c>
       <c r="K380" t="n">
-        <v>2.758451324092219</v>
+        <v>2.767343971360472</v>
       </c>
     </row>
     <row r="381">
@@ -16060,7 +16060,7 @@
         <v>2</v>
       </c>
       <c r="K381" t="n">
-        <v>2.718308847238013</v>
+        <v>2.730706374609796</v>
       </c>
     </row>
     <row r="382">
@@ -16101,7 +16101,7 @@
         <v>2</v>
       </c>
       <c r="K382" t="n">
-        <v>2.713405551329738</v>
+        <v>2.691750402130692</v>
       </c>
     </row>
     <row r="383">
@@ -16142,7 +16142,7 @@
         <v>2</v>
       </c>
       <c r="K383" t="n">
-        <v>2.58595042968048</v>
+        <v>2.602074553048171</v>
       </c>
     </row>
     <row r="384">
@@ -16183,7 +16183,7 @@
         <v>2</v>
       </c>
       <c r="K384" t="n">
-        <v>2.484596963201059</v>
+        <v>2.49815875274853</v>
       </c>
     </row>
     <row r="385">
@@ -16224,7 +16224,7 @@
         <v>2</v>
       </c>
       <c r="K385" t="n">
-        <v>2.47913383187016</v>
+        <v>2.453207340402886</v>
       </c>
     </row>
     <row r="386">
@@ -16265,7 +16265,7 @@
         <v>2</v>
       </c>
       <c r="K386" t="n">
-        <v>2.43478182435853</v>
+        <v>2.452332403162939</v>
       </c>
     </row>
     <row r="387">
@@ -16306,7 +16306,7 @@
         <v>2</v>
       </c>
       <c r="K387" t="n">
-        <v>2.43478182435853</v>
+        <v>2.415166011405054</v>
       </c>
     </row>
     <row r="388">
@@ -16347,7 +16347,7 @@
         <v>2</v>
       </c>
       <c r="K388" t="n">
-        <v>2.368843364186503</v>
+        <v>2.349357321309459</v>
       </c>
     </row>
     <row r="389">
@@ -16388,7 +16388,7 @@
         <v>2</v>
       </c>
       <c r="K389" t="n">
-        <v>2.25214800643259</v>
+        <v>2.258816638442839</v>
       </c>
     </row>
     <row r="390">
@@ -16429,7 +16429,7 @@
         <v>2</v>
       </c>
       <c r="K390" t="n">
-        <v>2.232363721869575</v>
+        <v>2.237173868782789</v>
       </c>
     </row>
     <row r="391">
@@ -16470,7 +16470,7 @@
         <v>2</v>
       </c>
       <c r="K391" t="n">
-        <v>2.231837605688082</v>
+        <v>2.237173868782789</v>
       </c>
     </row>
     <row r="392">
@@ -16511,7 +16511,7 @@
         <v>2</v>
       </c>
       <c r="K392" t="n">
-        <v>2.210318404191058</v>
+        <v>2.209273342985907</v>
       </c>
     </row>
     <row r="393">
@@ -16552,7 +16552,7 @@
         <v>2</v>
       </c>
       <c r="K393" t="n">
-        <v>2.216671271017764</v>
+        <v>2.214781296045799</v>
       </c>
     </row>
     <row r="394">
@@ -16593,7 +16593,7 @@
         <v>2</v>
       </c>
       <c r="K394" t="n">
-        <v>2.22988717299946</v>
+        <v>2.227767199283891</v>
       </c>
     </row>
     <row r="395">
@@ -16634,7 +16634,7 @@
         <v>2</v>
       </c>
       <c r="K395" t="n">
-        <v>2.268759589262716</v>
+        <v>2.280936393378677</v>
       </c>
     </row>
     <row r="396">
@@ -16675,7 +16675,7 @@
         <v>2</v>
       </c>
       <c r="K396" t="n">
-        <v>2.288662996731921</v>
+        <v>2.297951269585582</v>
       </c>
     </row>
     <row r="397">
@@ -16716,7 +16716,7 @@
         <v>2</v>
       </c>
       <c r="K397" t="n">
-        <v>2.352475311109939</v>
+        <v>2.36201282848879</v>
       </c>
     </row>
     <row r="398">
@@ -16757,7 +16757,7 @@
         <v>2</v>
       </c>
       <c r="K398" t="n">
-        <v>2.366001064509192</v>
+        <v>2.362299388184507</v>
       </c>
     </row>
     <row r="399">
@@ -16798,7 +16798,7 @@
         <v>2</v>
       </c>
       <c r="K399" t="n">
-        <v>2.398216889432669</v>
+        <v>2.406005864427903</v>
       </c>
     </row>
     <row r="400">
@@ -16839,7 +16839,7 @@
         <v>2</v>
       </c>
       <c r="K400" t="n">
-        <v>2.409412092032066</v>
+        <v>2.406252589218524</v>
       </c>
     </row>
     <row r="401">
@@ -16880,7 +16880,7 @@
         <v>2</v>
       </c>
       <c r="K401" t="n">
-        <v>2.41857346489639</v>
+        <v>2.41599300017818</v>
       </c>
     </row>
     <row r="402">
@@ -16921,7 +16921,7 @@
         <v>2</v>
       </c>
       <c r="K402" t="n">
-        <v>2.419658441947551</v>
+        <v>2.425678493221811</v>
       </c>
     </row>
     <row r="403">
@@ -16962,7 +16962,7 @@
         <v>2</v>
       </c>
       <c r="K403" t="n">
-        <v>2.45495802551393</v>
+        <v>2.472667052877094</v>
       </c>
     </row>
     <row r="404">
@@ -17003,7 +17003,7 @@
         <v>2</v>
       </c>
       <c r="K404" t="n">
-        <v>2.558467583368409</v>
+        <v>2.549885061676941</v>
       </c>
     </row>
     <row r="405">
@@ -17044,7 +17044,7 @@
         <v>2</v>
       </c>
       <c r="K405" t="n">
-        <v>2.562260704488763</v>
+        <v>2.578709450423326</v>
       </c>
     </row>
     <row r="406">
@@ -17085,7 +17085,7 @@
         <v>2</v>
       </c>
       <c r="K406" t="n">
-        <v>2.589655981420203</v>
+        <v>2.603557653339817</v>
       </c>
     </row>
     <row r="407">
@@ -17126,7 +17126,7 @@
         <v>2</v>
       </c>
       <c r="K407" t="n">
-        <v>2.661773406777044</v>
+        <v>2.65848691238964</v>
       </c>
     </row>
     <row r="408">
@@ -17167,7 +17167,7 @@
         <v>2</v>
       </c>
       <c r="K408" t="n">
-        <v>2.674091609927487</v>
+        <v>2.670595576065154</v>
       </c>
     </row>
     <row r="409">
@@ -17208,7 +17208,7 @@
         <v>2</v>
       </c>
       <c r="K409" t="n">
-        <v>2.7195196322338</v>
+        <v>2.729505896692063</v>
       </c>
     </row>
     <row r="410">
@@ -17249,7 +17249,7 @@
         <v>2</v>
       </c>
       <c r="K410" t="n">
-        <v>2.732876607136169</v>
+        <v>2.729505896692063</v>
       </c>
     </row>
     <row r="411">
@@ -17290,7 +17290,7 @@
         <v>2</v>
       </c>
       <c r="K411" t="n">
-        <v>2.712655642454856</v>
+        <v>2.719383432764725</v>
       </c>
     </row>
     <row r="412">
@@ -17331,7 +17331,7 @@
         <v>2</v>
       </c>
       <c r="K412" t="n">
-        <v>2.641424891311162</v>
+        <v>2.647374390344682</v>
       </c>
     </row>
     <row r="413">
@@ -17372,7 +17372,7 @@
         <v>2</v>
       </c>
       <c r="K413" t="n">
-        <v>2.638655258854448</v>
+        <v>2.647374390344682</v>
       </c>
     </row>
     <row r="414">
@@ -17413,7 +17413,7 @@
         <v>2</v>
       </c>
       <c r="K414" t="n">
-        <v>2.519634181471032</v>
+        <v>2.529946121244504</v>
       </c>
     </row>
     <row r="415">
@@ -17454,7 +17454,7 @@
         <v>2</v>
       </c>
       <c r="K415" t="n">
-        <v>2.478782202290914</v>
+        <v>2.491082145834306</v>
       </c>
     </row>
     <row r="416">
@@ -17495,7 +17495,7 @@
         <v>2</v>
       </c>
       <c r="K416" t="n">
-        <v>2.425357244639936</v>
+        <v>2.396667104848631</v>
       </c>
     </row>
     <row r="417">
@@ -17536,7 +17536,7 @@
         <v>2</v>
       </c>
       <c r="K417" t="n">
-        <v>2.380914291096624</v>
+        <v>2.395544273213098</v>
       </c>
     </row>
     <row r="418">
@@ -17577,7 +17577,7 @@
         <v>2</v>
       </c>
       <c r="K418" t="n">
-        <v>2.380914291096624</v>
+        <v>2.395544273213098</v>
       </c>
     </row>
     <row r="419">
@@ -17618,7 +17618,7 @@
         <v>2</v>
       </c>
       <c r="K419" t="n">
-        <v>2.18176137762674</v>
+        <v>2.139932954798277</v>
       </c>
     </row>
     <row r="420">
@@ -17659,7 +17659,7 @@
         <v>2</v>
       </c>
       <c r="K420" t="n">
-        <v>2.110580560016065</v>
+        <v>2.138369782990025</v>
       </c>
     </row>
     <row r="421">
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="K421" t="n">
-        <v>2.048863670413637</v>
+        <v>2.067028577756543</v>
       </c>
     </row>
     <row r="422">
@@ -17741,7 +17741,7 @@
         <v>2</v>
       </c>
       <c r="K422" t="n">
-        <v>1.900395550248122</v>
+        <v>1.909981851924296</v>
       </c>
     </row>
     <row r="423">
@@ -17782,7 +17782,7 @@
         <v>2</v>
       </c>
       <c r="K423" t="n">
-        <v>1.89629322626414</v>
+        <v>1.881039650564513</v>
       </c>
     </row>
     <row r="424">
@@ -17823,7 +17823,7 @@
         <v>2</v>
       </c>
       <c r="K424" t="n">
-        <v>1.852671258716622</v>
+        <v>1.850730460530859</v>
       </c>
     </row>
     <row r="425">
@@ -17864,7 +17864,7 @@
         <v>2</v>
       </c>
       <c r="K425" t="n">
-        <v>1.85087802246062</v>
+        <v>1.850713131817195</v>
       </c>
     </row>
     <row r="426">
@@ -17905,7 +17905,7 @@
         <v>2</v>
       </c>
       <c r="K426" t="n">
-        <v>1.850670598952984</v>
+        <v>1.850754333526299</v>
       </c>
     </row>
     <row r="427">
@@ -17946,7 +17946,7 @@
         <v>2</v>
       </c>
       <c r="K427" t="n">
-        <v>1.842365730565255</v>
+        <v>1.84487940247459</v>
       </c>
     </row>
     <row r="428">
@@ -17987,7 +17987,7 @@
         <v>2</v>
       </c>
       <c r="K428" t="n">
-        <v>1.827780845747513</v>
+        <v>1.83145660635608</v>
       </c>
     </row>
     <row r="429">
@@ -18028,7 +18028,7 @@
         <v>2</v>
       </c>
       <c r="K429" t="n">
-        <v>1.827780845747513</v>
+        <v>1.831137126346885</v>
       </c>
     </row>
     <row r="430">
@@ -18069,7 +18069,7 @@
         <v>2</v>
       </c>
       <c r="K430" t="n">
-        <v>1.827780845747513</v>
+        <v>1.831137126346885</v>
       </c>
     </row>
     <row r="431">
@@ -18110,7 +18110,7 @@
         <v>2</v>
       </c>
       <c r="K431" t="n">
-        <v>1.826016765575718</v>
+        <v>1.814611468114419</v>
       </c>
     </row>
     <row r="432">
@@ -18151,7 +18151,7 @@
         <v>2</v>
       </c>
       <c r="K432" t="n">
-        <v>1.826016765575718</v>
+        <v>1.814611468114419</v>
       </c>
     </row>
     <row r="433">
@@ -18192,7 +18192,7 @@
         <v>2</v>
       </c>
       <c r="K433" t="n">
-        <v>1.804538279676842</v>
+        <v>1.814100353576843</v>
       </c>
     </row>
     <row r="434">
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="K434" t="n">
-        <v>1.804538279676842</v>
+        <v>1.787058760955101</v>
       </c>
     </row>
     <row r="435">
@@ -18274,7 +18274,7 @@
         <v>2</v>
       </c>
       <c r="K435" t="n">
-        <v>1.779365439684264</v>
+        <v>1.786441320827773</v>
       </c>
     </row>
     <row r="436">
@@ -18315,7 +18315,7 @@
         <v>2</v>
       </c>
       <c r="K436" t="n">
-        <v>1.738874318272187</v>
+        <v>1.708352231683424</v>
       </c>
     </row>
     <row r="437">
@@ -18356,7 +18356,7 @@
         <v>2</v>
       </c>
       <c r="K437" t="n">
-        <v>1.598467165609943</v>
+        <v>1.611675886749983</v>
       </c>
     </row>
     <row r="438">
@@ -18397,7 +18397,7 @@
         <v>2</v>
       </c>
       <c r="K438" t="n">
-        <v>1.598467165609943</v>
+        <v>1.580787573213013</v>
       </c>
     </row>
     <row r="439">
@@ -18438,7 +18438,7 @@
         <v>2</v>
       </c>
       <c r="K439" t="n">
-        <v>1.540642156830476</v>
+        <v>1.548751298360699</v>
       </c>
     </row>
     <row r="440">
@@ -18479,7 +18479,7 @@
         <v>2</v>
       </c>
       <c r="K440" t="n">
-        <v>1.513901223512885</v>
+        <v>1.506182875045549</v>
       </c>
     </row>
     <row r="441">
@@ -18520,7 +18520,7 @@
         <v>2</v>
       </c>
       <c r="K441" t="n">
-        <v>1.545172147416411</v>
+        <v>1.537350604357719</v>
       </c>
     </row>
     <row r="442">
@@ -18561,7 +18561,7 @@
         <v>2</v>
       </c>
       <c r="K442" t="n">
-        <v>1.549486063043763</v>
+        <v>1.537350604357719</v>
       </c>
     </row>
     <row r="443">
@@ -18602,7 +18602,7 @@
         <v>2</v>
       </c>
       <c r="K443" t="n">
-        <v>1.549486063043763</v>
+        <v>1.568346931088525</v>
       </c>
     </row>
     <row r="444">
@@ -18643,7 +18643,7 @@
         <v>2</v>
       </c>
       <c r="K444" t="n">
-        <v>1.899336618499538</v>
+        <v>1.874292951198</v>
       </c>
     </row>
     <row r="445">
@@ -18684,7 +18684,7 @@
         <v>2</v>
       </c>
       <c r="K445" t="n">
-        <v>2.224233700446169</v>
+        <v>2.194736318640937</v>
       </c>
     </row>
     <row r="446">
@@ -18725,7 +18725,7 @@
         <v>2</v>
       </c>
       <c r="K446" t="n">
-        <v>2.330404289907134</v>
+        <v>2.303162446677891</v>
       </c>
     </row>
     <row r="447">
@@ -18766,7 +18766,7 @@
         <v>2</v>
       </c>
       <c r="K447" t="n">
-        <v>2.550071688613345</v>
+        <v>2.531541091281265</v>
       </c>
     </row>
     <row r="448">
@@ -18807,7 +18807,7 @@
         <v>2</v>
       </c>
       <c r="K448" t="n">
-        <v>2.550071688613345</v>
+        <v>2.576426434127854</v>
       </c>
     </row>
     <row r="449">
@@ -18848,7 +18848,7 @@
         <v>2</v>
       </c>
       <c r="K449" t="n">
-        <v>2.586586784958124</v>
+        <v>2.577384266817279</v>
       </c>
     </row>
     <row r="450">
@@ -18889,7 +18889,7 @@
         <v>2</v>
       </c>
       <c r="K450" t="n">
-        <v>2.61591183063859</v>
+        <v>2.60876052289624</v>
       </c>
     </row>
     <row r="451">
@@ -18930,7 +18930,7 @@
         <v>2</v>
       </c>
       <c r="K451" t="n">
-        <v>2.537699778527874</v>
+        <v>2.551808870664015</v>
       </c>
     </row>
     <row r="452">
@@ -18971,7 +18971,7 @@
         <v>2</v>
       </c>
       <c r="K452" t="n">
-        <v>2.474056520534348</v>
+        <v>2.489857817041605</v>
       </c>
     </row>
     <row r="453">
@@ -19012,7 +19012,7 @@
         <v>2</v>
       </c>
       <c r="K453" t="n">
-        <v>2.474056520534348</v>
+        <v>2.489857817041605</v>
       </c>
     </row>
     <row r="454">
@@ -19053,7 +19053,7 @@
         <v>2</v>
       </c>
       <c r="K454" t="n">
-        <v>2.474056520534348</v>
+        <v>2.489857817041605</v>
       </c>
     </row>
     <row r="455">
@@ -19094,7 +19094,7 @@
         <v>2</v>
       </c>
       <c r="K455" t="n">
-        <v>2.332531343452457</v>
+        <v>2.351239866520726</v>
       </c>
     </row>
     <row r="456">
@@ -19135,7 +19135,7 @@
         <v>2</v>
       </c>
       <c r="K456" t="n">
-        <v>2.321600695604415</v>
+        <v>2.276502646847667</v>
       </c>
     </row>
     <row r="457">
@@ -19176,7 +19176,7 @@
         <v>2</v>
       </c>
       <c r="K457" t="n">
-        <v>2.257276063767127</v>
+        <v>2.274773782200159</v>
       </c>
     </row>
     <row r="458">
@@ -19217,7 +19217,7 @@
         <v>2</v>
       </c>
       <c r="K458" t="n">
-        <v>2.069287627425231</v>
+        <v>2.077690662509931</v>
       </c>
     </row>
     <row r="459">
@@ -19258,7 +19258,7 @@
         <v>2</v>
       </c>
       <c r="K459" t="n">
-        <v>2.06525299783925</v>
+        <v>2.077690662509931</v>
       </c>
     </row>
     <row r="460">
@@ -19299,7 +19299,7 @@
         <v>2</v>
       </c>
       <c r="K460" t="n">
-        <v>2.06525299783925</v>
+        <v>2.077690662509931</v>
       </c>
     </row>
     <row r="461">
@@ -19340,7 +19340,7 @@
         <v>2</v>
       </c>
       <c r="K461" t="n">
-        <v>2.05459525953189</v>
+        <v>2.055495018606462</v>
       </c>
     </row>
     <row r="462">
@@ -19381,7 +19381,7 @@
         <v>2</v>
       </c>
       <c r="K462" t="n">
-        <v>2.056991536725648</v>
+        <v>2.055608448199757</v>
       </c>
     </row>
     <row r="463">
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="K463" t="n">
-        <v>2.064130175465934</v>
+        <v>2.071512276940043</v>
       </c>
     </row>
     <row r="464">
@@ -19463,7 +19463,7 @@
         <v>2</v>
       </c>
       <c r="K464" t="n">
-        <v>2.214671060823963</v>
+        <v>2.196159572085369</v>
       </c>
     </row>
     <row r="465">
@@ -19504,7 +19504,7 @@
         <v>2</v>
       </c>
       <c r="K465" t="n">
-        <v>2.22512500023652</v>
+        <v>2.197865358988584</v>
       </c>
     </row>
     <row r="466">
@@ -19545,7 +19545,7 @@
         <v>2</v>
       </c>
       <c r="K466" t="n">
-        <v>2.289300410662081</v>
+        <v>2.271522894461202</v>
       </c>
     </row>
     <row r="467">
@@ -19586,7 +19586,7 @@
         <v>2</v>
       </c>
       <c r="K467" t="n">
-        <v>2.382961362207613</v>
+        <v>2.438535301017394</v>
       </c>
     </row>
     <row r="468">
@@ -19627,7 +19627,7 @@
         <v>2</v>
       </c>
       <c r="K468" t="n">
-        <v>2.462609261231583</v>
+        <v>2.438535301017394</v>
       </c>
     </row>
     <row r="469">
@@ -19668,7 +19668,7 @@
         <v>2</v>
       </c>
       <c r="K469" t="n">
-        <v>2.659350941236433</v>
+        <v>2.636124467559942</v>
       </c>
     </row>
     <row r="470">
@@ -19709,7 +19709,7 @@
         <v>2</v>
       </c>
       <c r="K470" t="n">
-        <v>2.912964018205849</v>
+        <v>2.897379881239063</v>
       </c>
     </row>
     <row r="471">
@@ -19750,7 +19750,7 @@
         <v>2</v>
       </c>
       <c r="K471" t="n">
-        <v>2.922523816392022</v>
+        <v>2.897379881239063</v>
       </c>
     </row>
     <row r="472">
@@ -19791,7 +19791,7 @@
         <v>2</v>
       </c>
       <c r="K472" t="n">
-        <v>2.977320288555501</v>
+        <v>2.960344633230705</v>
       </c>
     </row>
     <row r="473">
@@ -19832,7 +19832,7 @@
         <v>2</v>
       </c>
       <c r="K473" t="n">
-        <v>2.987593593258851</v>
+        <v>2.988681258672736</v>
       </c>
     </row>
     <row r="474">
@@ -19873,7 +19873,7 @@
         <v>2</v>
       </c>
       <c r="K474" t="n">
-        <v>2.822026428754017</v>
+        <v>2.845654145285847</v>
       </c>
     </row>
     <row r="475">
@@ -19914,7 +19914,7 @@
         <v>2</v>
       </c>
       <c r="K475" t="n">
-        <v>2.806075475373767</v>
+        <v>2.739888232530778</v>
       </c>
     </row>
     <row r="476">
@@ -19955,7 +19955,7 @@
         <v>2</v>
       </c>
       <c r="K476" t="n">
-        <v>2.806075475373767</v>
+        <v>2.739888232530778</v>
       </c>
     </row>
     <row r="477">
@@ -19996,7 +19996,7 @@
         <v>2</v>
       </c>
       <c r="K477" t="n">
-        <v>2.712076875309097</v>
+        <v>2.737226940441403</v>
       </c>
     </row>
     <row r="478">
@@ -20037,7 +20037,7 @@
         <v>2</v>
       </c>
       <c r="K478" t="n">
-        <v>2.376263836303047</v>
+        <v>2.403530823712587</v>
       </c>
     </row>
     <row r="479">
@@ -20078,7 +20078,7 @@
         <v>2</v>
       </c>
       <c r="K479" t="n">
-        <v>2.376263836303047</v>
+        <v>2.400823334549036</v>
       </c>
     </row>
     <row r="480">
@@ -20119,7 +20119,7 @@
         <v>3</v>
       </c>
       <c r="K480" t="n">
-        <v>2.30280530514413</v>
+        <v>2.317546293819788</v>
       </c>
     </row>
     <row r="481">
@@ -20160,7 +20160,7 @@
         <v>3</v>
       </c>
       <c r="K481" t="n">
-        <v>2.250227729506013</v>
+        <v>2.266182162888653</v>
       </c>
     </row>
     <row r="482">
@@ -20201,7 +20201,7 @@
         <v>3</v>
       </c>
       <c r="K482" t="n">
-        <v>2.215775943332024</v>
+        <v>2.225089470793405</v>
       </c>
     </row>
     <row r="483">
@@ -20242,7 +20242,7 @@
         <v>3</v>
       </c>
       <c r="K483" t="n">
-        <v>2.215775943332024</v>
+        <v>2.225089470793405</v>
       </c>
     </row>
     <row r="484">
@@ -20283,7 +20283,7 @@
         <v>3</v>
       </c>
       <c r="K484" t="n">
-        <v>2.232330959169365</v>
+        <v>2.248363094707497</v>
       </c>
     </row>
     <row r="485">
@@ -20324,7 +20324,7 @@
         <v>3</v>
       </c>
       <c r="K485" t="n">
-        <v>2.256643808943577</v>
+        <v>2.248363094707497</v>
       </c>
     </row>
     <row r="486">
@@ -20365,7 +20365,7 @@
         <v>3</v>
       </c>
       <c r="K486" t="n">
-        <v>2.261991090551478</v>
+        <v>2.249157777791623</v>
       </c>
     </row>
     <row r="487">
@@ -20406,7 +20406,7 @@
         <v>3</v>
       </c>
       <c r="K487" t="n">
-        <v>2.301870039332318</v>
+        <v>2.289794080918707</v>
       </c>
     </row>
     <row r="488">
@@ -20447,7 +20447,7 @@
         <v>3</v>
       </c>
       <c r="K488" t="n">
-        <v>2.367155198339137</v>
+        <v>2.352329597521824</v>
       </c>
     </row>
     <row r="489">
@@ -20488,7 +20488,7 @@
         <v>3</v>
       </c>
       <c r="K489" t="n">
-        <v>2.377180243287329</v>
+        <v>2.352329597521824</v>
       </c>
     </row>
     <row r="490">
@@ -20529,7 +20529,7 @@
         <v>3</v>
       </c>
       <c r="K490" t="n">
-        <v>2.510186054048462</v>
+        <v>2.487715850147243</v>
       </c>
     </row>
     <row r="491">
@@ -20570,7 +20570,7 @@
         <v>3</v>
       </c>
       <c r="K491" t="n">
-        <v>2.557413986968126</v>
+        <v>2.543897578040192</v>
       </c>
     </row>
     <row r="492">
@@ -20611,7 +20611,7 @@
         <v>3</v>
       </c>
       <c r="K492" t="n">
-        <v>2.648846174480814</v>
+        <v>2.643756937649607</v>
       </c>
     </row>
     <row r="493">
@@ -20652,7 +20652,7 @@
         <v>3</v>
       </c>
       <c r="K493" t="n">
-        <v>2.662728291843294</v>
+        <v>2.66118619869942</v>
       </c>
     </row>
     <row r="494">
@@ -20693,7 +20693,7 @@
         <v>3</v>
       </c>
       <c r="K494" t="n">
-        <v>2.649219924340479</v>
+        <v>2.659227303931321</v>
       </c>
     </row>
     <row r="495">
@@ -20734,7 +20734,7 @@
         <v>3</v>
       </c>
       <c r="K495" t="n">
-        <v>2.59540559001166</v>
+        <v>2.581683245692532</v>
       </c>
     </row>
     <row r="496">
@@ -20775,7 +20775,7 @@
         <v>3</v>
       </c>
       <c r="K496" t="n">
-        <v>2.560817984339082</v>
+        <v>2.564618959103193</v>
       </c>
     </row>
     <row r="497">
@@ -20816,7 +20816,7 @@
         <v>3</v>
       </c>
       <c r="K497" t="n">
-        <v>2.501634689238714</v>
+        <v>2.51026888827337</v>
       </c>
     </row>
     <row r="498">
@@ -20857,7 +20857,7 @@
         <v>3</v>
       </c>
       <c r="K498" t="n">
-        <v>2.432418258565894</v>
+        <v>2.437063055438625</v>
       </c>
     </row>
     <row r="499">
@@ -20898,7 +20898,7 @@
         <v>3</v>
       </c>
       <c r="K499" t="n">
-        <v>2.40236383932226</v>
+        <v>2.398038066413498</v>
       </c>
     </row>
     <row r="500">
@@ -20939,7 +20939,7 @@
         <v>3</v>
       </c>
       <c r="K500" t="n">
-        <v>2.39909747195935</v>
+        <v>2.398038066413498</v>
       </c>
     </row>
     <row r="501">
@@ -20980,7 +20980,7 @@
         <v>3</v>
       </c>
       <c r="K501" t="n">
-        <v>2.474095389053848</v>
+        <v>2.460593066725835</v>
       </c>
     </row>
     <row r="502">
@@ -21021,7 +21021,7 @@
         <v>3</v>
       </c>
       <c r="K502" t="n">
-        <v>2.474095389053848</v>
+        <v>2.460593066725835</v>
       </c>
     </row>
     <row r="503">
@@ -21062,7 +21062,7 @@
         <v>3</v>
       </c>
       <c r="K503" t="n">
-        <v>2.595955455007303</v>
+        <v>2.624480883090083</v>
       </c>
     </row>
     <row r="504">
@@ -21103,7 +21103,7 @@
         <v>3</v>
       </c>
       <c r="K504" t="n">
-        <v>2.595955455007303</v>
+        <v>2.624480883090083</v>
       </c>
     </row>
     <row r="505">
@@ -21144,7 +21144,7 @@
         <v>3</v>
       </c>
       <c r="K505" t="n">
-        <v>2.72207002765784</v>
+        <v>2.709673707136087</v>
       </c>
     </row>
     <row r="506">
@@ -21185,7 +21185,7 @@
         <v>3</v>
       </c>
       <c r="K506" t="n">
-        <v>2.72207002765784</v>
+        <v>2.710956048097176</v>
       </c>
     </row>
     <row r="507">
@@ -21226,7 +21226,7 @@
         <v>3</v>
       </c>
       <c r="K507" t="n">
-        <v>2.788780703337199</v>
+        <v>2.773518455164883</v>
       </c>
     </row>
     <row r="508">
@@ -21267,7 +21267,7 @@
         <v>3</v>
       </c>
       <c r="K508" t="n">
-        <v>2.788780703337199</v>
+        <v>2.775244321802336</v>
       </c>
     </row>
     <row r="509">
@@ -21308,7 +21308,7 @@
         <v>3</v>
       </c>
       <c r="K509" t="n">
-        <v>2.97847013008986</v>
+        <v>2.965012326714395</v>
       </c>
     </row>
     <row r="510">
@@ -21349,7 +21349,7 @@
         <v>3</v>
       </c>
       <c r="K510" t="n">
-        <v>2.97847013008986</v>
+        <v>2.965012326714395</v>
       </c>
     </row>
     <row r="511">
@@ -21390,7 +21390,7 @@
         <v>3</v>
       </c>
       <c r="K511" t="n">
-        <v>3.01157986414617</v>
+        <v>3.005305048686576</v>
       </c>
     </row>
     <row r="512">
@@ -21431,7 +21431,7 @@
         <v>3</v>
       </c>
       <c r="K512" t="n">
-        <v>3.01157986414617</v>
+        <v>3.005859702384738</v>
       </c>
     </row>
     <row r="513">
@@ -21472,7 +21472,7 @@
         <v>3</v>
       </c>
       <c r="K513" t="n">
-        <v>3.039726491945422</v>
+        <v>3.039879098190566</v>
       </c>
     </row>
     <row r="514">
@@ -21513,7 +21513,7 @@
         <v>3</v>
       </c>
       <c r="K514" t="n">
-        <v>3.019010457551972</v>
+        <v>2.996972916507557</v>
       </c>
     </row>
     <row r="515">
@@ -21554,7 +21554,7 @@
         <v>3</v>
       </c>
       <c r="K515" t="n">
-        <v>2.862963616969401</v>
+        <v>2.867674977406217</v>
       </c>
     </row>
     <row r="516">
@@ -21595,7 +21595,7 @@
         <v>3</v>
       </c>
       <c r="K516" t="n">
-        <v>2.862963616969401</v>
+        <v>2.867125283973273</v>
       </c>
     </row>
     <row r="517">
@@ -21636,7 +21636,7 @@
         <v>3</v>
       </c>
       <c r="K517" t="n">
-        <v>2.859796011305207</v>
+        <v>2.848264608500432</v>
       </c>
     </row>
     <row r="518">
@@ -21677,7 +21677,7 @@
         <v>3</v>
       </c>
       <c r="K518" t="n">
-        <v>2.841411184601648</v>
+        <v>2.837333472987813</v>
       </c>
     </row>
     <row r="519">
@@ -21718,7 +21718,7 @@
         <v>3</v>
       </c>
       <c r="K519" t="n">
-        <v>2.841411184601648</v>
+        <v>2.837333472987813</v>
       </c>
     </row>
     <row r="520">
@@ -21759,7 +21759,7 @@
         <v>3</v>
       </c>
       <c r="K520" t="n">
-        <v>2.863266209391949</v>
+        <v>2.857778965931774</v>
       </c>
     </row>
     <row r="521">
@@ -21800,7 +21800,7 @@
         <v>3</v>
       </c>
       <c r="K521" t="n">
-        <v>2.888024879348644</v>
+        <v>2.8887181008879</v>
       </c>
     </row>
     <row r="522">
@@ -21841,7 +21841,7 @@
         <v>3</v>
       </c>
       <c r="K522" t="n">
-        <v>2.888024879348644</v>
+        <v>2.8887181008879</v>
       </c>
     </row>
     <row r="523">
@@ -21882,7 +21882,7 @@
         <v>3</v>
       </c>
       <c r="K523" t="n">
-        <v>2.825179314631639</v>
+        <v>2.812847529506985</v>
       </c>
     </row>
     <row r="524">
@@ -21923,7 +21923,7 @@
         <v>3</v>
       </c>
       <c r="K524" t="n">
-        <v>2.627764807843734</v>
+        <v>2.637050514292856</v>
       </c>
     </row>
     <row r="525">
@@ -21964,7 +21964,7 @@
         <v>3</v>
       </c>
       <c r="K525" t="n">
-        <v>2.627764807843734</v>
+        <v>2.635934282084738</v>
       </c>
     </row>
     <row r="526">
@@ -22005,7 +22005,7 @@
         <v>3</v>
       </c>
       <c r="K526" t="n">
-        <v>2.54725174433134</v>
+        <v>2.546339104368124</v>
       </c>
     </row>
     <row r="527">
@@ -22046,7 +22046,7 @@
         <v>3</v>
       </c>
       <c r="K527" t="n">
-        <v>2.550229610186616</v>
+        <v>2.548950533834845</v>
       </c>
     </row>
     <row r="528">
@@ -22087,7 +22087,7 @@
         <v>3</v>
       </c>
       <c r="K528" t="n">
-        <v>2.644362600916906</v>
+        <v>2.62563614426418</v>
       </c>
     </row>
     <row r="529">
@@ -22128,7 +22128,7 @@
         <v>3</v>
       </c>
       <c r="K529" t="n">
-        <v>3.224048162476565</v>
+        <v>3.190200595234527</v>
       </c>
     </row>
     <row r="530">
@@ -22169,7 +22169,7 @@
         <v>3</v>
       </c>
       <c r="K530" t="n">
-        <v>3.224048162476565</v>
+        <v>3.194298632110459</v>
       </c>
     </row>
     <row r="531">
@@ -22210,7 +22210,7 @@
         <v>3</v>
       </c>
       <c r="K531" t="n">
-        <v>3.598305332340881</v>
+        <v>3.576086941709023</v>
       </c>
     </row>
     <row r="532">
@@ -22251,7 +22251,7 @@
         <v>3</v>
       </c>
       <c r="K532" t="n">
-        <v>3.713474251746511</v>
+        <v>3.680012636622824</v>
       </c>
     </row>
     <row r="533">
@@ -22292,7 +22292,7 @@
         <v>3</v>
       </c>
       <c r="K533" t="n">
-        <v>3.852246060264426</v>
+        <v>3.838290269886043</v>
       </c>
     </row>
     <row r="534">
@@ -22333,7 +22333,7 @@
         <v>3</v>
       </c>
       <c r="K534" t="n">
-        <v>3.852246060264426</v>
+        <v>3.840089638193538</v>
       </c>
     </row>
     <row r="535">
@@ -22374,7 +22374,7 @@
         <v>3</v>
       </c>
       <c r="K535" t="n">
-        <v>3.893659775089872</v>
+        <v>3.889218511957885</v>
       </c>
     </row>
     <row r="536">
@@ -22415,7 +22415,7 @@
         <v>3</v>
       </c>
       <c r="K536" t="n">
-        <v>3.893659775089872</v>
+        <v>3.889218511957885</v>
       </c>
     </row>
     <row r="537">
@@ -22456,7 +22456,7 @@
         <v>3</v>
       </c>
       <c r="K537" t="n">
-        <v>3.893659775089872</v>
+        <v>3.889218511957885</v>
       </c>
     </row>
     <row r="538">
@@ -22497,7 +22497,7 @@
         <v>3</v>
       </c>
       <c r="K538" t="n">
-        <v>3.816978752115189</v>
+        <v>3.825430714796644</v>
       </c>
     </row>
     <row r="539">
@@ -22538,7 +22538,7 @@
         <v>3</v>
       </c>
       <c r="K539" t="n">
-        <v>3.816978752115189</v>
+        <v>3.824375191075222</v>
       </c>
     </row>
     <row r="540">
@@ -22579,7 +22579,7 @@
         <v>3</v>
       </c>
       <c r="K540" t="n">
-        <v>3.777794437671376</v>
+        <v>3.784666315216216</v>
       </c>
     </row>
     <row r="541">
@@ -22620,7 +22620,7 @@
         <v>3</v>
       </c>
       <c r="K541" t="n">
-        <v>3.771957833551445</v>
+        <v>3.748871193906942</v>
       </c>
     </row>
     <row r="542">
@@ -22661,7 +22661,7 @@
         <v>3</v>
       </c>
       <c r="K542" t="n">
-        <v>3.740814557077054</v>
+        <v>3.748871193906942</v>
       </c>
     </row>
     <row r="543">
@@ -22702,7 +22702,7 @@
         <v>3</v>
       </c>
       <c r="K543" t="n">
-        <v>3.722757542332938</v>
+        <v>3.72331195944887</v>
       </c>
     </row>
     <row r="544">
@@ -22743,7 +22743,7 @@
         <v>3</v>
       </c>
       <c r="K544" t="n">
-        <v>3.722757542332938</v>
+        <v>3.72331195944887</v>
       </c>
     </row>
     <row r="545">
@@ -22784,7 +22784,7 @@
         <v>3</v>
       </c>
       <c r="K545" t="n">
-        <v>3.722614145366322</v>
+        <v>3.72331195944887</v>
       </c>
     </row>
     <row r="546">
@@ -22825,7 +22825,7 @@
         <v>3</v>
       </c>
       <c r="K546" t="n">
-        <v>3.722614145366322</v>
+        <v>3.719971173153199</v>
       </c>
     </row>
     <row r="547">
@@ -22866,7 +22866,7 @@
         <v>3</v>
       </c>
       <c r="K547" t="n">
-        <v>3.72091113297808</v>
+        <v>3.723177361910333</v>
       </c>
     </row>
     <row r="548">
@@ -22907,7 +22907,7 @@
         <v>3</v>
       </c>
       <c r="K548" t="n">
-        <v>3.729350083519563</v>
+        <v>3.742342915932148</v>
       </c>
     </row>
     <row r="549">
@@ -22948,7 +22948,7 @@
         <v>3</v>
       </c>
       <c r="K549" t="n">
-        <v>3.750723599828893</v>
+        <v>3.742964175684912</v>
       </c>
     </row>
     <row r="550">
@@ -22989,7 +22989,7 @@
         <v>3</v>
       </c>
       <c r="K550" t="n">
-        <v>3.779628580035076</v>
+        <v>3.766081785152715</v>
       </c>
     </row>
     <row r="551">
@@ -23030,7 +23030,7 @@
         <v>3</v>
       </c>
       <c r="K551" t="n">
-        <v>4.051357667744662</v>
+        <v>4.037403738701596</v>
       </c>
     </row>
     <row r="552">
@@ -23071,7 +23071,7 @@
         <v>3</v>
       </c>
       <c r="K552" t="n">
-        <v>4.063584428200659</v>
+        <v>4.105366092587189</v>
       </c>
     </row>
     <row r="553">
@@ -23112,7 +23112,7 @@
         <v>3</v>
       </c>
       <c r="K553" t="n">
-        <v>4.159805490030706</v>
+        <v>4.154721307686508</v>
       </c>
     </row>
     <row r="554">
@@ -23153,7 +23153,7 @@
         <v>3</v>
       </c>
       <c r="K554" t="n">
-        <v>4.16159612051079</v>
+        <v>4.164259749149452</v>
       </c>
     </row>
     <row r="555">
@@ -23194,7 +23194,7 @@
         <v>3</v>
       </c>
       <c r="K555" t="n">
-        <v>4.159103137144754</v>
+        <v>4.149367685114449</v>
       </c>
     </row>
     <row r="556">
@@ -23235,7 +23235,7 @@
         <v>3</v>
       </c>
       <c r="K556" t="n">
-        <v>4.143805075357495</v>
+        <v>4.148857586960689</v>
       </c>
     </row>
     <row r="557">
@@ -23276,7 +23276,7 @@
         <v>3</v>
       </c>
       <c r="K557" t="n">
-        <v>4.12884095766673</v>
+        <v>4.132975585711481</v>
       </c>
     </row>
     <row r="558">
@@ -23317,7 +23317,7 @@
         <v>3</v>
       </c>
       <c r="K558" t="n">
-        <v>4.12455310443984</v>
+        <v>4.103929834562875</v>
       </c>
     </row>
     <row r="559">
@@ -23358,7 +23358,7 @@
         <v>3</v>
       </c>
       <c r="K559" t="n">
-        <v>4.087388290903759</v>
+        <v>4.057427138904227</v>
       </c>
     </row>
     <row r="560">
@@ -23399,7 +23399,7 @@
         <v>3</v>
       </c>
       <c r="K560" t="n">
-        <v>4.044968575389446</v>
+        <v>4.057427138904227</v>
       </c>
     </row>
     <row r="561">
@@ -23440,7 +23440,7 @@
         <v>3</v>
       </c>
       <c r="K561" t="n">
-        <v>3.977637725962148</v>
+        <v>3.989953707192166</v>
       </c>
     </row>
     <row r="562">
@@ -23481,7 +23481,7 @@
         <v>3</v>
       </c>
       <c r="K562" t="n">
-        <v>3.912419575923587</v>
+        <v>3.930140262938094</v>
       </c>
     </row>
     <row r="563">
@@ -23522,7 +23522,7 @@
         <v>3</v>
       </c>
       <c r="K563" t="n">
-        <v>3.912419575923587</v>
+        <v>3.879074865305455</v>
       </c>
     </row>
     <row r="564">
@@ -23563,7 +23563,7 @@
         <v>3</v>
       </c>
       <c r="K564" t="n">
-        <v>3.809613153755713</v>
+        <v>3.783072957612017</v>
       </c>
     </row>
     <row r="565">
@@ -23604,7 +23604,7 @@
         <v>3</v>
       </c>
       <c r="K565" t="n">
-        <v>3.773534856961286</v>
+        <v>3.781787785218484</v>
       </c>
     </row>
     <row r="566">
@@ -23645,7 +23645,7 @@
         <v>3</v>
       </c>
       <c r="K566" t="n">
-        <v>3.738548552469321</v>
+        <v>3.73804783887082</v>
       </c>
     </row>
     <row r="567">
@@ -23686,7 +23686,7 @@
         <v>3</v>
       </c>
       <c r="K567" t="n">
-        <v>3.726771371055897</v>
+        <v>3.712958437146414</v>
       </c>
     </row>
     <row r="568">
@@ -23727,7 +23727,7 @@
         <v>3</v>
       </c>
       <c r="K568" t="n">
-        <v>3.641986224342939</v>
+        <v>3.646138062815979</v>
       </c>
     </row>
     <row r="569">
@@ -23768,7 +23768,7 @@
         <v>3</v>
       </c>
       <c r="K569" t="n">
-        <v>3.637904397151695</v>
+        <v>3.636362658192369</v>
       </c>
     </row>
     <row r="570">
@@ -23809,7 +23809,7 @@
         <v>3</v>
       </c>
       <c r="K570" t="n">
-        <v>3.639793545672112</v>
+        <v>3.648821354335476</v>
       </c>
     </row>
     <row r="571">
@@ -23850,7 +23850,7 @@
         <v>3</v>
       </c>
       <c r="K571" t="n">
-        <v>3.727322442089522</v>
+        <v>3.730124287090561</v>
       </c>
     </row>
     <row r="572">
@@ -23891,7 +23891,7 @@
         <v>3</v>
       </c>
       <c r="K572" t="n">
-        <v>3.727322442089522</v>
+        <v>3.730124287090561</v>
       </c>
     </row>
     <row r="573">
@@ -23932,7 +23932,7 @@
         <v>3</v>
       </c>
       <c r="K573" t="n">
-        <v>3.727322442089522</v>
+        <v>3.730124287090561</v>
       </c>
     </row>
     <row r="574">
@@ -23973,7 +23973,7 @@
         <v>3</v>
       </c>
       <c r="K574" t="n">
-        <v>3.696780061471487</v>
+        <v>3.703053431827432</v>
       </c>
     </row>
     <row r="575">
@@ -24014,7 +24014,7 @@
         <v>3</v>
       </c>
       <c r="K575" t="n">
-        <v>3.648887556502674</v>
+        <v>3.659865436429206</v>
       </c>
     </row>
     <row r="576">
@@ -24055,7 +24055,7 @@
         <v>3</v>
       </c>
       <c r="K576" t="n">
-        <v>3.648887556502674</v>
+        <v>3.659865436429206</v>
       </c>
     </row>
     <row r="577">
@@ -24096,7 +24096,7 @@
         <v>3</v>
       </c>
       <c r="K577" t="n">
-        <v>3.580716454266587</v>
+        <v>3.595640800581458</v>
       </c>
     </row>
     <row r="578">
@@ -24137,7 +24137,7 @@
         <v>3</v>
       </c>
       <c r="K578" t="n">
-        <v>3.580716454266587</v>
+        <v>3.595640800581458</v>
       </c>
     </row>
     <row r="579">
@@ -24178,7 +24178,7 @@
         <v>3</v>
       </c>
       <c r="K579" t="n">
-        <v>3.400574246844875</v>
+        <v>3.41403392707766</v>
       </c>
     </row>
     <row r="580">
@@ -24219,7 +24219,7 @@
         <v>3</v>
       </c>
       <c r="K580" t="n">
-        <v>3.331795405673061</v>
+        <v>3.341806945553894</v>
       </c>
     </row>
     <row r="581">
@@ -24260,7 +24260,7 @@
         <v>3</v>
       </c>
       <c r="K581" t="n">
-        <v>3.322258425256809</v>
+        <v>3.341806945553894</v>
       </c>
     </row>
     <row r="582">
@@ -24301,7 +24301,7 @@
         <v>3</v>
       </c>
       <c r="K582" t="n">
-        <v>3.141595763257749</v>
+        <v>3.148926856210697</v>
       </c>
     </row>
     <row r="583">
@@ -24342,7 +24342,7 @@
         <v>3</v>
       </c>
       <c r="K583" t="n">
-        <v>3.160898782349284</v>
+        <v>3.155708453406447</v>
       </c>
     </row>
     <row r="584">
@@ -24383,7 +24383,7 @@
         <v>3</v>
       </c>
       <c r="K584" t="n">
-        <v>3.166803215221587</v>
+        <v>3.193466319703044</v>
       </c>
     </row>
     <row r="585">
@@ -24424,7 +24424,7 @@
         <v>3</v>
       </c>
       <c r="K585" t="n">
-        <v>3.203183585331309</v>
+        <v>3.193466319703044</v>
       </c>
     </row>
     <row r="586">
@@ -24465,7 +24465,7 @@
         <v>3</v>
       </c>
       <c r="K586" t="n">
-        <v>3.452014293068538</v>
+        <v>3.434090644350436</v>
       </c>
     </row>
     <row r="587">
@@ -24506,7 +24506,7 @@
         <v>3</v>
       </c>
       <c r="K587" t="n">
-        <v>3.574337471173696</v>
+        <v>3.542782337973954</v>
       </c>
     </row>
     <row r="588">
@@ -24547,7 +24547,7 @@
         <v>3</v>
       </c>
       <c r="K588" t="n">
-        <v>3.648174591356619</v>
+        <v>3.62665496623556</v>
       </c>
     </row>
     <row r="589">
@@ -24588,7 +24588,7 @@
         <v>3</v>
       </c>
       <c r="K589" t="n">
-        <v>3.685613172857863</v>
+        <v>3.683077031021423</v>
       </c>
     </row>
     <row r="590">
@@ -24629,7 +24629,7 @@
         <v>3</v>
       </c>
       <c r="K590" t="n">
-        <v>3.738505277220195</v>
+        <v>3.732775317452945</v>
       </c>
     </row>
     <row r="591">
@@ -24670,7 +24670,7 @@
         <v>3</v>
       </c>
       <c r="K591" t="n">
-        <v>3.810277718818141</v>
+        <v>3.811896908506674</v>
       </c>
     </row>
     <row r="592">
@@ -24711,7 +24711,7 @@
         <v>3</v>
       </c>
       <c r="K592" t="n">
-        <v>3.810277718818141</v>
+        <v>3.811685643058471</v>
       </c>
     </row>
     <row r="593">
@@ -24752,7 +24752,7 @@
         <v>3</v>
       </c>
       <c r="K593" t="n">
-        <v>3.79961834668442</v>
+        <v>3.801285748313703</v>
       </c>
     </row>
     <row r="594">
@@ -24793,7 +24793,7 @@
         <v>3</v>
       </c>
       <c r="K594" t="n">
-        <v>3.829308753991201</v>
+        <v>3.859018336106048</v>
       </c>
     </row>
     <row r="595">
@@ -24834,7 +24834,7 @@
         <v>3</v>
       </c>
       <c r="K595" t="n">
-        <v>3.903204952569961</v>
+        <v>3.899573564336937</v>
       </c>
     </row>
     <row r="596">
@@ -24875,7 +24875,7 @@
         <v>3</v>
       </c>
       <c r="K596" t="n">
-        <v>3.91461405714379</v>
+        <v>3.913283885938012</v>
       </c>
     </row>
     <row r="597">
@@ -24916,7 +24916,7 @@
         <v>3</v>
       </c>
       <c r="K597" t="n">
-        <v>3.942299363667987</v>
+        <v>3.96743397142932</v>
       </c>
     </row>
     <row r="598">
@@ -24957,7 +24957,7 @@
         <v>3</v>
       </c>
       <c r="K598" t="n">
-        <v>3.978058997701828</v>
+        <v>3.96849708375632</v>
       </c>
     </row>
     <row r="599">
@@ -24998,7 +24998,7 @@
         <v>3</v>
       </c>
       <c r="K599" t="n">
-        <v>3.978058997701828</v>
+        <v>3.96849708375632</v>
       </c>
     </row>
     <row r="600">
@@ -25039,7 +25039,7 @@
         <v>3</v>
       </c>
       <c r="K600" t="n">
-        <v>3.923686260811308</v>
+        <v>3.933080822316375</v>
       </c>
     </row>
     <row r="601">
@@ -25080,7 +25080,7 @@
         <v>3</v>
       </c>
       <c r="K601" t="n">
-        <v>3.872735511609227</v>
+        <v>3.882280267920926</v>
       </c>
     </row>
     <row r="602">
@@ -25121,7 +25121,7 @@
         <v>3</v>
       </c>
       <c r="K602" t="n">
-        <v>3.804517660543222</v>
+        <v>3.74727706259662</v>
       </c>
     </row>
     <row r="603">
@@ -25162,7 +25162,7 @@
         <v>3</v>
       </c>
       <c r="K603" t="n">
-        <v>3.614568201969552</v>
+        <v>3.593701148921845</v>
       </c>
     </row>
     <row r="604">
@@ -25203,7 +25203,7 @@
         <v>3</v>
       </c>
       <c r="K604" t="n">
-        <v>3.587134043046796</v>
+        <v>3.593701148921845</v>
       </c>
     </row>
     <row r="605">
@@ -25244,7 +25244,7 @@
         <v>3</v>
       </c>
       <c r="K605" t="n">
-        <v>3.585188671498764</v>
+        <v>3.592559050313146</v>
       </c>
     </row>
     <row r="606">
@@ -25285,7 +25285,7 @@
         <v>3</v>
       </c>
       <c r="K606" t="n">
-        <v>3.594209574588128</v>
+        <v>3.591028134771129</v>
       </c>
     </row>
     <row r="607">
@@ -25326,7 +25326,7 @@
         <v>3</v>
       </c>
       <c r="K607" t="n">
-        <v>3.594209574588128</v>
+        <v>3.591028134771129</v>
       </c>
     </row>
     <row r="608">
@@ -25367,7 +25367,7 @@
         <v>3</v>
       </c>
       <c r="K608" t="n">
-        <v>3.613969064175789</v>
+        <v>3.611249219620875</v>
       </c>
     </row>
     <row r="609">
@@ -25408,7 +25408,7 @@
         <v>3</v>
       </c>
       <c r="K609" t="n">
-        <v>3.627757478111978</v>
+        <v>3.625894824149705</v>
       </c>
     </row>
     <row r="610">
@@ -25449,7 +25449,7 @@
         <v>3</v>
       </c>
       <c r="K610" t="n">
-        <v>3.613084587547306</v>
+        <v>3.597874613895376</v>
       </c>
     </row>
     <row r="611">
@@ -25490,7 +25490,7 @@
         <v>3</v>
       </c>
       <c r="K611" t="n">
-        <v>3.547460659883082</v>
+        <v>3.549397382074472</v>
       </c>
     </row>
     <row r="612">
@@ -25531,7 +25531,7 @@
         <v>3</v>
       </c>
       <c r="K612" t="n">
-        <v>3.547460659883082</v>
+        <v>3.549397382074472</v>
       </c>
     </row>
     <row r="613">
@@ -25572,7 +25572,7 @@
         <v>3</v>
       </c>
       <c r="K613" t="n">
-        <v>3.521405444870771</v>
+        <v>3.530169682756298</v>
       </c>
     </row>
     <row r="614">
@@ -25613,7 +25613,7 @@
         <v>3</v>
       </c>
       <c r="K614" t="n">
-        <v>3.521405444870771</v>
+        <v>3.530169682756298</v>
       </c>
     </row>
     <row r="615">
@@ -25654,7 +25654,7 @@
         <v>3</v>
       </c>
       <c r="K615" t="n">
-        <v>3.497761886664333</v>
+        <v>3.506064403006139</v>
       </c>
     </row>
     <row r="616">
@@ -25695,7 +25695,7 @@
         <v>3</v>
       </c>
       <c r="K616" t="n">
-        <v>3.506548633564904</v>
+        <v>3.506064403006139</v>
       </c>
     </row>
     <row r="617">
@@ -25736,7 +25736,7 @@
         <v>3</v>
       </c>
       <c r="K617" t="n">
-        <v>3.399702733378625</v>
+        <v>3.407686674518889</v>
       </c>
     </row>
     <row r="618">
@@ -25777,7 +25777,7 @@
         <v>3</v>
       </c>
       <c r="K618" t="n">
-        <v>3.298684359939724</v>
+        <v>3.306062547487647</v>
       </c>
     </row>
     <row r="619">
@@ -25818,7 +25818,7 @@
         <v>3</v>
       </c>
       <c r="K619" t="n">
-        <v>3.291953468671688</v>
+        <v>3.304692561544982</v>
       </c>
     </row>
     <row r="620">
@@ -25859,7 +25859,7 @@
         <v>3</v>
       </c>
       <c r="K620" t="n">
-        <v>3.260284983130716</v>
+        <v>3.261627080052556</v>
       </c>
     </row>
     <row r="621">
@@ -25900,7 +25900,7 @@
         <v>3</v>
       </c>
       <c r="K621" t="n">
-        <v>3.27344869049019</v>
+        <v>3.271907657661389</v>
       </c>
     </row>
     <row r="622">
@@ -25941,7 +25941,7 @@
         <v>3</v>
       </c>
       <c r="K622" t="n">
-        <v>3.27344869049019</v>
+        <v>3.271907657661389</v>
       </c>
     </row>
     <row r="623">
@@ -25982,7 +25982,7 @@
         <v>3</v>
       </c>
       <c r="K623" t="n">
-        <v>3.27519779776497</v>
+        <v>3.272176898551753</v>
       </c>
     </row>
     <row r="624">
@@ -26023,7 +26023,7 @@
         <v>3</v>
       </c>
       <c r="K624" t="n">
-        <v>3.301263738147957</v>
+        <v>3.301990028386357</v>
       </c>
     </row>
     <row r="625">
@@ -26064,7 +26064,7 @@
         <v>3</v>
       </c>
       <c r="K625" t="n">
-        <v>3.301263738147957</v>
+        <v>3.301990028386357</v>
       </c>
     </row>
     <row r="626">
@@ -26105,7 +26105,7 @@
         <v>3</v>
       </c>
       <c r="K626" t="n">
-        <v>3.289410319604709</v>
+        <v>3.291631364290922</v>
       </c>
     </row>
     <row r="627">
@@ -26146,7 +26146,7 @@
         <v>3</v>
       </c>
       <c r="K627" t="n">
-        <v>3.208301282896448</v>
+        <v>3.214860271889209</v>
       </c>
     </row>
     <row r="628">
@@ -26187,7 +26187,7 @@
         <v>3</v>
       </c>
       <c r="K628" t="n">
-        <v>3.18654657786798</v>
+        <v>3.189902011851539</v>
       </c>
     </row>
     <row r="629">
@@ -26228,7 +26228,7 @@
         <v>3</v>
       </c>
       <c r="K629" t="n">
-        <v>3.181394693844502</v>
+        <v>3.181906899083868</v>
       </c>
     </row>
     <row r="630">
@@ -26269,7 +26269,7 @@
         <v>3</v>
       </c>
       <c r="K630" t="n">
-        <v>3.191953177748146</v>
+        <v>3.185894616210725</v>
       </c>
     </row>
     <row r="631">
@@ -26310,7 +26310,7 @@
         <v>3</v>
       </c>
       <c r="K631" t="n">
-        <v>3.209944922811141</v>
+        <v>3.205610161266541</v>
       </c>
     </row>
     <row r="632">
@@ -26351,7 +26351,7 @@
         <v>3</v>
       </c>
       <c r="K632" t="n">
-        <v>3.263353336253617</v>
+        <v>3.243774420459675</v>
       </c>
     </row>
     <row r="633">
@@ -26392,7 +26392,7 @@
         <v>3</v>
       </c>
       <c r="K633" t="n">
-        <v>3.337831290092738</v>
+        <v>3.334093043654648</v>
       </c>
     </row>
     <row r="634">
@@ -26433,7 +26433,7 @@
         <v>3</v>
       </c>
       <c r="K634" t="n">
-        <v>3.363580644358798</v>
+        <v>3.359359343732297</v>
       </c>
     </row>
     <row r="635">
@@ -26474,7 +26474,7 @@
         <v>3</v>
       </c>
       <c r="K635" t="n">
-        <v>3.401967929630747</v>
+        <v>3.421913690506645</v>
       </c>
     </row>
     <row r="636">
@@ -26515,7 +26515,7 @@
         <v>3</v>
       </c>
       <c r="K636" t="n">
-        <v>3.465703123588942</v>
+        <v>3.464150393066759</v>
       </c>
     </row>
     <row r="637">
@@ -26556,7 +26556,7 @@
         <v>3</v>
       </c>
       <c r="K637" t="n">
-        <v>3.465703123588942</v>
+        <v>3.468174437957325</v>
       </c>
     </row>
     <row r="638">
@@ -26597,7 +26597,7 @@
         <v>3</v>
       </c>
       <c r="K638" t="n">
-        <v>3.469812617773127</v>
+        <v>3.468450685520399</v>
       </c>
     </row>
     <row r="639">
@@ -26638,7 +26638,7 @@
         <v>3</v>
       </c>
       <c r="K639" t="n">
-        <v>3.516233206805755</v>
+        <v>3.5106407331394</v>
       </c>
     </row>
     <row r="640">
@@ -26679,7 +26679,7 @@
         <v>3</v>
       </c>
       <c r="K640" t="n">
-        <v>3.547168334934347</v>
+        <v>3.564309092804139</v>
       </c>
     </row>
     <row r="641">
@@ -26720,7 +26720,7 @@
         <v>3</v>
       </c>
       <c r="K641" t="n">
-        <v>3.567610492370573</v>
+        <v>3.565020271224166</v>
       </c>
     </row>
     <row r="642">
@@ -26761,7 +26761,7 @@
         <v>3</v>
       </c>
       <c r="K642" t="n">
-        <v>3.543565877588542</v>
+        <v>3.554273922910002</v>
       </c>
     </row>
     <row r="643">
@@ -26802,7 +26802,7 @@
         <v>3</v>
       </c>
       <c r="K643" t="n">
-        <v>3.497853436442588</v>
+        <v>3.463455385264521</v>
       </c>
     </row>
     <row r="644">
@@ -26843,7 +26843,7 @@
         <v>3</v>
       </c>
       <c r="K644" t="n">
-        <v>3.464758678334794</v>
+        <v>3.454800395029265</v>
       </c>
     </row>
     <row r="645">
@@ -26884,7 +26884,7 @@
         <v>3</v>
       </c>
       <c r="K645" t="n">
-        <v>3.474236902706298</v>
+        <v>3.453651116063476</v>
       </c>
     </row>
     <row r="646">
@@ -26925,7 +26925,7 @@
         <v>3</v>
       </c>
       <c r="K646" t="n">
-        <v>3.53247599786009</v>
+        <v>3.525354839904051</v>
       </c>
     </row>
     <row r="647">
@@ -26966,7 +26966,7 @@
         <v>3</v>
       </c>
       <c r="K647" t="n">
-        <v>3.703058491773652</v>
+        <v>3.689059502635577</v>
       </c>
     </row>
     <row r="648">
@@ -27007,7 +27007,7 @@
         <v>3</v>
       </c>
       <c r="K648" t="n">
-        <v>3.775875263652584</v>
+        <v>3.766230538907068</v>
       </c>
     </row>
     <row r="649">
@@ -27048,7 +27048,7 @@
         <v>3</v>
       </c>
       <c r="K649" t="n">
-        <v>3.775875263652584</v>
+        <v>3.766230538907068</v>
       </c>
     </row>
     <row r="650">
@@ -27089,7 +27089,7 @@
         <v>3</v>
       </c>
       <c r="K650" t="n">
-        <v>3.775875263652584</v>
+        <v>3.766230538907068</v>
       </c>
     </row>
     <row r="651">
@@ -27130,7 +27130,7 @@
         <v>3</v>
       </c>
       <c r="K651" t="n">
-        <v>3.931452018409427</v>
+        <v>3.957314212967365</v>
       </c>
     </row>
     <row r="652">
@@ -27171,7 +27171,7 @@
         <v>3</v>
       </c>
       <c r="K652" t="n">
-        <v>3.982667614685595</v>
+        <v>3.979694121947808</v>
       </c>
     </row>
     <row r="653">
@@ -27212,7 +27212,7 @@
         <v>3</v>
       </c>
       <c r="K653" t="n">
-        <v>4.002782577201176</v>
+        <v>3.998967213104235</v>
       </c>
     </row>
     <row r="654">
@@ -27253,7 +27253,7 @@
         <v>3</v>
       </c>
       <c r="K654" t="n">
-        <v>4.114682607796798</v>
+        <v>4.110973085495024</v>
       </c>
     </row>
     <row r="655">
@@ -27294,7 +27294,7 @@
         <v>3</v>
       </c>
       <c r="K655" t="n">
-        <v>4.114682607796798</v>
+        <v>4.110973085495024</v>
       </c>
     </row>
     <row r="656">
@@ -27335,7 +27335,7 @@
         <v>3</v>
       </c>
       <c r="K656" t="n">
-        <v>4.114682607796798</v>
+        <v>4.110973085495024</v>
       </c>
     </row>
     <row r="657">
@@ -27376,7 +27376,7 @@
         <v>3</v>
       </c>
       <c r="K657" t="n">
-        <v>4.179457048694251</v>
+        <v>4.177638591084119</v>
       </c>
     </row>
     <row r="658">
@@ -27417,7 +27417,7 @@
         <v>3</v>
       </c>
       <c r="K658" t="n">
-        <v>4.227356761953456</v>
+        <v>4.281339662953634</v>
       </c>
     </row>
     <row r="659">
@@ -27458,7 +27458,7 @@
         <v>3</v>
       </c>
       <c r="K659" t="n">
-        <v>4.348700606631981</v>
+        <v>4.387914243141883</v>
       </c>
     </row>
     <row r="660">
@@ -27499,7 +27499,7 @@
         <v>3</v>
       </c>
       <c r="K660" t="n">
-        <v>4.521183869121915</v>
+        <v>4.498855079418536</v>
       </c>
     </row>
     <row r="661">
@@ -27540,7 +27540,7 @@
         <v>3</v>
       </c>
       <c r="K661" t="n">
-        <v>4.500583131286295</v>
+        <v>4.498855079418536</v>
       </c>
     </row>
     <row r="662">
@@ -27581,7 +27581,7 @@
         <v>3</v>
       </c>
       <c r="K662" t="n">
-        <v>4.440990973619624</v>
+        <v>4.444164022899476</v>
       </c>
     </row>
     <row r="663">
@@ -27622,7 +27622,7 @@
         <v>3</v>
       </c>
       <c r="K663" t="n">
-        <v>4.422617725795629</v>
+        <v>4.42315175316554</v>
       </c>
     </row>
     <row r="664">
@@ -27663,7 +27663,7 @@
         <v>3</v>
       </c>
       <c r="K664" t="n">
-        <v>4.42108450919492</v>
+        <v>4.421917841021873</v>
       </c>
     </row>
     <row r="665">
@@ -27704,7 +27704,7 @@
         <v>3</v>
       </c>
       <c r="K665" t="n">
-        <v>4.376839312327779</v>
+        <v>4.389319812508438</v>
       </c>
     </row>
     <row r="666">
@@ -27745,7 +27745,7 @@
         <v>3</v>
       </c>
       <c r="K666" t="n">
-        <v>4.366531490052812</v>
+        <v>4.375258073497261</v>
       </c>
     </row>
     <row r="667">
@@ -27786,7 +27786,7 @@
         <v>3</v>
       </c>
       <c r="K667" t="n">
-        <v>4.366531490052812</v>
+        <v>4.341014834536546</v>
       </c>
     </row>
     <row r="668">
@@ -27827,7 +27827,7 @@
         <v>3</v>
       </c>
       <c r="K668" t="n">
-        <v>4.289627799319583</v>
+        <v>4.301786731435585</v>
       </c>
     </row>
     <row r="669">
@@ -27868,7 +27868,7 @@
         <v>3</v>
       </c>
       <c r="K669" t="n">
-        <v>4.215443368471973</v>
+        <v>4.226294517172393</v>
       </c>
     </row>
     <row r="670">
@@ -27909,7 +27909,7 @@
         <v>3</v>
       </c>
       <c r="K670" t="n">
-        <v>4.141064684913851</v>
+        <v>4.073479900212987</v>
       </c>
     </row>
     <row r="671">
@@ -27950,7 +27950,7 @@
         <v>3</v>
       </c>
       <c r="K671" t="n">
-        <v>3.966351004065593</v>
+        <v>3.980845299052108</v>
       </c>
     </row>
     <row r="672">
@@ -27991,7 +27991,7 @@
         <v>3</v>
       </c>
       <c r="K672" t="n">
-        <v>3.88080202022502</v>
+        <v>3.889546275300095</v>
       </c>
     </row>
     <row r="673">
@@ -28032,7 +28032,7 @@
         <v>3</v>
       </c>
       <c r="K673" t="n">
-        <v>3.850941208949669</v>
+        <v>3.850482331398048</v>
       </c>
     </row>
     <row r="674">
@@ -28073,7 +28073,7 @@
         <v>3</v>
       </c>
       <c r="K674" t="n">
-        <v>3.850941208949669</v>
+        <v>3.850482331398048</v>
       </c>
     </row>
     <row r="675">
@@ -28114,7 +28114,7 @@
         <v>3</v>
       </c>
       <c r="K675" t="n">
-        <v>3.811480648489826</v>
+        <v>3.817497224794757</v>
       </c>
     </row>
     <row r="676">
@@ -28155,7 +28155,7 @@
         <v>3</v>
       </c>
       <c r="K676" t="n">
-        <v>3.762419281057994</v>
+        <v>3.769796393588116</v>
       </c>
     </row>
     <row r="677">
@@ -28196,7 +28196,7 @@
         <v>3</v>
       </c>
       <c r="K677" t="n">
-        <v>3.762419281057994</v>
+        <v>3.727954291086882</v>
       </c>
     </row>
     <row r="678">
@@ -28237,7 +28237,7 @@
         <v>3</v>
       </c>
       <c r="K678" t="n">
-        <v>3.698222083745885</v>
+        <v>3.700628339584838</v>
       </c>
     </row>
     <row r="679">
@@ -28278,7 +28278,7 @@
         <v>3</v>
       </c>
       <c r="K679" t="n">
-        <v>3.684853168547362</v>
+        <v>3.686591327340248</v>
       </c>
     </row>
     <row r="680">
@@ -28319,7 +28319,7 @@
         <v>3</v>
       </c>
       <c r="K680" t="n">
-        <v>3.662098804452061</v>
+        <v>3.665944594526547</v>
       </c>
     </row>
     <row r="681">
@@ -28360,7 +28360,7 @@
         <v>3</v>
       </c>
       <c r="K681" t="n">
-        <v>3.662098804452061</v>
+        <v>3.665944594526547</v>
       </c>
     </row>
     <row r="682">
@@ -28401,7 +28401,7 @@
         <v>3</v>
       </c>
       <c r="K682" t="n">
-        <v>3.61623451407822</v>
+        <v>3.616458148086634</v>
       </c>
     </row>
     <row r="683">
@@ -28442,7 +28442,7 @@
         <v>3</v>
       </c>
       <c r="K683" t="n">
-        <v>3.670640138196266</v>
+        <v>3.687216244061484</v>
       </c>
     </row>
     <row r="684">
@@ -28483,7 +28483,7 @@
         <v>3</v>
       </c>
       <c r="K684" t="n">
-        <v>3.670640138196266</v>
+        <v>3.687216244061484</v>
       </c>
     </row>
     <row r="685">
@@ -28524,7 +28524,7 @@
         <v>3</v>
       </c>
       <c r="K685" t="n">
-        <v>3.670640138196266</v>
+        <v>3.683083798851799</v>
       </c>
     </row>
     <row r="686">
@@ -28565,7 +28565,7 @@
         <v>3</v>
       </c>
       <c r="K686" t="n">
-        <v>3.77296637088824</v>
+        <v>3.76329220573069</v>
       </c>
     </row>
     <row r="687">
@@ -28606,7 +28606,7 @@
         <v>3</v>
       </c>
       <c r="K687" t="n">
-        <v>4.367673490085361</v>
+        <v>4.28401300631225</v>
       </c>
     </row>
     <row r="688">
@@ -28647,7 +28647,7 @@
         <v>3</v>
       </c>
       <c r="K688" t="n">
-        <v>4.750769397264579</v>
+        <v>4.720825133839709</v>
       </c>
     </row>
     <row r="689">
@@ -28688,7 +28688,7 @@
         <v>3</v>
       </c>
       <c r="K689" t="n">
-        <v>3.867519880845868</v>
+        <v>3.9726365330883</v>
       </c>
     </row>
     <row r="690">
@@ -28729,7 +28729,7 @@
         <v>3</v>
       </c>
       <c r="K690" t="n">
-        <v>3.867519880845868</v>
+        <v>3.9726365330883</v>
       </c>
     </row>
     <row r="691">
@@ -28770,7 +28770,7 @@
         <v>3</v>
       </c>
       <c r="K691" t="n">
-        <v>3.078655280970453</v>
+        <v>3.1953911503779</v>
       </c>
     </row>
     <row r="692">
@@ -28811,7 +28811,7 @@
         <v>3</v>
       </c>
       <c r="K692" t="n">
-        <v>1.328337265668739</v>
+        <v>1.346701945578485</v>
       </c>
     </row>
     <row r="693">
@@ -28852,7 +28852,7 @@
         <v>3</v>
       </c>
       <c r="K693" t="n">
-        <v>1.15908494429521</v>
+        <v>1.157562385616418</v>
       </c>
     </row>
     <row r="694">
@@ -28893,7 +28893,7 @@
         <v>3</v>
       </c>
       <c r="K694" t="n">
-        <v>1.15908494429521</v>
+        <v>1.157562385616418</v>
       </c>
     </row>
     <row r="695">
@@ -28934,7 +28934,7 @@
         <v>3</v>
       </c>
       <c r="K695" t="n">
-        <v>1.364781195035363</v>
+        <v>1.343671916154519</v>
       </c>
     </row>
     <row r="696">
@@ -28975,7 +28975,7 @@
         <v>3</v>
       </c>
       <c r="K696" t="n">
-        <v>1.53639448201659</v>
+        <v>1.688597933244252</v>
       </c>
     </row>
     <row r="697">
@@ -29016,7 +29016,7 @@
         <v>3</v>
       </c>
       <c r="K697" t="n">
-        <v>1.887002571168518</v>
+        <v>1.863596644919217</v>
       </c>
     </row>
     <row r="698">
@@ -29057,7 +29057,7 @@
         <v>3</v>
       </c>
       <c r="K698" t="n">
-        <v>2.323128897170909</v>
+        <v>2.31261790459486</v>
       </c>
     </row>
     <row r="699">
@@ -29098,7 +29098,7 @@
         <v>3</v>
       </c>
       <c r="K699" t="n">
-        <v>2.323128897170909</v>
+        <v>2.31261790459486</v>
       </c>
     </row>
     <row r="700">
@@ -29139,7 +29139,7 @@
         <v>3</v>
       </c>
       <c r="K700" t="n">
-        <v>2.450743265661965</v>
+        <v>2.445405554782473</v>
       </c>
     </row>
     <row r="701">
@@ -29180,7 +29180,7 @@
         <v>3</v>
       </c>
       <c r="K701" t="n">
-        <v>2.450743265661965</v>
+        <v>2.473396015865601</v>
       </c>
     </row>
     <row r="702">
@@ -29221,7 +29221,7 @@
         <v>3</v>
       </c>
       <c r="K702" t="n">
-        <v>2.475254261949296</v>
+        <v>2.473396015865601</v>
       </c>
     </row>
     <row r="703">
@@ -29262,7 +29262,7 @@
         <v>3</v>
       </c>
       <c r="K703" t="n">
-        <v>2.475254261949296</v>
+        <v>2.462535160835919</v>
       </c>
     </row>
     <row r="704">
@@ -29303,7 +29303,7 @@
         <v>3</v>
       </c>
       <c r="K704" t="n">
-        <v>2.459227771244468</v>
+        <v>2.462535160835919</v>
       </c>
     </row>
     <row r="705">
@@ -29344,7 +29344,7 @@
         <v>3</v>
       </c>
       <c r="K705" t="n">
-        <v>2.459227771244468</v>
+        <v>2.462535160835919</v>
       </c>
     </row>
     <row r="706">
@@ -29385,7 +29385,7 @@
         <v>3</v>
       </c>
       <c r="K706" t="n">
-        <v>2.43461815898368</v>
+        <v>2.438107980153016</v>
       </c>
     </row>
     <row r="707">
@@ -29426,7 +29426,7 @@
         <v>3</v>
       </c>
       <c r="K707" t="n">
-        <v>2.326200551573592</v>
+        <v>2.333469451904161</v>
       </c>
     </row>
     <row r="708">
@@ -29467,7 +29467,7 @@
         <v>3</v>
       </c>
       <c r="K708" t="n">
-        <v>2.264299598695442</v>
+        <v>2.273161453170722</v>
       </c>
     </row>
     <row r="709">
@@ -29508,7 +29508,7 @@
         <v>3</v>
       </c>
       <c r="K709" t="n">
-        <v>2.264299598695442</v>
+        <v>2.192696467671554</v>
       </c>
     </row>
     <row r="710">
@@ -29549,7 +29549,7 @@
         <v>3</v>
       </c>
       <c r="K710" t="n">
-        <v>1.967348237245286</v>
+        <v>1.980016376199999</v>
       </c>
     </row>
     <row r="711">
@@ -29590,7 +29590,7 @@
         <v>3</v>
       </c>
       <c r="K711" t="n">
-        <v>1.967348237245286</v>
+        <v>1.873411258523338</v>
       </c>
     </row>
     <row r="712">
@@ -29631,7 +29631,7 @@
         <v>3</v>
       </c>
       <c r="K712" t="n">
-        <v>1.86013837832737</v>
+        <v>1.873411258523338</v>
       </c>
     </row>
     <row r="713">
@@ -29672,7 +29672,7 @@
         <v>3</v>
       </c>
       <c r="K713" t="n">
-        <v>1.708920233583261</v>
+        <v>1.712586258622858</v>
       </c>
     </row>
     <row r="714">
@@ -29713,7 +29713,7 @@
         <v>3</v>
       </c>
       <c r="K714" t="n">
-        <v>1.708920233583261</v>
+        <v>1.712586258622858</v>
       </c>
     </row>
     <row r="715">
@@ -29754,7 +29754,7 @@
         <v>3</v>
       </c>
       <c r="K715" t="n">
-        <v>1.708920233583261</v>
+        <v>1.683214146574525</v>
       </c>
     </row>
     <row r="716">
@@ -29795,7 +29795,7 @@
         <v>3</v>
       </c>
       <c r="K716" t="n">
-        <v>1.644876511437556</v>
+        <v>1.648076103268485</v>
       </c>
     </row>
     <row r="717">
@@ -29836,7 +29836,7 @@
         <v>3</v>
       </c>
       <c r="K717" t="n">
-        <v>1.644876511437556</v>
+        <v>1.648076103268485</v>
       </c>
     </row>
     <row r="718">
@@ -29877,7 +29877,7 @@
         <v>3</v>
       </c>
       <c r="K718" t="n">
-        <v>1.588400297438308</v>
+        <v>1.565590920902434</v>
       </c>
     </row>
     <row r="719">
@@ -29918,7 +29918,7 @@
         <v>3</v>
       </c>
       <c r="K719" t="n">
-        <v>1.56213921201233</v>
+        <v>1.565590920902434</v>
       </c>
     </row>
     <row r="720">
@@ -29959,7 +29959,7 @@
         <v>3</v>
       </c>
       <c r="K720" t="n">
-        <v>1.49043004624687</v>
+        <v>1.495601309229054</v>
       </c>
     </row>
     <row r="721">
@@ -30000,7 +30000,7 @@
         <v>3</v>
       </c>
       <c r="K721" t="n">
-        <v>1.49043004624687</v>
+        <v>1.495601309229054</v>
       </c>
     </row>
     <row r="722">
@@ -30041,7 +30041,7 @@
         <v>3</v>
       </c>
       <c r="K722" t="n">
-        <v>1.454721901079359</v>
+        <v>1.45915516018987</v>
       </c>
     </row>
     <row r="723">
@@ -30082,7 +30082,7 @@
         <v>3</v>
       </c>
       <c r="K723" t="n">
-        <v>1.416444895233653</v>
+        <v>1.386713964801691</v>
       </c>
     </row>
     <row r="724">
@@ -30123,7 +30123,7 @@
         <v>3</v>
       </c>
       <c r="K724" t="n">
-        <v>1.361824591920848</v>
+        <v>1.36389647528651</v>
       </c>
     </row>
     <row r="725">
@@ -30164,7 +30164,7 @@
         <v>3</v>
       </c>
       <c r="K725" t="n">
-        <v>1.357822264239969</v>
+        <v>1.357579586272581</v>
       </c>
     </row>
     <row r="726">
@@ -30205,7 +30205,7 @@
         <v>3</v>
       </c>
       <c r="K726" t="n">
-        <v>1.387877769991956</v>
+        <v>1.42228495564398</v>
       </c>
     </row>
     <row r="727">
@@ -30246,7 +30246,7 @@
         <v>3</v>
       </c>
       <c r="K727" t="n">
-        <v>1.474383223676014</v>
+        <v>1.468182534704101</v>
       </c>
     </row>
     <row r="728">
@@ -30287,7 +30287,7 @@
         <v>3</v>
       </c>
       <c r="K728" t="n">
-        <v>1.528205210346673</v>
+        <v>1.521965635534352</v>
       </c>
     </row>
     <row r="729">
@@ -30328,7 +30328,7 @@
         <v>3</v>
       </c>
       <c r="K729" t="n">
-        <v>1.528205210346673</v>
+        <v>1.521965635534352</v>
       </c>
     </row>
     <row r="730">
@@ -30369,7 +30369,7 @@
         <v>3</v>
       </c>
       <c r="K730" t="n">
-        <v>1.583339945519227</v>
+        <v>1.576420366644265</v>
       </c>
     </row>
     <row r="731">
@@ -30410,7 +30410,7 @@
         <v>3</v>
       </c>
       <c r="K731" t="n">
-        <v>1.701033919475326</v>
+        <v>1.693966551294203</v>
       </c>
     </row>
     <row r="732">
@@ -30451,7 +30451,7 @@
         <v>3</v>
       </c>
       <c r="K732" t="n">
-        <v>1.701033919475326</v>
+        <v>1.693966551294203</v>
       </c>
     </row>
     <row r="733">
@@ -30492,7 +30492,7 @@
         <v>3</v>
       </c>
       <c r="K733" t="n">
-        <v>1.856092099585409</v>
+        <v>1.846674206629854</v>
       </c>
     </row>
     <row r="734">
@@ -30533,7 +30533,7 @@
         <v>3</v>
       </c>
       <c r="K734" t="n">
-        <v>1.931189381095863</v>
+        <v>1.922830201506537</v>
       </c>
     </row>
     <row r="735">
@@ -30574,7 +30574,7 @@
         <v>3</v>
       </c>
       <c r="K735" t="n">
-        <v>2.003662893191851</v>
+        <v>2.002276854943303</v>
       </c>
     </row>
     <row r="736">
@@ -30615,7 +30615,7 @@
         <v>3</v>
       </c>
       <c r="K736" t="n">
-        <v>1.964593875611641</v>
+        <v>1.969497098474953</v>
       </c>
     </row>
     <row r="737">
@@ -30656,7 +30656,7 @@
         <v>3</v>
       </c>
       <c r="K737" t="n">
-        <v>1.964593875611641</v>
+        <v>1.969497098474953</v>
       </c>
     </row>
     <row r="738">
@@ -30697,7 +30697,7 @@
         <v>3</v>
       </c>
       <c r="K738" t="n">
-        <v>1.754517992862946</v>
+        <v>1.762895713385428</v>
       </c>
     </row>
     <row r="739">
@@ -30738,7 +30738,7 @@
         <v>3</v>
       </c>
       <c r="K739" t="n">
-        <v>1.628068560037562</v>
+        <v>1.63564320829893</v>
       </c>
     </row>
     <row r="740">
@@ -30779,7 +30779,7 @@
         <v>3</v>
       </c>
       <c r="K740" t="n">
-        <v>1.411330553839739</v>
+        <v>1.415714365888807</v>
       </c>
     </row>
     <row r="741">
@@ -30820,7 +30820,7 @@
         <v>3</v>
       </c>
       <c r="K741" t="n">
-        <v>1.411330553839739</v>
+        <v>1.415714365888807</v>
       </c>
     </row>
     <row r="742">
@@ -30861,7 +30861,7 @@
         <v>3</v>
       </c>
       <c r="K742" t="n">
-        <v>1.463640379107531</v>
+        <v>1.461633231616903</v>
       </c>
     </row>
     <row r="743">
@@ -30902,7 +30902,7 @@
         <v>3</v>
       </c>
       <c r="K743" t="n">
-        <v>1.463640379107531</v>
+        <v>1.461633231616903</v>
       </c>
     </row>
     <row r="744">
@@ -30943,7 +30943,7 @@
         <v>3</v>
       </c>
       <c r="K744" t="n">
-        <v>1.542850296116594</v>
+        <v>1.539380061538582</v>
       </c>
     </row>
     <row r="745">
@@ -30984,7 +30984,7 @@
         <v>3</v>
       </c>
       <c r="K745" t="n">
-        <v>1.542850296116594</v>
+        <v>1.539380061538582</v>
       </c>
     </row>
     <row r="746">
@@ -31025,7 +31025,7 @@
         <v>3</v>
       </c>
       <c r="K746" t="n">
-        <v>1.56972057377767</v>
+        <v>1.586620735203013</v>
       </c>
     </row>
     <row r="747">
@@ -31066,7 +31066,7 @@
         <v>3</v>
       </c>
       <c r="K747" t="n">
-        <v>1.588168873634134</v>
+        <v>1.586620735203013</v>
       </c>
     </row>
     <row r="748">
@@ -31107,7 +31107,7 @@
         <v>3</v>
       </c>
       <c r="K748" t="n">
-        <v>1.59698593109862</v>
+        <v>1.596509204469319</v>
       </c>
     </row>
     <row r="749">
@@ -31148,7 +31148,7 @@
         <v>3</v>
       </c>
       <c r="K749" t="n">
-        <v>1.612466123059784</v>
+        <v>1.612360344561925</v>
       </c>
     </row>
     <row r="750">
@@ -31189,7 +31189,7 @@
         <v>3</v>
       </c>
       <c r="K750" t="n">
-        <v>1.612466123059784</v>
+        <v>1.612360344561925</v>
       </c>
     </row>
     <row r="751">
@@ -31230,7 +31230,7 @@
         <v>3</v>
       </c>
       <c r="K751" t="n">
-        <v>1.610180754619413</v>
+        <v>1.610449938295707</v>
       </c>
     </row>
     <row r="752">
@@ -31271,7 +31271,7 @@
         <v>3</v>
       </c>
       <c r="K752" t="n">
-        <v>1.623648222273373</v>
+        <v>1.623074320521391</v>
       </c>
     </row>
     <row r="753">
@@ -31312,7 +31312,7 @@
         <v>3</v>
       </c>
       <c r="K753" t="n">
-        <v>1.623648222273373</v>
+        <v>1.623074320521391</v>
       </c>
     </row>
     <row r="754">
@@ -31353,7 +31353,7 @@
         <v>3</v>
       </c>
       <c r="K754" t="n">
-        <v>1.622013018675033</v>
+        <v>1.624365395543103</v>
       </c>
     </row>
     <row r="755">
@@ -31394,7 +31394,7 @@
         <v>3</v>
       </c>
       <c r="K755" t="n">
-        <v>1.535534834485925</v>
+        <v>1.536768374139363</v>
       </c>
     </row>
     <row r="756">
@@ -31435,7 +31435,7 @@
         <v>3</v>
       </c>
       <c r="K756" t="n">
-        <v>1.535534834485925</v>
+        <v>1.536768374139363</v>
       </c>
     </row>
     <row r="757">
@@ -31476,7 +31476,7 @@
         <v>3</v>
       </c>
       <c r="K757" t="n">
-        <v>1.535534834485925</v>
+        <v>1.536768374139363</v>
       </c>
     </row>
     <row r="758">
@@ -31517,7 +31517,7 @@
         <v>3</v>
       </c>
       <c r="K758" t="n">
-        <v>1.518363871998768</v>
+        <v>1.517701932223214</v>
       </c>
     </row>
     <row r="759">
@@ -31558,7 +31558,7 @@
         <v>3</v>
       </c>
       <c r="K759" t="n">
-        <v>1.437142010422004</v>
+        <v>1.43895242353117</v>
       </c>
     </row>
     <row r="760">
@@ -31599,7 +31599,7 @@
         <v>3</v>
       </c>
       <c r="K760" t="n">
-        <v>1.416938535151454</v>
+        <v>1.418130298731935</v>
       </c>
     </row>
     <row r="761">
@@ -31640,7 +31640,7 @@
         <v>3</v>
       </c>
       <c r="K761" t="n">
-        <v>1.4059865388659</v>
+        <v>1.407224418635325</v>
       </c>
     </row>
     <row r="762">
@@ -31681,7 +31681,7 @@
         <v>3</v>
       </c>
       <c r="K762" t="n">
-        <v>1.389829268916629</v>
+        <v>1.391970808451878</v>
       </c>
     </row>
     <row r="763">
@@ -31722,7 +31722,7 @@
         <v>3</v>
       </c>
       <c r="K763" t="n">
-        <v>1.457731679114018</v>
+        <v>1.454176045103107</v>
       </c>
     </row>
     <row r="764">
@@ -31763,7 +31763,7 @@
         <v>3</v>
       </c>
       <c r="K764" t="n">
-        <v>1.457731679114018</v>
+        <v>1.454176045103107</v>
       </c>
     </row>
     <row r="765">
@@ -31804,7 +31804,7 @@
         <v>3</v>
       </c>
       <c r="K765" t="n">
-        <v>1.602765195103935</v>
+        <v>1.60015187067598</v>
       </c>
     </row>
     <row r="766">
@@ -31845,7 +31845,7 @@
         <v>3</v>
       </c>
       <c r="K766" t="n">
-        <v>1.645938856782272</v>
+        <v>1.644598100525032</v>
       </c>
     </row>
     <row r="767">
@@ -31886,7 +31886,7 @@
         <v>3</v>
       </c>
       <c r="K767" t="n">
-        <v>1.65086205045192</v>
+        <v>1.651246915623016</v>
       </c>
     </row>
     <row r="768">
@@ -31927,7 +31927,7 @@
         <v>3</v>
       </c>
       <c r="K768" t="n">
-        <v>1.656882688899178</v>
+        <v>1.656553740410196</v>
       </c>
     </row>
     <row r="769">
@@ -31968,7 +31968,7 @@
         <v>3</v>
       </c>
       <c r="K769" t="n">
-        <v>1.658299181951782</v>
+        <v>1.658542328480888</v>
       </c>
     </row>
     <row r="770">
@@ -32009,7 +32009,7 @@
         <v>3</v>
       </c>
       <c r="K770" t="n">
-        <v>1.621214772240193</v>
+        <v>1.621410905230934</v>
       </c>
     </row>
     <row r="771">
@@ -32050,7 +32050,7 @@
         <v>3</v>
       </c>
       <c r="K771" t="n">
-        <v>1.626111691365553</v>
+        <v>1.626410883111978</v>
       </c>
     </row>
     <row r="772">
@@ -32091,7 +32091,7 @@
         <v>3</v>
       </c>
       <c r="K772" t="n">
-        <v>1.600083268497904</v>
+        <v>1.600473734302414</v>
       </c>
     </row>
     <row r="773">
@@ -32132,7 +32132,7 @@
         <v>3</v>
       </c>
       <c r="K773" t="n">
-        <v>1.597658316370406</v>
+        <v>1.598176777683864</v>
       </c>
     </row>
     <row r="774">
@@ -32173,7 +32173,7 @@
         <v>3</v>
       </c>
       <c r="K774" t="n">
-        <v>1.573484351772946</v>
+        <v>1.573030103288943</v>
       </c>
     </row>
     <row r="775">
@@ -32214,7 +32214,7 @@
         <v>3</v>
       </c>
       <c r="K775" t="n">
-        <v>1.550149124987181</v>
+        <v>1.551679059859181</v>
       </c>
     </row>
     <row r="776">
@@ -32255,7 +32255,7 @@
         <v>3</v>
       </c>
       <c r="K776" t="n">
-        <v>1.550149124987181</v>
+        <v>1.551679059859181</v>
       </c>
     </row>
     <row r="777">
@@ -32296,7 +32296,7 @@
         <v>3</v>
       </c>
       <c r="K777" t="n">
-        <v>1.535490989039913</v>
+        <v>1.531222620031818</v>
       </c>
     </row>
     <row r="778">
@@ -32337,7 +32337,7 @@
         <v>3</v>
       </c>
       <c r="K778" t="n">
-        <v>1.610683562545311</v>
+        <v>1.608404270057553</v>
       </c>
     </row>
     <row r="779">
@@ -32378,7 +32378,7 @@
         <v>3</v>
       </c>
       <c r="K779" t="n">
-        <v>1.610683562545311</v>
+        <v>1.608404270057553</v>
       </c>
     </row>
     <row r="780">
@@ -32419,7 +32419,7 @@
         <v>3</v>
       </c>
       <c r="K780" t="n">
-        <v>1.610683562545311</v>
+        <v>1.608404270057553</v>
       </c>
     </row>
     <row r="781">
@@ -32460,7 +32460,7 @@
         <v>3</v>
       </c>
       <c r="K781" t="n">
-        <v>1.65052031808787</v>
+        <v>1.647901580316787</v>
       </c>
     </row>
     <row r="782">
@@ -32501,7 +32501,7 @@
         <v>3</v>
       </c>
       <c r="K782" t="n">
-        <v>1.663352898553057</v>
+        <v>1.66640571474049</v>
       </c>
     </row>
     <row r="783">
@@ -32542,7 +32542,7 @@
         <v>3</v>
       </c>
       <c r="K783" t="n">
-        <v>1.639169584595099</v>
+        <v>1.641766114375239</v>
       </c>
     </row>
     <row r="784">
@@ -32583,7 +32583,7 @@
         <v>3</v>
       </c>
       <c r="K784" t="n">
-        <v>1.639169584595099</v>
+        <v>1.641766114375239</v>
       </c>
     </row>
     <row r="785">
@@ -32624,7 +32624,7 @@
         <v>3</v>
       </c>
       <c r="K785" t="n">
-        <v>1.639169584595099</v>
+        <v>1.641766114375239</v>
       </c>
     </row>
     <row r="786">
@@ -32665,7 +32665,7 @@
         <v>3</v>
       </c>
       <c r="K786" t="n">
-        <v>1.466846655279628</v>
+        <v>1.46805458965451</v>
       </c>
     </row>
     <row r="787">
@@ -32706,7 +32706,7 @@
         <v>3</v>
       </c>
       <c r="K787" t="n">
-        <v>1.424481712947825</v>
+        <v>1.424466556311827</v>
       </c>
     </row>
     <row r="788">
@@ -32747,7 +32747,7 @@
         <v>3</v>
       </c>
       <c r="K788" t="n">
-        <v>1.426674946458663</v>
+        <v>1.427550843930794</v>
       </c>
     </row>
     <row r="789">
@@ -32788,7 +32788,7 @@
         <v>3</v>
       </c>
       <c r="K789" t="n">
-        <v>1.388737677464995</v>
+        <v>1.390619457034252</v>
       </c>
     </row>
     <row r="790">
@@ -32829,7 +32829,7 @@
         <v>3</v>
       </c>
       <c r="K790" t="n">
-        <v>1.388737677464995</v>
+        <v>1.390619457034252</v>
       </c>
     </row>
     <row r="791">
@@ -32870,7 +32870,7 @@
         <v>3</v>
       </c>
       <c r="K791" t="n">
-        <v>1.315851809743908</v>
+        <v>1.316856584236149</v>
       </c>
     </row>
     <row r="792">
@@ -32911,7 +32911,7 @@
         <v>3</v>
       </c>
       <c r="K792" t="n">
-        <v>1.315851809743908</v>
+        <v>1.316856584236149</v>
       </c>
     </row>
     <row r="793">
@@ -32952,7 +32952,7 @@
         <v>3</v>
       </c>
       <c r="K793" t="n">
-        <v>1.315851809743908</v>
+        <v>1.316856584236149</v>
       </c>
     </row>
     <row r="794">
@@ -32993,7 +32993,7 @@
         <v>3</v>
       </c>
       <c r="K794" t="n">
-        <v>1.21119443862518</v>
+        <v>1.211107967147349</v>
       </c>
     </row>
     <row r="795">
@@ -33034,7 +33034,7 @@
         <v>3</v>
       </c>
       <c r="K795" t="n">
-        <v>1.191174190868714</v>
+        <v>1.191624378807359</v>
       </c>
     </row>
     <row r="796">
@@ -33075,7 +33075,7 @@
         <v>3</v>
       </c>
       <c r="K796" t="n">
-        <v>1.255408596812928</v>
+        <v>1.254509837406959</v>
       </c>
     </row>
     <row r="797">
@@ -33116,7 +33116,7 @@
         <v>3</v>
       </c>
       <c r="K797" t="n">
-        <v>1.255408596812928</v>
+        <v>1.254509837406959</v>
       </c>
     </row>
     <row r="798">
@@ -33157,7 +33157,7 @@
         <v>3</v>
       </c>
       <c r="K798" t="n">
-        <v>1.30004727814302</v>
+        <v>1.35130818488692</v>
       </c>
     </row>
     <row r="799">
@@ -33198,7 +33198,7 @@
         <v>3</v>
       </c>
       <c r="K799" t="n">
-        <v>1.409982395079707</v>
+        <v>1.409314863919275</v>
       </c>
     </row>
     <row r="800">
@@ -33239,7 +33239,7 @@
         <v>3</v>
       </c>
       <c r="K800" t="n">
-        <v>1.447687291787138</v>
+        <v>1.447077928466838</v>
       </c>
     </row>
     <row r="801">
@@ -33280,7 +33280,7 @@
         <v>3</v>
       </c>
       <c r="K801" t="n">
-        <v>1.484278946352729</v>
+        <v>1.484381374227275</v>
       </c>
     </row>
     <row r="802">
@@ -33321,7 +33321,7 @@
         <v>3</v>
       </c>
       <c r="K802" t="n">
-        <v>1.513130508765279</v>
+        <v>1.512873307400485</v>
       </c>
     </row>
     <row r="803">
@@ -33362,7 +33362,7 @@
         <v>3</v>
       </c>
       <c r="K803" t="n">
-        <v>1.526360999900184</v>
+        <v>1.52611503965198</v>
       </c>
     </row>
     <row r="804">
@@ -33403,7 +33403,7 @@
         <v>3</v>
       </c>
       <c r="K804" t="n">
-        <v>1.668973296776535</v>
+        <v>1.668093272356203</v>
       </c>
     </row>
     <row r="805">
@@ -33444,7 +33444,7 @@
         <v>3</v>
       </c>
       <c r="K805" t="n">
-        <v>1.731309012041773</v>
+        <v>1.730503213983379</v>
       </c>
     </row>
     <row r="806">
@@ -33485,7 +33485,7 @@
         <v>3</v>
       </c>
       <c r="K806" t="n">
-        <v>1.781540024534186</v>
+        <v>1.782500586162827</v>
       </c>
     </row>
     <row r="807">
@@ -33526,7 +33526,7 @@
         <v>3</v>
       </c>
       <c r="K807" t="n">
-        <v>1.781540024534186</v>
+        <v>1.782500586162827</v>
       </c>
     </row>
     <row r="808">
@@ -33567,7 +33567,7 @@
         <v>3</v>
       </c>
       <c r="K808" t="n">
-        <v>1.781540024534186</v>
+        <v>1.782500586162827</v>
       </c>
     </row>
     <row r="809">
@@ -33608,7 +33608,7 @@
         <v>3</v>
       </c>
       <c r="K809" t="n">
-        <v>1.5038282806164</v>
+        <v>1.505450839826564</v>
       </c>
     </row>
     <row r="810">
@@ -33649,7 +33649,7 @@
         <v>3</v>
       </c>
       <c r="K810" t="n">
-        <v>1.245663507909112</v>
+        <v>1.247025884765449</v>
       </c>
     </row>
     <row r="811">
@@ -33690,7 +33690,7 @@
         <v>3</v>
       </c>
       <c r="K811" t="n">
-        <v>1.037827792884522</v>
+        <v>1.038958632434521</v>
       </c>
     </row>
     <row r="812">
@@ -33731,7 +33731,7 @@
         <v>3</v>
       </c>
       <c r="K812" t="n">
-        <v>0.9383552217234602</v>
+        <v>0.9392637355875426</v>
       </c>
     </row>
     <row r="813">
@@ -33772,7 +33772,7 @@
         <v>3</v>
       </c>
       <c r="K813" t="n">
-        <v>0.8736400230626112</v>
+        <v>0.8740146449021037</v>
       </c>
     </row>
     <row r="814">
@@ -33813,7 +33813,7 @@
         <v>3</v>
       </c>
       <c r="K814" t="n">
-        <v>0.8363483773273188</v>
+        <v>0.8366866910874583</v>
       </c>
     </row>
     <row r="815">
@@ -33854,7 +33854,7 @@
         <v>3</v>
       </c>
       <c r="K815" t="n">
-        <v>0.7976886523627105</v>
+        <v>0.7980773703191306</v>
       </c>
     </row>
     <row r="816">
@@ -33895,7 +33895,7 @@
         <v>3</v>
       </c>
       <c r="K816" t="n">
-        <v>0.7976886523627105</v>
+        <v>0.7980773703191306</v>
       </c>
     </row>
     <row r="817">
@@ -33936,7 +33936,7 @@
         <v>3</v>
       </c>
       <c r="K817" t="n">
-        <v>0.7524597540443071</v>
+        <v>0.7528663461523607</v>
       </c>
     </row>
     <row r="818">
@@ -33977,7 +33977,7 @@
         <v>3</v>
       </c>
       <c r="K818" t="n">
-        <v>0.7550536054579302</v>
+        <v>0.7549657479226958</v>
       </c>
     </row>
     <row r="819">
@@ -34018,7 +34018,7 @@
         <v>3</v>
       </c>
       <c r="K819" t="n">
-        <v>0.7550536054579302</v>
+        <v>0.7549657479226958</v>
       </c>
     </row>
     <row r="820">
@@ -34059,7 +34059,7 @@
         <v>3</v>
       </c>
       <c r="K820" t="n">
-        <v>0.761867319251107</v>
+        <v>0.7618515293192978</v>
       </c>
     </row>
     <row r="821">
@@ -34100,7 +34100,7 @@
         <v>3</v>
       </c>
       <c r="K821" t="n">
-        <v>0.761867319251107</v>
+        <v>0.7618515293192978</v>
       </c>
     </row>
     <row r="822">
@@ -34141,7 +34141,7 @@
         <v>3</v>
       </c>
       <c r="K822" t="n">
-        <v>0.761867319251107</v>
+        <v>0.7618515293192978</v>
       </c>
     </row>
     <row r="823">
@@ -34182,7 +34182,7 @@
         <v>3</v>
       </c>
       <c r="K823" t="n">
-        <v>0.761867319251107</v>
+        <v>0.7618515293192978</v>
       </c>
     </row>
     <row r="824">
@@ -34223,7 +34223,7 @@
         <v>3</v>
       </c>
       <c r="K824" t="n">
-        <v>0.7372526854463468</v>
+        <v>0.7374640260055649</v>
       </c>
     </row>
     <row r="825">
@@ -34264,7 +34264,7 @@
         <v>3</v>
       </c>
       <c r="K825" t="n">
-        <v>0.6918143305450244</v>
+        <v>0.692148363857926</v>
       </c>
     </row>
     <row r="826">
@@ -34305,7 +34305,7 @@
         <v>3</v>
       </c>
       <c r="K826" t="n">
-        <v>0.6253216690507472</v>
+        <v>0.625756364672693</v>
       </c>
     </row>
     <row r="827">
@@ -34346,7 +34346,7 @@
         <v>3</v>
       </c>
       <c r="K827" t="n">
-        <v>0.4513025567209175</v>
+        <v>0.4517034482436226</v>
       </c>
     </row>
     <row r="828">
@@ -34387,7 +34387,7 @@
         <v>3</v>
       </c>
       <c r="K828" t="n">
-        <v>0.3317775833481664</v>
+        <v>0.3319303948117</v>
       </c>
     </row>
     <row r="829">
@@ -34428,7 +34428,7 @@
         <v>3</v>
       </c>
       <c r="K829" t="n">
-        <v>0.2973576002577951</v>
+        <v>0.297492114265517</v>
       </c>
     </row>
     <row r="830">
@@ -34469,7 +34469,7 @@
         <v>3</v>
       </c>
       <c r="K830" t="n">
-        <v>0.2637201247108184</v>
+        <v>0.2638381410719248</v>
       </c>
     </row>
     <row r="831">
@@ -34510,7 +34510,7 @@
         <v>3</v>
       </c>
       <c r="K831" t="n">
-        <v>0.2103350914282464</v>
+        <v>0.2103356169046333</v>
       </c>
     </row>
     <row r="832">
@@ -34551,7 +34551,7 @@
         <v>3</v>
       </c>
       <c r="K832" t="n">
-        <v>0.2271430704265892</v>
+        <v>0.2271267330519866</v>
       </c>
     </row>
     <row r="833">
@@ -34592,7 +34592,7 @@
         <v>3</v>
       </c>
       <c r="K833" t="n">
-        <v>0.2416766239145968</v>
+        <v>0.2416507279978915</v>
       </c>
     </row>
     <row r="834">
@@ -34633,7 +34633,7 @@
         <v>3</v>
       </c>
       <c r="K834" t="n">
-        <v>0.2942158157727213</v>
+        <v>0.2941931848203747</v>
       </c>
     </row>
     <row r="835">
@@ -34674,7 +34674,7 @@
         <v>3</v>
       </c>
       <c r="K835" t="n">
-        <v>0.2609192312848662</v>
+        <v>0.2609229729646434</v>
       </c>
     </row>
   </sheetData>
